--- a/АЧХ_result.xlsx
+++ b/АЧХ_result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{325014C8-87D0-4FCB-B8CC-D6B976C472F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A84B767-40C5-4C51-BA3A-94F82940D0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="195" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="2010" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,30 +34,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
-  <si>
-    <t>Установленное значение при коэффициенте усиления 10</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>частота\канал</t>
-  </si>
-  <si>
-    <t>Измеренное значение при коэффициенте усиления 10</t>
-  </si>
-  <si>
-    <t>Погрешность при коеффициенте усления 10</t>
-  </si>
-  <si>
-    <t>Установленное значение при коэффициенте усиления 1</t>
   </si>
   <si>
     <t>частота/канал</t>
   </si>
   <si>
-    <t>Измеренное значение при коэффициенте усиления 1</t>
+    <t>Установленное значение при коэффициенте усиления BOE "-1", BOC "0"</t>
   </si>
   <si>
-    <t>Погрешность при коеффициенте усления 1</t>
+    <t>Измеренное значение при коэффициенте усиления BOE "-1", BOC "0"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "-1", BOC "0"</t>
+  </si>
+  <si>
+    <t>Установленное значение при коэффициенте усиления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Измеренное значение при коэффициенте усиления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Установленное значение при коэффициенте усиления BOE "0", BOC "0"</t>
+  </si>
+  <si>
+    <t>Измеренное значение при коэффициенте усиления BOE "0", BOC "0"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "0", BOC "0"</t>
   </si>
 </sst>
 </file>
@@ -123,16 +132,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -489,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="20" width="13.5703125" customWidth="1"/>
@@ -497,7 +546,7 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -507,34 +556,34 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-      <c r="M1" s="5">
-        <v>1.0494033999999999E-2</v>
-      </c>
-      <c r="N1" s="5">
-        <v>1.0488305999999999E-2</v>
-      </c>
-      <c r="O1" s="5">
-        <v>1.0509714E-2</v>
-      </c>
-      <c r="P1" s="5">
-        <v>1.0486987E-2</v>
-      </c>
-      <c r="Q1" s="5">
-        <v>1.0473503E-2</v>
-      </c>
-      <c r="R1" s="5">
-        <v>1.0518176000000001E-2</v>
-      </c>
-      <c r="S1" s="5">
-        <v>1.0392599000000001E-2</v>
-      </c>
-      <c r="T1" s="5">
-        <v>1.0447369E-2</v>
+      <c r="M1" s="3">
+        <v>1.5376035E-2</v>
+      </c>
+      <c r="N1" s="3">
+        <v>1.537591E-2</v>
+      </c>
+      <c r="O1" s="3">
+        <v>1.5391224E-2</v>
+      </c>
+      <c r="P1" s="3">
+        <v>1.5368181999999999E-2</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>1.5366306E-2</v>
+      </c>
+      <c r="R1" s="3">
+        <v>1.5395584E-2</v>
+      </c>
+      <c r="S1" s="3">
+        <v>1.528886E-2</v>
+      </c>
+      <c r="T1" s="3">
+        <v>1.5344295000000001E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -560,29 +609,29 @@
       <c r="I2">
         <v>8</v>
       </c>
-      <c r="M2" s="5">
-        <v>1.0125511E-2</v>
-      </c>
-      <c r="N2" s="5">
-        <v>1.0133171E-2</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1.0129958999999999E-2</v>
-      </c>
-      <c r="P2" s="5">
-        <v>1.0135435999999999E-2</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>1.0096318E-2</v>
-      </c>
-      <c r="R2" s="5">
-        <v>1.0156302000000001E-2</v>
-      </c>
-      <c r="S2" s="5">
-        <v>9.9705479999999992E-3</v>
-      </c>
-      <c r="T2" s="5">
-        <v>1.0059319000000001E-2</v>
+      <c r="M2" s="3">
+        <v>1.5305892999999999E-2</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1.5330559000000001E-2</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1.5318595000000001E-2</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1.5323323E-2</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1.5290596E-2</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1.5335092999999999E-2</v>
+      </c>
+      <c r="S2" s="3">
+        <v>1.5176845E-2</v>
+      </c>
+      <c r="T2" s="3">
+        <v>1.5262398E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -591,59 +640,59 @@
       </c>
       <c r="B3" s="1">
         <f>M1</f>
-        <v>1.0494033999999999E-2</v>
+        <v>1.5376035E-2</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:I10" si="0">N1</f>
-        <v>1.0488305999999999E-2</v>
+        <v>1.537591E-2</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0509714E-2</v>
+        <v>1.5391224E-2</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0486987E-2</v>
+        <v>1.5368181999999999E-2</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0473503E-2</v>
+        <v>1.5366306E-2</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0518176000000001E-2</v>
+        <v>1.5395584E-2</v>
       </c>
       <c r="H3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0392599000000001E-2</v>
+        <v>1.528886E-2</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" si="0"/>
-        <v>1.0447369E-2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1.0072579999999999E-2</v>
-      </c>
-      <c r="N3" s="5">
-        <v>1.0079855E-2</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1.0063241000000001E-2</v>
-      </c>
-      <c r="P3" s="5">
-        <v>1.0087572E-2</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>1.0038597999999999E-2</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1.0099267E-2</v>
-      </c>
-      <c r="S3" s="5">
-        <v>9.9135270000000001E-3</v>
-      </c>
-      <c r="T3" s="5">
-        <v>1.0005877E-2</v>
+        <v>1.5344295000000001E-2</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1.5320057999999999E-2</v>
+      </c>
+      <c r="N3" s="3">
+        <v>1.5341385000000001E-2</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1.5318424000000001E-2</v>
+      </c>
+      <c r="P3" s="3">
+        <v>1.5333683000000001E-2</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1.5292973E-2</v>
+      </c>
+      <c r="R3" s="3">
+        <v>1.5344165E-2</v>
+      </c>
+      <c r="S3" s="3">
+        <v>1.5187617E-2</v>
+      </c>
+      <c r="T3" s="3">
+        <v>1.5265819999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -652,59 +701,59 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B10" si="1">M2</f>
-        <v>1.0125511E-2</v>
+        <v>1.5305892999999999E-2</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0133171E-2</v>
+        <v>1.5330559000000001E-2</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0129958999999999E-2</v>
+        <v>1.5318595000000001E-2</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0135435999999999E-2</v>
+        <v>1.5323323E-2</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0096318E-2</v>
+        <v>1.5290596E-2</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0156302000000001E-2</v>
+        <v>1.5335092999999999E-2</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="0"/>
-        <v>9.9705479999999992E-3</v>
+        <v>1.5176845E-2</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" si="0"/>
-        <v>1.0059319000000001E-2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1.0291616999999999E-2</v>
-      </c>
-      <c r="N4" s="5">
-        <v>1.0285301E-2</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1.0278666000000001E-2</v>
-      </c>
-      <c r="P4" s="5">
-        <v>1.0302929000000001E-2</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>1.0258524E-2</v>
-      </c>
-      <c r="R4" s="5">
-        <v>1.0298618000000001E-2</v>
-      </c>
-      <c r="S4" s="5">
-        <v>1.0191199E-2</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1.0240351E-2</v>
+        <v>1.5262398E-2</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1.5387424E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1.5394990000000001E-2</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1.5376333000000001E-2</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1.5391624E-2</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1.5357696000000001E-2</v>
+      </c>
+      <c r="R4" s="3">
+        <v>1.5393785E-2</v>
+      </c>
+      <c r="S4" s="3">
+        <v>1.5307537E-2</v>
+      </c>
+      <c r="T4" s="3">
+        <v>1.5342791999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -713,59 +762,59 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="1"/>
-        <v>1.0072579999999999E-2</v>
+        <v>1.5320057999999999E-2</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0079855E-2</v>
+        <v>1.5341385000000001E-2</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0063241000000001E-2</v>
+        <v>1.5318424000000001E-2</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0087572E-2</v>
+        <v>1.5333683000000001E-2</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0038597999999999E-2</v>
+        <v>1.5292973E-2</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0099267E-2</v>
+        <v>1.5344165E-2</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" si="0"/>
-        <v>9.9135270000000001E-3</v>
+        <v>1.5187617E-2</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" si="0"/>
-        <v>1.0005877E-2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1.0501385E-2</v>
-      </c>
-      <c r="N5" s="5">
-        <v>1.0481285E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.0489877E-2</v>
-      </c>
-      <c r="P5" s="5">
-        <v>1.049393E-2</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1.0463108E-2</v>
-      </c>
-      <c r="R5" s="5">
-        <v>1.0497444E-2</v>
-      </c>
-      <c r="S5" s="5">
-        <v>1.0431411999999999E-2</v>
-      </c>
-      <c r="T5" s="5">
-        <v>1.0466695E-2</v>
+        <v>1.5265819999999999E-2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.5424235E-2</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1.5416251000000001E-2</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1.5419547E-2</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1.5417858E-2</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1.5395139E-2</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1.5422699E-2</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1.5376453999999999E-2</v>
+      </c>
+      <c r="T5" s="3">
+        <v>1.5395277000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -774,59 +823,59 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="1"/>
-        <v>1.0291616999999999E-2</v>
+        <v>1.5387424E-2</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0285301E-2</v>
+        <v>1.5394990000000001E-2</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0278666000000001E-2</v>
+        <v>1.5376333000000001E-2</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0302929000000001E-2</v>
+        <v>1.5391624E-2</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0258524E-2</v>
+        <v>1.5357696000000001E-2</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0298618000000001E-2</v>
+        <v>1.5393785E-2</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0191199E-2</v>
+        <v>1.5307537E-2</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="0"/>
-        <v>1.0240351E-2</v>
-      </c>
-      <c r="M6" s="5">
-        <v>1.0584153000000001E-2</v>
-      </c>
-      <c r="N6" s="5">
-        <v>1.0567930999999999E-2</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1.0585679000000001E-2</v>
-      </c>
-      <c r="P6" s="5">
-        <v>1.0580803999999999E-2</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>1.0545996E-2</v>
-      </c>
-      <c r="R6" s="5">
-        <v>1.0583868999999999E-2</v>
-      </c>
-      <c r="S6" s="5">
-        <v>1.0541148E-2</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1.0563116000000001E-2</v>
+        <v>1.5342791999999999E-2</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1.5450648000000001E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1.5437126000000001E-2</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1.5445314999999999E-2</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1.5436627E-2</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1.5418896E-2</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1.5444869E-2</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1.5412613E-2</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1.542731E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -835,59 +884,59 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="1"/>
-        <v>1.0501385E-2</v>
+        <v>1.5424235E-2</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0481285E-2</v>
+        <v>1.5416251000000001E-2</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0489877E-2</v>
+        <v>1.5419547E-2</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>1.049393E-2</v>
+        <v>1.5417858E-2</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0463108E-2</v>
+        <v>1.5395139E-2</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0497444E-2</v>
+        <v>1.5422699E-2</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0431411999999999E-2</v>
+        <v>1.5376453999999999E-2</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v>1.0466695E-2</v>
-      </c>
-      <c r="M7" s="5">
-        <v>1.0618206E-2</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1.0597331E-2</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1.0613358999999999E-2</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1.059712E-2</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1.0579145E-2</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1.0614465E-2</v>
-      </c>
-      <c r="S7" s="5">
-        <v>1.0574251999999999E-2</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1.0587200999999999E-2</v>
+        <v>1.5395277000000001E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1.5467297E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1.5453483E-2</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1.5465311000000001E-2</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1.5453695999999999E-2</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>1.5434441E-2</v>
+      </c>
+      <c r="R7" s="3">
+        <v>1.546058E-2</v>
+      </c>
+      <c r="S7" s="3">
+        <v>1.5431287E-2</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1.544688E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -896,59 +945,59 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="1"/>
-        <v>1.0584153000000001E-2</v>
+        <v>1.5450648000000001E-2</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0567930999999999E-2</v>
+        <v>1.5437126000000001E-2</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0585679000000001E-2</v>
+        <v>1.5445314999999999E-2</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0580803999999999E-2</v>
+        <v>1.5436627E-2</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0545996E-2</v>
+        <v>1.5418896E-2</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0583868999999999E-2</v>
+        <v>1.5444869E-2</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0541148E-2</v>
+        <v>1.5412613E-2</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="0"/>
-        <v>1.0563116000000001E-2</v>
-      </c>
-      <c r="M8" s="5">
-        <v>1.0632855E-2</v>
-      </c>
-      <c r="N8" s="5">
-        <v>1.0606206E-2</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1.0624727E-2</v>
-      </c>
-      <c r="P8" s="5">
-        <v>1.0614002000000001E-2</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>1.0590876000000001E-2</v>
-      </c>
-      <c r="R8" s="5">
-        <v>1.0623273000000001E-2</v>
-      </c>
-      <c r="S8" s="5">
-        <v>1.0590271E-2</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1.0605582000000001E-2</v>
+        <v>1.542731E-2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1.5490632000000001E-2</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1.5474174E-2</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1.5484538000000001E-2</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1.5475826999999999E-2</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1.5462731E-2</v>
+      </c>
+      <c r="R8" s="3">
+        <v>1.5482434999999999E-2</v>
+      </c>
+      <c r="S8" s="3">
+        <v>1.5458355999999999E-2</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1.5470955999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -957,59 +1006,59 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="1"/>
-        <v>1.0618206E-2</v>
+        <v>1.5467297E-2</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0597331E-2</v>
+        <v>1.5453483E-2</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0613358999999999E-2</v>
+        <v>1.5465311000000001E-2</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>1.059712E-2</v>
+        <v>1.5453695999999999E-2</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0579145E-2</v>
+        <v>1.5434441E-2</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0614465E-2</v>
+        <v>1.546058E-2</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0574251999999999E-2</v>
+        <v>1.5431287E-2</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="0"/>
-        <v>1.0587200999999999E-2</v>
-      </c>
-      <c r="M9" s="5">
-        <v>3.0131411E-2</v>
-      </c>
-      <c r="N9" s="5">
-        <v>3.0141085000000001E-2</v>
-      </c>
-      <c r="O9" s="5">
-        <v>2.9945295E-2</v>
-      </c>
-      <c r="P9" s="5">
-        <v>3.0340947E-2</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>3.0025737E-2</v>
-      </c>
-      <c r="R9" s="5">
-        <v>3.019179E-2</v>
-      </c>
-      <c r="S9" s="5">
-        <v>2.9763161999999999E-2</v>
-      </c>
-      <c r="T9" s="5">
-        <v>2.9904217E-2</v>
+        <v>1.544688E-2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>8.985916E-3</v>
+      </c>
+      <c r="N9" s="3">
+        <v>8.9683349999999992E-3</v>
+      </c>
+      <c r="O9" s="3">
+        <v>8.8729020000000002E-3</v>
+      </c>
+      <c r="P9" s="3">
+        <v>9.0172989999999995E-3</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>8.9233200000000002E-3</v>
+      </c>
+      <c r="R9" s="3">
+        <v>8.9655870000000006E-3</v>
+      </c>
+      <c r="S9" s="3">
+        <v>8.8888860000000004E-3</v>
+      </c>
+      <c r="T9" s="3">
+        <v>8.9290859999999993E-3</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1018,90 +1067,90 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="1"/>
-        <v>1.0632855E-2</v>
+        <v>1.5490632000000001E-2</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0606206E-2</v>
+        <v>1.5474174E-2</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0624727E-2</v>
+        <v>1.5484538000000001E-2</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0614002000000001E-2</v>
+        <v>1.5475826999999999E-2</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0590876000000001E-2</v>
+        <v>1.5462731E-2</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0623273000000001E-2</v>
+        <v>1.5482434999999999E-2</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0590271E-2</v>
+        <v>1.5458355999999999E-2</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="0"/>
-        <v>1.0605582000000001E-2</v>
-      </c>
-      <c r="M10" s="5">
-        <v>4.1457887999999998E-2</v>
-      </c>
-      <c r="N10" s="5">
-        <v>4.1428588000000002E-2</v>
-      </c>
-      <c r="O10" s="5">
-        <v>4.1284281999999999E-2</v>
-      </c>
-      <c r="P10" s="5">
-        <v>4.1602548000000003E-2</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>4.1383247999999997E-2</v>
-      </c>
-      <c r="R10" s="5">
-        <v>4.1467591999999998E-2</v>
-      </c>
-      <c r="S10" s="5">
-        <v>4.1339519999999998E-2</v>
-      </c>
-      <c r="T10" s="5">
-        <v>4.1283432000000002E-2</v>
+        <v>1.5470955999999999E-2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1.2896555000000001E-2</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1.2819697E-2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.2756648000000001E-2</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1.2875129000000001E-2</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1.2809541000000001E-2</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1.2843141000000001E-2</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1.2857366E-2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1.2847195E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M11" s="5">
-        <v>4.5550148999999998E-2</v>
-      </c>
-      <c r="N11" s="5">
-        <v>4.5443698999999997E-2</v>
-      </c>
-      <c r="O11" s="5">
-        <v>4.5377102000000002E-2</v>
-      </c>
-      <c r="P11" s="5">
-        <v>4.5608825999999998E-2</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>4.5470916E-2</v>
-      </c>
-      <c r="R11" s="5">
-        <v>4.5559015000000001E-2</v>
-      </c>
-      <c r="S11" s="5">
-        <v>4.5512863000000001E-2</v>
-      </c>
-      <c r="T11" s="5">
-        <v>4.5396559000000003E-2</v>
+      <c r="M11" s="3">
+        <v>1.4292417E-2</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1.4190101E-2</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.4151115000000001E-2</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1.4236709E-2</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1.4195940000000001E-2</v>
+      </c>
+      <c r="R11" s="3">
+        <v>1.4232452E-2</v>
+      </c>
+      <c r="S11" s="3">
+        <v>1.4270338E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>1.425939E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1111,34 +1160,34 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="M12" s="5">
-        <v>4.7938927999999999E-2</v>
-      </c>
-      <c r="N12" s="5">
-        <v>4.7806762000000003E-2</v>
-      </c>
-      <c r="O12" s="5">
-        <v>4.7828294E-2</v>
-      </c>
-      <c r="P12" s="5">
-        <v>4.7889393000000002E-2</v>
-      </c>
-      <c r="Q12" s="5">
-        <v>4.7811590000000001E-2</v>
-      </c>
-      <c r="R12" s="5">
-        <v>4.7953102999999997E-2</v>
-      </c>
-      <c r="S12" s="5">
-        <v>4.7797422999999999E-2</v>
-      </c>
-      <c r="T12" s="5">
-        <v>4.7794666E-2</v>
+      <c r="M12" s="3">
+        <v>1.4789633E-2</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1.4681454E-2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.4664734E-2</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1.4720458000000001E-2</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1.4680418000000001E-2</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.4744762999999999E-2</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1.4699577E-2</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1.4753726E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1164,29 +1213,29 @@
       <c r="I13">
         <v>8</v>
       </c>
-      <c r="M13" s="5">
-        <v>4.8385723999999998E-2</v>
-      </c>
-      <c r="N13" s="5">
-        <v>4.8330642E-2</v>
-      </c>
-      <c r="O13" s="5">
-        <v>4.833585E-2</v>
-      </c>
-      <c r="P13" s="5">
-        <v>4.8378833000000003E-2</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>4.8218842999999997E-2</v>
-      </c>
-      <c r="R13" s="5">
-        <v>4.8402454999999997E-2</v>
-      </c>
-      <c r="S13" s="5">
-        <v>4.8116259000000002E-2</v>
-      </c>
-      <c r="T13" s="5">
-        <v>4.8199624000000003E-2</v>
+      <c r="M13" s="3">
+        <v>1.4701643E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>1.4636616999999999E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1.460235E-2</v>
+      </c>
+      <c r="P13" s="3">
+        <v>1.4660184E-2</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1.4591923999999999E-2</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.4672404E-2</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1.4565448999999999E-2</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1.464184E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -1195,59 +1244,59 @@
       </c>
       <c r="B14" s="1">
         <f>M9</f>
-        <v>3.0131411E-2</v>
+        <v>8.985916E-3</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" ref="C14:I21" si="2">N9</f>
-        <v>3.0141085000000001E-2</v>
+        <v>8.9683349999999992E-3</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="2"/>
-        <v>2.9945295E-2</v>
+        <v>8.8729020000000002E-3</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="2"/>
-        <v>3.0340947E-2</v>
+        <v>9.0172989999999995E-3</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="2"/>
-        <v>3.0025737E-2</v>
+        <v>8.9233200000000002E-3</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="2"/>
-        <v>3.019179E-2</v>
+        <v>8.9655870000000006E-3</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v>2.9763161999999999E-2</v>
+        <v>8.8888860000000004E-3</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>2.9904217E-2</v>
-      </c>
-      <c r="M14" s="5">
-        <v>4.8007142000000003E-2</v>
-      </c>
-      <c r="N14" s="5">
-        <v>4.8134532000000001E-2</v>
-      </c>
-      <c r="O14" s="5">
-        <v>4.8046242000000003E-2</v>
-      </c>
-      <c r="P14" s="5">
-        <v>4.8153824999999997E-2</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>4.7803231000000002E-2</v>
-      </c>
-      <c r="R14" s="5">
-        <v>4.7988899000000002E-2</v>
-      </c>
-      <c r="S14" s="5">
-        <v>4.7696412000000001E-2</v>
-      </c>
-      <c r="T14" s="5">
-        <v>4.7777451999999998E-2</v>
+        <v>8.9290859999999993E-3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1.4582238000000001E-2</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1.4572541E-2</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1.4506811E-2</v>
+      </c>
+      <c r="P14" s="3">
+        <v>1.457554E-2</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1.4458726999999999E-2</v>
+      </c>
+      <c r="R14" s="3">
+        <v>1.4538061E-2</v>
+      </c>
+      <c r="S14" s="3">
+        <v>1.4420420999999999E-2</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1.4504530999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -1256,59 +1305,59 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" ref="B15:B21" si="3">M10</f>
-        <v>4.1457887999999998E-2</v>
+        <v>1.2896555000000001E-2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1428588000000002E-2</v>
+        <v>1.2819697E-2</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1284281999999999E-2</v>
+        <v>1.2756648000000001E-2</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1602548000000003E-2</v>
+        <v>1.2875129000000001E-2</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1383247999999997E-2</v>
+        <v>1.2809541000000001E-2</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1467591999999998E-2</v>
+        <v>1.2843141000000001E-2</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1339519999999998E-2</v>
+        <v>1.2857366E-2</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>4.1283432000000002E-2</v>
-      </c>
-      <c r="M15" s="5">
-        <v>4.5826089E-2</v>
-      </c>
-      <c r="N15" s="5">
-        <v>4.6176257999999998E-2</v>
-      </c>
-      <c r="O15" s="5">
-        <v>4.6027235999999999E-2</v>
-      </c>
-      <c r="P15" s="5">
-        <v>4.6220891E-2</v>
-      </c>
-      <c r="Q15" s="5">
-        <v>4.5628961000000003E-2</v>
-      </c>
-      <c r="R15" s="5">
-        <v>4.5809172000000002E-2</v>
-      </c>
-      <c r="S15" s="5">
-        <v>4.5618393E-2</v>
-      </c>
-      <c r="T15" s="5">
-        <v>4.5613542E-2</v>
+        <v>1.2847195E-2</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.3981667E-2</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1.4047521E-2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>1.3962280000000001E-2</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1.4055382999999999E-2</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.3871331000000001E-2</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.3936169E-2</v>
+      </c>
+      <c r="S15" s="3">
+        <v>1.3855258000000001E-2</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1.3912627E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -1317,59 +1366,59 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="3"/>
-        <v>4.5550148999999998E-2</v>
+        <v>1.4292417E-2</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5443698999999997E-2</v>
+        <v>1.4190101E-2</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5377102000000002E-2</v>
+        <v>1.4151115000000001E-2</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5608825999999998E-2</v>
+        <v>1.4236709E-2</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5470916E-2</v>
+        <v>1.4195940000000001E-2</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5559015000000001E-2</v>
+        <v>1.4232452E-2</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5512863000000001E-2</v>
+        <v>1.4270338E-2</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>4.5396559000000003E-2</v>
-      </c>
-      <c r="M16" s="5">
-        <v>3.7037548000000003E-2</v>
-      </c>
-      <c r="N16" s="5">
-        <v>3.7772853000000002E-2</v>
-      </c>
-      <c r="O16" s="5">
-        <v>3.7604138000000002E-2</v>
-      </c>
-      <c r="P16" s="5">
-        <v>3.7933670000000003E-2</v>
-      </c>
-      <c r="Q16" s="5">
-        <v>3.6930340999999998E-2</v>
-      </c>
-      <c r="R16" s="5">
-        <v>3.7049789E-2</v>
-      </c>
-      <c r="S16" s="5">
-        <v>3.7182234000000002E-2</v>
-      </c>
-      <c r="T16" s="5">
-        <v>3.6972597000000003E-2</v>
+        <v>1.425939E-2</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1.1421339000000001E-2</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1.1611799000000001E-2</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1.1520239E-2</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1.1648794000000001E-2</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1.1346047E-2</v>
+      </c>
+      <c r="R16" s="3">
+        <v>1.1378055E-2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>1.1398449E-2</v>
+      </c>
+      <c r="T16" s="3">
+        <v>1.1392868E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -1378,59 +1427,59 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="3"/>
-        <v>4.7938927999999999E-2</v>
+        <v>1.4789633E-2</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7806762000000003E-2</v>
+        <v>1.4681454E-2</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7828294E-2</v>
+        <v>1.4664734E-2</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7889393000000002E-2</v>
+        <v>1.4720458000000001E-2</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7811590000000001E-2</v>
+        <v>1.4680418000000001E-2</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7953102999999997E-2</v>
+        <v>1.4744762999999999E-2</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7797422999999999E-2</v>
+        <v>1.4699577E-2</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>4.7794666E-2</v>
-      </c>
-      <c r="M17" s="5">
-        <v>1.0490151E-2</v>
-      </c>
-      <c r="N17" s="5">
-        <v>1.0480651000000001E-2</v>
-      </c>
-      <c r="O17" s="5">
-        <v>1.0506338E-2</v>
-      </c>
-      <c r="P17" s="5">
-        <v>1.0485833E-2</v>
-      </c>
-      <c r="Q17" s="5">
-        <v>1.0479697E-2</v>
-      </c>
-      <c r="R17" s="5">
-        <v>1.0509965E-2</v>
-      </c>
-      <c r="S17" s="5">
-        <v>1.0383121E-2</v>
-      </c>
-      <c r="T17" s="5">
-        <v>1.0453898999999999E-2</v>
+        <v>1.4753726E-2</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1.5375669999999999E-2</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1.5377666E-2</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1.5388990999999999E-2</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1.5366177999999999E-2</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1.5365943999999999E-2</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1.5399579E-2</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1.5290356999999999E-2</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1.534628E-2</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -1439,59 +1488,59 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="3"/>
-        <v>4.8385723999999998E-2</v>
+        <v>1.4701643E-2</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8330642E-2</v>
+        <v>1.4636616999999999E-2</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="2"/>
-        <v>4.833585E-2</v>
+        <v>1.460235E-2</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8378833000000003E-2</v>
+        <v>1.4660184E-2</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8218842999999997E-2</v>
+        <v>1.4591923999999999E-2</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8402454999999997E-2</v>
+        <v>1.4672404E-2</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8116259000000002E-2</v>
+        <v>1.4565448999999999E-2</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>4.8199624000000003E-2</v>
-      </c>
-      <c r="M18" s="5">
-        <v>1.0123907999999999E-2</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1.0124431999999999E-2</v>
-      </c>
-      <c r="O18" s="5">
-        <v>1.0119766000000001E-2</v>
-      </c>
-      <c r="P18" s="5">
-        <v>1.0137551999999999E-2</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>1.009993E-2</v>
-      </c>
-      <c r="R18" s="5">
-        <v>1.0151504E-2</v>
-      </c>
-      <c r="S18" s="5">
-        <v>9.9624929999999993E-3</v>
-      </c>
-      <c r="T18" s="5">
-        <v>1.0060243E-2</v>
+        <v>1.464184E-2</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1.5309168E-2</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1.5330808E-2</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1.5316252000000001E-2</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.532235E-2</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>1.5290758999999999E-2</v>
+      </c>
+      <c r="R18" s="3">
+        <v>1.5338831000000001E-2</v>
+      </c>
+      <c r="S18" s="3">
+        <v>1.517571E-2</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1.5264967000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -1500,59 +1549,59 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="3"/>
-        <v>4.8007142000000003E-2</v>
+        <v>1.4582238000000001E-2</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="2"/>
-        <v>4.8134532000000001E-2</v>
+        <v>1.4572541E-2</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="2"/>
-        <v>4.8046242000000003E-2</v>
+        <v>1.4506811E-2</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="2"/>
-        <v>4.8153824999999997E-2</v>
+        <v>1.457554E-2</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
-        <v>4.7803231000000002E-2</v>
+        <v>1.4458726999999999E-2</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>4.7988899000000002E-2</v>
+        <v>1.4538061E-2</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v>4.7696412000000001E-2</v>
+        <v>1.4420420999999999E-2</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>4.7777451999999998E-2</v>
-      </c>
-      <c r="M19" s="5">
-        <v>1.0066887E-2</v>
-      </c>
-      <c r="N19" s="5">
-        <v>1.0076791999999999E-2</v>
-      </c>
-      <c r="O19" s="5">
-        <v>1.0065421E-2</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1.0089071E-2</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>1.0036257E-2</v>
-      </c>
-      <c r="R19" s="5">
-        <v>1.0085612000000001E-2</v>
-      </c>
-      <c r="S19" s="5">
-        <v>9.9118729999999999E-3</v>
-      </c>
-      <c r="T19" s="5">
-        <v>1.0002407E-2</v>
+        <v>1.4504530999999999E-2</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1.5318884E-2</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1.5343228E-2</v>
+      </c>
+      <c r="O19" s="3">
+        <v>1.5319531000000001E-2</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1.5340347000000001E-2</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1.5297453000000001E-2</v>
+      </c>
+      <c r="R19" s="3">
+        <v>1.5346501E-2</v>
+      </c>
+      <c r="S19" s="3">
+        <v>1.5188333E-2</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1.5267694E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1561,59 +1610,59 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="3"/>
-        <v>4.5826089E-2</v>
+        <v>1.3981667E-2</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="2"/>
-        <v>4.6176257999999998E-2</v>
+        <v>1.4047521E-2</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="2"/>
-        <v>4.6027235999999999E-2</v>
+        <v>1.3962280000000001E-2</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>4.6220891E-2</v>
+        <v>1.4055382999999999E-2</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
-        <v>4.5628961000000003E-2</v>
+        <v>1.3871331000000001E-2</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>4.5809172000000002E-2</v>
+        <v>1.3936169E-2</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v>4.5618393E-2</v>
+        <v>1.3855258000000001E-2</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>4.5613542E-2</v>
-      </c>
-      <c r="M20" s="5">
-        <v>1.0285987999999999E-2</v>
-      </c>
-      <c r="N20" s="5">
-        <v>1.0284677000000001E-2</v>
-      </c>
-      <c r="O20" s="5">
-        <v>1.0279755999999999E-2</v>
-      </c>
-      <c r="P20" s="5">
-        <v>1.0293392E-2</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>1.0249882E-2</v>
-      </c>
-      <c r="R20" s="5">
-        <v>1.0297203E-2</v>
-      </c>
-      <c r="S20" s="5">
-        <v>1.0183467999999999E-2</v>
-      </c>
-      <c r="T20" s="5">
-        <v>1.0238315E-2</v>
+        <v>1.3912627E-2</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1.5390482E-2</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1.5396429999999999E-2</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1.5377711000000001E-2</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1.5394699E-2</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1.536245E-2</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1.5398093E-2</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1.5310285E-2</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1.5347315E-2</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1622,127 +1671,127 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="3"/>
-        <v>3.7037548000000003E-2</v>
+        <v>1.1421339000000001E-2</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="2"/>
-        <v>3.7772853000000002E-2</v>
+        <v>1.1611799000000001E-2</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="2"/>
-        <v>3.7604138000000002E-2</v>
+        <v>1.1520239E-2</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="2"/>
-        <v>3.7933670000000003E-2</v>
+        <v>1.1648794000000001E-2</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
-        <v>3.6930340999999998E-2</v>
+        <v>1.1346047E-2</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>3.7049789E-2</v>
+        <v>1.1378055E-2</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="2"/>
-        <v>3.7182234000000002E-2</v>
+        <v>1.1398449E-2</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>3.6972597000000003E-2</v>
-      </c>
-      <c r="M21" s="5">
-        <v>1.0495918E-2</v>
-      </c>
-      <c r="N21" s="5">
-        <v>1.0479209999999999E-2</v>
-      </c>
-      <c r="O21" s="5">
-        <v>1.0490681999999999E-2</v>
-      </c>
-      <c r="P21" s="5">
-        <v>1.0485810999999999E-2</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>1.0462079000000001E-2</v>
-      </c>
-      <c r="R21" s="5">
-        <v>1.0497101999999999E-2</v>
-      </c>
-      <c r="S21" s="5">
-        <v>1.0434504000000001E-2</v>
-      </c>
-      <c r="T21" s="5">
-        <v>1.0455389000000001E-2</v>
+        <v>1.1392868E-2</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1.5428266E-2</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1.5419347E-2</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1.5418766E-2</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1.5418616E-2</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1.539627E-2</v>
+      </c>
+      <c r="R21" s="3">
+        <v>1.5424863E-2</v>
+      </c>
+      <c r="S21" s="3">
+        <v>1.5377003E-2</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1.5394955E-2</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M22" s="5">
-        <v>1.0584085999999999E-2</v>
-      </c>
-      <c r="N22" s="5">
-        <v>1.05632E-2</v>
-      </c>
-      <c r="O22" s="5">
-        <v>1.0580806E-2</v>
-      </c>
-      <c r="P22" s="5">
-        <v>1.0572813E-2</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>1.0550011E-2</v>
-      </c>
-      <c r="R22" s="5">
-        <v>1.0581893E-2</v>
-      </c>
-      <c r="S22" s="5">
-        <v>1.0534942E-2</v>
-      </c>
-      <c r="T22" s="5">
-        <v>1.0556335999999999E-2</v>
+      <c r="M22" s="3">
+        <v>1.5449371E-2</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1.5436352E-2</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1.5444223E-2</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1.5436355000000001E-2</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>1.5419452E-2</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1.5445212999999999E-2</v>
+      </c>
+      <c r="S22" s="3">
+        <v>1.5412172999999999E-2</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1.5425555000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="M23" s="5">
-        <v>1.0614313E-2</v>
-      </c>
-      <c r="N23" s="5">
-        <v>1.0590861999999999E-2</v>
-      </c>
-      <c r="O23" s="5">
-        <v>1.0605112999999999E-2</v>
-      </c>
-      <c r="P23" s="5">
-        <v>1.059566E-2</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>1.0572536E-2</v>
-      </c>
-      <c r="R23" s="5">
-        <v>1.0601502E-2</v>
-      </c>
-      <c r="S23" s="5">
-        <v>1.05685E-2</v>
-      </c>
-      <c r="T23" s="5">
-        <v>1.0590196E-2</v>
+      <c r="A23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="M23" s="3">
+        <v>1.5466885E-2</v>
+      </c>
+      <c r="N23" s="3">
+        <v>1.5450837E-2</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1.5464853000000001E-2</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1.5453527999999999E-2</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1.543607E-2</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1.5463789E-2</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1.5432859E-2</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1.5450679E-2</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1768,29 +1817,29 @@
       <c r="I24">
         <v>8</v>
       </c>
-      <c r="M24" s="5">
-        <v>1.0625847000000001E-2</v>
-      </c>
-      <c r="N24" s="5">
-        <v>1.0599020000000001E-2</v>
-      </c>
-      <c r="O24" s="5">
-        <v>1.0627653000000001E-2</v>
-      </c>
-      <c r="P24" s="5">
-        <v>1.0614989999999999E-2</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>1.0592413E-2</v>
-      </c>
-      <c r="R24" s="5">
-        <v>1.0617784E-2</v>
-      </c>
-      <c r="S24" s="5">
-        <v>1.0589582E-2</v>
-      </c>
-      <c r="T24" s="5">
-        <v>1.061075E-2</v>
+      <c r="M24" s="3">
+        <v>1.5493457E-2</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1.5475907000000001E-2</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1.5485989E-2</v>
+      </c>
+      <c r="P24" s="3">
+        <v>1.5478252E-2</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1.5462424000000001E-2</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1.5485408000000001E-2</v>
+      </c>
+      <c r="S24" s="3">
+        <v>1.5460293E-2</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.5477258000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1798,60 +1847,60 @@
         <v>50</v>
       </c>
       <c r="B25" s="2">
-        <f>20*LOG(((B14/5)*B$6)/(B3*(B$17/5)), 10)</f>
-        <v>-4.2025540019744279</v>
+        <f>20*LOG(((B14)*B$6)/(B3*(B$17)), 10)</f>
+        <v>-4.3214696143988984</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" ref="C25:I25" si="4">20*LOG(((C14/5)*C$6)/(C3*(C$17/5)), 10)</f>
-        <v>-4.1763758291177808</v>
+        <f t="shared" ref="C25:I25" si="4">20*LOG(((C14)*C$6)/(C3*(C$17)), 10)</f>
+        <v>-4.2703732696348879</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.2602087607149066</v>
+        <v>-4.372577760992753</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.1180044634381483</v>
+        <v>-4.2436580321311199</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.2209318603192862</v>
+        <v>-4.3291072945240909</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.2017867448520487</v>
+        <v>-4.3221963623064061</v>
       </c>
       <c r="H25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.2844860465792642</v>
+        <v>-4.3585457422889924</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.246781737342471</v>
-      </c>
-      <c r="M25" s="5">
-        <v>2.9746196999999999E-2</v>
-      </c>
-      <c r="N25" s="5">
-        <v>2.9754082000000001E-2</v>
-      </c>
-      <c r="O25" s="5">
-        <v>2.9554103000000002E-2</v>
-      </c>
-      <c r="P25" s="5">
-        <v>2.9956720999999999E-2</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>2.9595379000000002E-2</v>
-      </c>
-      <c r="R25" s="5">
-        <v>2.9812162999999999E-2</v>
-      </c>
-      <c r="S25" s="5">
-        <v>2.9406972E-2</v>
-      </c>
-      <c r="T25" s="5">
-        <v>2.9516153E-2</v>
+        <v>-4.3627449953402806</v>
+      </c>
+      <c r="M25" s="3">
+        <v>9.1777060000000008E-3</v>
+      </c>
+      <c r="N25" s="3">
+        <v>9.171383E-3</v>
+      </c>
+      <c r="O25" s="3">
+        <v>9.0899499999999994E-3</v>
+      </c>
+      <c r="P25" s="3">
+        <v>9.233069E-3</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>9.1374620000000007E-3</v>
+      </c>
+      <c r="R25" s="3">
+        <v>9.1664499999999996E-3</v>
+      </c>
+      <c r="S25" s="3">
+        <v>9.0865879999999996E-3</v>
+      </c>
+      <c r="T25" s="3">
+        <v>9.1434689999999996E-3</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1859,60 +1908,60 @@
         <v>60</v>
       </c>
       <c r="B26" s="2">
-        <f t="shared" ref="B26:I32" si="5">20*LOG(((B15/5)*B$6)/(B4*(B$17/5)), 10)</f>
-        <v>-1.1202895677274234</v>
+        <f t="shared" ref="B26:I26" si="5">20*LOG(((B15)*B$6)/(B4*(B$17)), 10)</f>
+        <v>-1.1435286932881064</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1143512713047257</v>
+        <v>-1.1413977584423898</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1514217550835213</v>
+        <v>-1.1780755254095265</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.0800226133448465</v>
+        <v>-1.124764881614712</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1157351016947812</v>
+        <v>-1.1460640117069705</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1412911029320096</v>
+        <v>-1.1661508654714874</v>
       </c>
       <c r="H26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.0706559839883809</v>
+        <v>-1.0885802325635594</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1171474932874206</v>
-      </c>
-      <c r="M26" s="5">
-        <v>4.0996376000000001E-2</v>
-      </c>
-      <c r="N26" s="5">
-        <v>4.0933046000000001E-2</v>
-      </c>
-      <c r="O26" s="5">
-        <v>4.0783867000000001E-2</v>
-      </c>
-      <c r="P26" s="5">
-        <v>4.1091435000000003E-2</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>4.0832184000000001E-2</v>
-      </c>
-      <c r="R26" s="5">
-        <v>4.1040249000000001E-2</v>
-      </c>
-      <c r="S26" s="5">
-        <v>4.0866199999999998E-2</v>
-      </c>
-      <c r="T26" s="5">
-        <v>4.0790203999999997E-2</v>
+        <v>-1.156235494201634</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1.3138046E-2</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1.3071134E-2</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1.3018643999999999E-2</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1.3143881E-2</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1.3078963000000001E-2</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1.3086079E-2</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1.3111291000000001E-2</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1.3109829999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -1920,60 +1969,60 @@
         <v>70</v>
       </c>
       <c r="B27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.25711251968013432</v>
+        <f t="shared" ref="B27:I27" si="6">20*LOG(((B16)*B$6)/(B5*(B$17)), 10)</f>
+        <v>-0.25892413988106289</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.26505867594116089</v>
+        <f t="shared" si="6"/>
+        <v>-0.26537479758349675</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.2729850661789911</v>
+        <f t="shared" si="6"/>
+        <v>-0.27689679918788113</v>
       </c>
       <c r="E27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.24032759032475609</v>
+        <f t="shared" si="6"/>
+        <v>-0.25747499080257219</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.2477533565370601</v>
+        <f t="shared" si="6"/>
+        <v>-0.25480243170557026</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.27506587749332667</v>
+        <f t="shared" si="6"/>
+        <v>-0.27911823675154684</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.18546476424785072</v>
+        <f t="shared" si="6"/>
+        <v>-0.18909793132738123</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.24593625811116462</v>
-      </c>
-      <c r="M27" s="5">
-        <v>4.5094627999999998E-2</v>
-      </c>
-      <c r="N27" s="5">
-        <v>4.4950824E-2</v>
-      </c>
-      <c r="O27" s="5">
-        <v>4.4891371999999999E-2</v>
-      </c>
-      <c r="P27" s="5">
-        <v>4.5112885999999998E-2</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>4.4922706E-2</v>
-      </c>
-      <c r="R27" s="5">
-        <v>4.5079052000000001E-2</v>
-      </c>
-      <c r="S27" s="5">
-        <v>4.5038178999999998E-2</v>
-      </c>
-      <c r="T27" s="5">
-        <v>4.4899902999999998E-2</v>
+        <f t="shared" si="6"/>
+        <v>-0.25233012468488153</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1.454047E-2</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1.4450714E-2</v>
+      </c>
+      <c r="O27" s="3">
+        <v>1.4421216000000001E-2</v>
+      </c>
+      <c r="P27" s="3">
+        <v>1.4511537E-2</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1.4477686E-2</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1.4489207E-2</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1.4532478E-2</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1.4524854E-2</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -1981,60 +2030,60 @@
         <v>100</v>
       </c>
       <c r="B28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B28:I28" si="7">20*LOG(((B17)*B$6)/(B6*(B$17)), 10)</f>
         <v>0</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M28" s="5">
-        <v>4.7583759000000003E-2</v>
-      </c>
-      <c r="N28" s="5">
-        <v>4.7418310999999998E-2</v>
-      </c>
-      <c r="O28" s="5">
-        <v>4.7459293E-2</v>
-      </c>
-      <c r="P28" s="5">
-        <v>4.7510732E-2</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>4.7379698999999997E-2</v>
-      </c>
-      <c r="R28" s="5">
-        <v>4.7577750000000002E-2</v>
-      </c>
-      <c r="S28" s="5">
-        <v>4.7424830000000001E-2</v>
-      </c>
-      <c r="T28" s="5">
-        <v>4.7401220000000001E-2</v>
+      <c r="M28" s="3">
+        <v>1.5011606E-2</v>
+      </c>
+      <c r="N28" s="3">
+        <v>1.4909253000000001E-2</v>
+      </c>
+      <c r="O28" s="3">
+        <v>1.4900296E-2</v>
+      </c>
+      <c r="P28" s="3">
+        <v>1.4952145999999999E-2</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1.4922763E-2</v>
+      </c>
+      <c r="R28" s="3">
+        <v>1.4968993E-2</v>
+      </c>
+      <c r="S28" s="3">
+        <v>1.4927147999999999E-2</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1.4981971E-2</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -2042,60 +2091,60 @@
         <v>140</v>
       </c>
       <c r="B29" s="2">
-        <f t="shared" si="5"/>
-        <v>-9.4680790192493577E-2</v>
+        <f t="shared" ref="B29:I29" si="8">20*LOG(((B18)*B$6)/(B7*(B$17)), 10)</f>
+        <v>-7.2584743588500464E-2</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="5"/>
-        <v>-6.9285793523278461E-2</v>
+        <f t="shared" si="8"/>
+        <v>-3.8554431463447197E-2</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="5"/>
-        <v>-8.4983434919450845E-2</v>
+        <f t="shared" si="8"/>
+        <v>-6.1405507627318862E-2</v>
       </c>
       <c r="E29" s="2">
-        <f t="shared" si="5"/>
-        <v>-7.1228004450633681E-2</v>
+        <f t="shared" si="8"/>
+        <v>-5.0429945501508866E-2</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="5"/>
-        <v>-9.7844611055397018E-2</v>
+        <f t="shared" si="8"/>
+        <v>-7.3668206303857134E-2</v>
       </c>
       <c r="G29" s="2">
-        <f t="shared" si="5"/>
-        <v>-8.5078848239986002E-2</v>
+        <f t="shared" si="8"/>
+        <v>-5.902971444548117E-2</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.14460889974642635</v>
+        <f t="shared" si="8"/>
+        <v>-0.11863672256063537</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.11661013561123831</v>
-      </c>
-      <c r="M29" s="5">
-        <v>4.8276599000000003E-2</v>
-      </c>
-      <c r="N29" s="5">
-        <v>4.8211731000000001E-2</v>
-      </c>
-      <c r="O29" s="5">
-        <v>4.8183723999999997E-2</v>
-      </c>
-      <c r="P29" s="5">
-        <v>4.8214551000000001E-2</v>
-      </c>
-      <c r="Q29" s="5">
-        <v>4.8033926999999997E-2</v>
-      </c>
-      <c r="R29" s="5">
-        <v>4.8261302999999998E-2</v>
-      </c>
-      <c r="S29" s="5">
-        <v>4.7958731999999997E-2</v>
-      </c>
-      <c r="T29" s="5">
-        <v>4.8058986999999997E-2</v>
+        <f t="shared" si="8"/>
+        <v>-9.5783337271758764E-2</v>
+      </c>
+      <c r="M29" s="3">
+        <v>1.4851836E-2</v>
+      </c>
+      <c r="N29" s="3">
+        <v>1.4793120999999999E-2</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1.4760192E-2</v>
+      </c>
+      <c r="P29" s="3">
+        <v>1.4817568E-2</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1.4763116E-2</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.4817163E-2</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1.4719731E-2</v>
+      </c>
+      <c r="T29" s="3">
+        <v>1.4800363E-2</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2103,60 +2152,60 @@
         <v>180</v>
       </c>
       <c r="B30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.23109919524005954</v>
+        <f t="shared" ref="B30:I30" si="9">20*LOG(((B19)*B$6)/(B8*(B$17)), 10)</f>
+        <v>-0.15827985207385914</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.17611078016323506</v>
+        <f t="shared" si="9"/>
+        <v>-8.8416412850498713E-2</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.21614863936346745</v>
+        <f t="shared" si="9"/>
+        <v>-0.13292462110536857</v>
       </c>
       <c r="E30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.18333009586596449</v>
+        <f t="shared" si="9"/>
+        <v>-0.11129267295693045</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.24157317380362847</v>
+        <f t="shared" si="9"/>
+        <v>-0.16671152638702819</v>
       </c>
       <c r="G30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.23082870916706352</v>
+        <f t="shared" si="9"/>
+        <v>-0.15140243965818517</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.31162802172725079</v>
+        <f t="shared" si="9"/>
+        <v>-0.2259570744142321</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.27267304757943261</v>
-      </c>
-      <c r="M30" s="5">
-        <v>4.8189270999999999E-2</v>
-      </c>
-      <c r="N30" s="5">
-        <v>4.8318962999999999E-2</v>
-      </c>
-      <c r="O30" s="5">
-        <v>4.8207859999999998E-2</v>
-      </c>
-      <c r="P30" s="5">
-        <v>4.8289783000000003E-2</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>4.7948356999999997E-2</v>
-      </c>
-      <c r="R30" s="5">
-        <v>4.8168800999999997E-2</v>
-      </c>
-      <c r="S30" s="5">
-        <v>4.7867324000000003E-2</v>
-      </c>
-      <c r="T30" s="5">
-        <v>4.7957743999999997E-2</v>
+        <f t="shared" si="9"/>
+        <v>-0.19567664202728607</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1.4627967E-2</v>
+      </c>
+      <c r="N30" s="3">
+        <v>1.4622161E-2</v>
+      </c>
+      <c r="O30" s="3">
+        <v>1.4561447999999999E-2</v>
+      </c>
+      <c r="P30" s="3">
+        <v>1.4641372E-2</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>1.4519815E-2</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.4588353E-2</v>
+      </c>
+      <c r="S30" s="3">
+        <v>1.448259E-2</v>
+      </c>
+      <c r="T30" s="3">
+        <v>1.4555444000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -2164,60 +2213,60 @@
         <v>210</v>
       </c>
       <c r="B31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.66286109965933926</v>
+        <f t="shared" ref="B31:I31" si="10">20*LOG(((B20)*B$6)/(B9*(B$17)), 10)</f>
+        <v>-0.53293893621245836</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.5610017418440636</v>
+        <f t="shared" si="10"/>
+        <v>-0.41632692605474098</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.61172190009817462</v>
+        <f t="shared" si="10"/>
+        <v>-0.47647457603601273</v>
       </c>
       <c r="E31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.5525632898782632</v>
+        <f t="shared" si="10"/>
+        <v>-0.43653114674231724</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.67316595555565306</v>
+        <f t="shared" si="10"/>
+        <v>-0.53570249620754318</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.65966866251975298</v>
+        <f t="shared" si="10"/>
+        <v>-0.52749515548907044</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.72577748016683374</v>
+        <f t="shared" si="10"/>
+        <v>-0.58374102086030355</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.69503897859132935</v>
-      </c>
-      <c r="M31" s="5">
-        <v>4.6276849000000002E-2</v>
-      </c>
-      <c r="N31" s="5">
-        <v>4.6639359999999998E-2</v>
-      </c>
-      <c r="O31" s="5">
-        <v>4.6467979E-2</v>
-      </c>
-      <c r="P31" s="5">
-        <v>4.6619814000000002E-2</v>
-      </c>
-      <c r="Q31" s="5">
-        <v>4.6057787000000003E-2</v>
-      </c>
-      <c r="R31" s="5">
-        <v>4.6232268E-2</v>
-      </c>
-      <c r="S31" s="5">
-        <v>4.6032666999999999E-2</v>
-      </c>
-      <c r="T31" s="5">
-        <v>4.6071521999999997E-2</v>
+        <f t="shared" si="10"/>
+        <v>-0.56857894385884045</v>
+      </c>
+      <c r="M31" s="3">
+        <v>1.3947795000000001E-2</v>
+      </c>
+      <c r="N31" s="3">
+        <v>1.4004518000000001E-2</v>
+      </c>
+      <c r="O31" s="3">
+        <v>1.3934732999999999E-2</v>
+      </c>
+      <c r="P31" s="3">
+        <v>1.4033811E-2</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1.38382E-2</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1.3909871000000001E-2</v>
+      </c>
+      <c r="S31" s="3">
+        <v>1.3834123E-2</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1.387715E-2</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -2225,65 +2274,117 @@
         <v>250</v>
       </c>
       <c r="B32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.5242473331410418</v>
+        <f t="shared" ref="B32:I32" si="11">20*LOG(((B21)*B$6)/(B10*(B$17)), 10)</f>
+        <v>-2.3028718204946403</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.3130518617768807</v>
+        <f t="shared" si="11"/>
+        <v>-2.0819524795615081</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.3766055609320293</v>
+        <f t="shared" si="11"/>
+        <v>-2.1571635423992195</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.2826585743394308</v>
+        <f t="shared" si="11"/>
+        <v>-2.0801955607375753</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.5199374659004259</v>
+        <f t="shared" si="11"/>
+        <v>-2.2970795466652123</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.5102073802655629</v>
+        <f t="shared" si="11"/>
+        <v>-2.3012723264040917</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.5150158837645038</v>
+        <f t="shared" si="11"/>
+        <v>-2.2943412795830391</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="5"/>
-        <v>-2.5343827465081645</v>
-      </c>
-      <c r="M32" s="5">
-        <v>3.773278E-2</v>
-      </c>
-      <c r="N32" s="5">
-        <v>3.8503263000000003E-2</v>
-      </c>
-      <c r="O32" s="5">
-        <v>3.8305044000000003E-2</v>
-      </c>
-      <c r="P32" s="5">
-        <v>3.8606066000000001E-2</v>
-      </c>
-      <c r="Q32" s="5">
-        <v>3.7645034000000001E-2</v>
-      </c>
-      <c r="R32" s="5">
-        <v>3.7717618000000001E-2</v>
-      </c>
-      <c r="S32" s="5">
-        <v>3.7844087999999998E-2</v>
-      </c>
-      <c r="T32" s="5">
-        <v>3.7688381999999999E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>-2.3176280327801888</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1.1283257999999999E-2</v>
+      </c>
+      <c r="N32" s="3">
+        <v>1.1460112E-2</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1.1402773E-2</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1.1532779999999999E-2</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1.1205911000000001E-2</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1.1256657999999999E-2</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1.1291907E-2</v>
+      </c>
+      <c r="T32" s="3">
+        <v>1.1257814E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M33" s="3">
+        <v>1.5380922E-2</v>
+      </c>
+      <c r="N33" s="3">
+        <v>1.5383163E-2</v>
+      </c>
+      <c r="O33" s="3">
+        <v>1.539715E-2</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1.5370943999999999E-2</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>1.5370253E-2</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1.5403902000000001E-2</v>
+      </c>
+      <c r="S33" s="3">
+        <v>1.5296475E-2</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1.5350206999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M34" s="3">
+        <v>1.5313413E-2</v>
+      </c>
+      <c r="N34" s="3">
+        <v>1.5338276E-2</v>
+      </c>
+      <c r="O34" s="3">
+        <v>1.5325737000000001E-2</v>
+      </c>
+      <c r="P34" s="3">
+        <v>1.5325640999999999E-2</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1.5296034E-2</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.5345457999999999E-2</v>
+      </c>
+      <c r="S34" s="3">
+        <v>1.5182747999999999E-2</v>
+      </c>
+      <c r="T34" s="3">
+        <v>1.5267711999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2293,10 +2394,34 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M35" s="3">
+        <v>1.5326503E-2</v>
+      </c>
+      <c r="N35" s="3">
+        <v>1.5348766E-2</v>
+      </c>
+      <c r="O35" s="3">
+        <v>1.5326907000000001E-2</v>
+      </c>
+      <c r="P35" s="3">
+        <v>1.5345444999999999E-2</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>1.5301830000000001E-2</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1.5350822E-2</v>
+      </c>
+      <c r="S35" s="3">
+        <v>1.5191023999999999E-2</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1.5273738E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -2322,304 +2447,546 @@
       <c r="I36">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M36" s="3">
+        <v>1.5392706000000001E-2</v>
+      </c>
+      <c r="N36" s="3">
+        <v>1.5397447999999999E-2</v>
+      </c>
+      <c r="O36" s="3">
+        <v>1.5381127E-2</v>
+      </c>
+      <c r="P36" s="3">
+        <v>1.539577E-2</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1.5362136E-2</v>
+      </c>
+      <c r="R36" s="3">
+        <v>1.5398012000000001E-2</v>
+      </c>
+      <c r="S36" s="3">
+        <v>1.5310169E-2</v>
+      </c>
+      <c r="T36" s="3">
+        <v>1.5349612E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>50</v>
       </c>
       <c r="B37" s="1">
-        <f t="shared" ref="B37:I44" si="6">M17</f>
-        <v>1.0490151E-2</v>
+        <f t="shared" ref="B37:I44" si="12">M17</f>
+        <v>1.5375669999999999E-2</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0480651000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5377666E-2</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0506338E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5388990999999999E-2</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0485833E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5366177999999999E-2</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0479697E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5365943999999999E-2</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0509965E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5399579E-2</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0383121E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5290356999999999E-2</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0453898999999999E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.534628E-2</v>
+      </c>
+      <c r="M37" s="3">
+        <v>1.5429739E-2</v>
+      </c>
+      <c r="N37" s="3">
+        <v>1.5421574E-2</v>
+      </c>
+      <c r="O37" s="3">
+        <v>1.5421126E-2</v>
+      </c>
+      <c r="P37" s="3">
+        <v>1.5419791E-2</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>1.5398075000000001E-2</v>
+      </c>
+      <c r="R37" s="3">
+        <v>1.5423998E-2</v>
+      </c>
+      <c r="S37" s="3">
+        <v>1.5375206000000001E-2</v>
+      </c>
+      <c r="T37" s="3">
+        <v>1.5397058E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>60</v>
       </c>
       <c r="B38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0123907999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5309168E-2</v>
       </c>
       <c r="C38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0124431999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5330808E-2</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0119766000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5316252000000001E-2</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0137551999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.532235E-2</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.009993E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5290758999999999E-2</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0151504E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5338831000000001E-2</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="6"/>
-        <v>9.9624929999999993E-3</v>
+        <f t="shared" si="12"/>
+        <v>1.517571E-2</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0060243E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5264967000000001E-2</v>
+      </c>
+      <c r="M38" s="3">
+        <v>1.5449902E-2</v>
+      </c>
+      <c r="N38" s="3">
+        <v>1.5437565E-2</v>
+      </c>
+      <c r="O38" s="3">
+        <v>1.5448257E-2</v>
+      </c>
+      <c r="P38" s="3">
+        <v>1.5439754999999999E-2</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1.5422119E-2</v>
+      </c>
+      <c r="R38" s="3">
+        <v>1.5447664E-2</v>
+      </c>
+      <c r="S38" s="3">
+        <v>1.5410841E-2</v>
+      </c>
+      <c r="T38" s="3">
+        <v>1.5427445E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>70</v>
       </c>
       <c r="B39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0066887E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5318884E-2</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0076791999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5343228E-2</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0065421E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5319531000000001E-2</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0089071E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5340347000000001E-2</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0036257E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5297453000000001E-2</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0085612000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5346501E-2</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="6"/>
-        <v>9.9118729999999999E-3</v>
+        <f t="shared" si="12"/>
+        <v>1.5188333E-2</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0002407E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5267694E-2</v>
+      </c>
+      <c r="M39" s="3">
+        <v>1.5468647E-2</v>
+      </c>
+      <c r="N39" s="3">
+        <v>1.5454557000000001E-2</v>
+      </c>
+      <c r="O39" s="3">
+        <v>1.5464772E-2</v>
+      </c>
+      <c r="P39" s="3">
+        <v>1.5451281000000001E-2</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>1.5439167E-2</v>
+      </c>
+      <c r="R39" s="3">
+        <v>1.5462383999999999E-2</v>
+      </c>
+      <c r="S39" s="3">
+        <v>1.5435552999999999E-2</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1.5447021999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>100</v>
       </c>
       <c r="B40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0285987999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5390482E-2</v>
       </c>
       <c r="C40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0284677000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5396429999999999E-2</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0279755999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5377711000000001E-2</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0293392E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5394699E-2</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0249882E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.536245E-2</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0297203E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5398093E-2</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0183467999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5310285E-2</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0238315E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5347315E-2</v>
+      </c>
+      <c r="M40" s="3">
+        <v>1.5492574E-2</v>
+      </c>
+      <c r="N40" s="3">
+        <v>1.5474836E-2</v>
+      </c>
+      <c r="O40" s="3">
+        <v>1.5491540999999999E-2</v>
+      </c>
+      <c r="P40" s="3">
+        <v>1.5473674999999999E-2</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1.5459815999999999E-2</v>
+      </c>
+      <c r="R40" s="3">
+        <v>1.5482315E-2</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1.545941E-2</v>
+      </c>
+      <c r="T40" s="3">
+        <v>1.547053E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>140</v>
       </c>
       <c r="B41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0495918E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5428266E-2</v>
       </c>
       <c r="C41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0479209999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5419347E-2</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0490681999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5418766E-2</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0485810999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5418616E-2</v>
       </c>
       <c r="F41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0462079000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.539627E-2</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0497101999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5424863E-2</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0434504000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5377003E-2</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0455389000000001E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5394955E-2</v>
+      </c>
+      <c r="M41" s="3">
+        <v>4.5960542E-2</v>
+      </c>
+      <c r="N41" s="3">
+        <v>4.5977580999999997E-2</v>
+      </c>
+      <c r="O41" s="3">
+        <v>4.5643758E-2</v>
+      </c>
+      <c r="P41" s="3">
+        <v>4.6246134000000001E-2</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>4.5710128000000003E-2</v>
+      </c>
+      <c r="R41" s="3">
+        <v>4.5984231E-2</v>
+      </c>
+      <c r="S41" s="3">
+        <v>4.5665773999999999E-2</v>
+      </c>
+      <c r="T41" s="3">
+        <v>4.5674807999999997E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>180</v>
       </c>
       <c r="B42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0584085999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5449371E-2</v>
       </c>
       <c r="C42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.05632E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5436352E-2</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0580806E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5444223E-2</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0572813E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5436355000000001E-2</v>
       </c>
       <c r="F42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0550011E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5419452E-2</v>
       </c>
       <c r="G42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0581893E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5445212999999999E-2</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0534942E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5412172999999999E-2</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0556335999999999E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5425555000000001E-2</v>
+      </c>
+      <c r="M42" s="3">
+        <v>6.5592742999999995E-2</v>
+      </c>
+      <c r="N42" s="3">
+        <v>6.5440811000000002E-2</v>
+      </c>
+      <c r="O42" s="3">
+        <v>6.5263182000000003E-2</v>
+      </c>
+      <c r="P42" s="3">
+        <v>6.5762229000000005E-2</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>6.5361470000000005E-2</v>
+      </c>
+      <c r="R42" s="3">
+        <v>6.5536610999999995E-2</v>
+      </c>
+      <c r="S42" s="3">
+        <v>6.5749921000000003E-2</v>
+      </c>
+      <c r="T42" s="3">
+        <v>6.5409816999999995E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>210</v>
       </c>
       <c r="B43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0614313E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5466885E-2</v>
       </c>
       <c r="C43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0590861999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5450837E-2</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0605112999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5464853000000001E-2</v>
       </c>
       <c r="E43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.059566E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5453527999999999E-2</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0572536E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.543607E-2</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0601502E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5463789E-2</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.05685E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5432859E-2</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0590196E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5450679E-2</v>
+      </c>
+      <c r="M43" s="3">
+        <v>7.2610959000000003E-2</v>
+      </c>
+      <c r="N43" s="3">
+        <v>7.2274594999999997E-2</v>
+      </c>
+      <c r="O43" s="3">
+        <v>7.2271787000000004E-2</v>
+      </c>
+      <c r="P43" s="3">
+        <v>7.2546862000000004E-2</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>7.2342478000000002E-2</v>
+      </c>
+      <c r="R43" s="3">
+        <v>7.2500274000000003E-2</v>
+      </c>
+      <c r="S43" s="3">
+        <v>7.2896904999999998E-2</v>
+      </c>
+      <c r="T43" s="3">
+        <v>7.2430580999999994E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>250</v>
       </c>
       <c r="B44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0625847000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5493457E-2</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0599020000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5475907000000001E-2</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0627653000000001E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5485989E-2</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0614989999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5478252E-2</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0592413E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5462424000000001E-2</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0617784E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5485408000000001E-2</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.0589582E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.5460293E-2</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="6"/>
-        <v>1.061075E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>1.5477258000000001E-2</v>
+      </c>
+      <c r="M44" s="3">
+        <v>7.4945994000000002E-2</v>
+      </c>
+      <c r="N44" s="3">
+        <v>7.4669205000000002E-2</v>
+      </c>
+      <c r="O44" s="3">
+        <v>7.4766494000000003E-2</v>
+      </c>
+      <c r="P44" s="3">
+        <v>7.4819839999999999E-2</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>7.4683114999999994E-2</v>
+      </c>
+      <c r="R44" s="3">
+        <v>7.4932343999999998E-2</v>
+      </c>
+      <c r="S44" s="3">
+        <v>7.4944884000000003E-2</v>
+      </c>
+      <c r="T44" s="3">
+        <v>7.4783987999999996E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M45" s="3">
+        <v>7.4408165999999998E-2</v>
+      </c>
+      <c r="N45" s="3">
+        <v>7.4323311000000003E-2</v>
+      </c>
+      <c r="O45" s="3">
+        <v>7.4282467000000005E-2</v>
+      </c>
+      <c r="P45" s="3">
+        <v>7.4351132E-2</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>7.4117905999999997E-2</v>
+      </c>
+      <c r="R45" s="3">
+        <v>7.4391946E-2</v>
+      </c>
+      <c r="S45" s="3">
+        <v>7.4059725000000007E-2</v>
+      </c>
+      <c r="T45" s="3">
+        <v>7.4131608000000002E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
@@ -2631,10 +2998,34 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M46" s="3">
+        <v>7.3590039999999995E-2</v>
+      </c>
+      <c r="N46" s="3">
+        <v>7.3822409000000005E-2</v>
+      </c>
+      <c r="O46" s="3">
+        <v>7.3630102000000003E-2</v>
+      </c>
+      <c r="P46" s="3">
+        <v>7.3788062000000001E-2</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>7.3336445E-2</v>
+      </c>
+      <c r="R46" s="3">
+        <v>7.3570370999999996E-2</v>
+      </c>
+      <c r="S46" s="3">
+        <v>7.3163575999999994E-2</v>
+      </c>
+      <c r="T46" s="3">
+        <v>7.3288045999999996E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2660,42 +3051,90 @@
       <c r="I47">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M47" s="3">
+        <v>7.0452951E-2</v>
+      </c>
+      <c r="N47" s="3">
+        <v>7.1054018999999996E-2</v>
+      </c>
+      <c r="O47" s="3">
+        <v>7.0731550000000004E-2</v>
+      </c>
+      <c r="P47" s="3">
+        <v>7.1036756000000006E-2</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>7.0240363E-2</v>
+      </c>
+      <c r="R47" s="3">
+        <v>7.0420838999999999E-2</v>
+      </c>
+      <c r="S47" s="3">
+        <v>7.0151231999999994E-2</v>
+      </c>
+      <c r="T47" s="3">
+        <v>7.0192254999999995E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>50</v>
       </c>
       <c r="B48" s="1">
-        <f t="shared" ref="B48:I55" si="7">M25</f>
-        <v>2.9746196999999999E-2</v>
+        <f t="shared" ref="B48:I55" si="13">M25</f>
+        <v>9.1777060000000008E-3</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9754082000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.171383E-3</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9554103000000002E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.0899499999999994E-3</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9956720999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.233069E-3</v>
       </c>
       <c r="F48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9595379000000002E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.1374620000000007E-3</v>
       </c>
       <c r="G48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9812162999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.1664499999999996E-3</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9406972E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.0865879999999996E-3</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="7"/>
-        <v>2.9516153E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.1434689999999996E-3</v>
+      </c>
+      <c r="M48" s="3">
+        <v>5.7374074999999997E-2</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5.8583143999999997E-2</v>
+      </c>
+      <c r="O48" s="3">
+        <v>5.8242376999999998E-2</v>
+      </c>
+      <c r="P48" s="3">
+        <v>5.8739059000000003E-2</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>5.7329547000000002E-2</v>
+      </c>
+      <c r="R48" s="3">
+        <v>5.7384297000000001E-2</v>
+      </c>
+      <c r="S48" s="3">
+        <v>5.7602301000000002E-2</v>
+      </c>
+      <c r="T48" s="3">
+        <v>5.7346570999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2703,36 +3142,36 @@
         <v>60</v>
       </c>
       <c r="B49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0996376000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3138046E-2</v>
       </c>
       <c r="C49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0933046000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3071134E-2</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0783867000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3018643999999999E-2</v>
       </c>
       <c r="E49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.1091435000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3143881E-2</v>
       </c>
       <c r="F49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0832184000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3078963000000001E-2</v>
       </c>
       <c r="G49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.1040249000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3086079E-2</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0866199999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3111291000000001E-2</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="7"/>
-        <v>4.0790203999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3109829999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2740,36 +3179,36 @@
         <v>70</v>
       </c>
       <c r="B50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.5094627999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.454047E-2</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.4950824E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4450714E-2</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.4891371999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4421216000000001E-2</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.5112885999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4511537E-2</v>
       </c>
       <c r="F50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.4922706E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4477686E-2</v>
       </c>
       <c r="G50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.5079052000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4489207E-2</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.5038178999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4532478E-2</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="7"/>
-        <v>4.4899902999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4524854E-2</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2777,36 +3216,36 @@
         <v>100</v>
       </c>
       <c r="B51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7583759000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.5011606E-2</v>
       </c>
       <c r="C51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7418310999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4909253000000001E-2</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7459293E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4900296E-2</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7510732E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4952145999999999E-2</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7379698999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4922763E-2</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7577750000000002E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4968993E-2</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7424830000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4927147999999999E-2</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7401220000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4981971E-2</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2814,36 +3253,36 @@
         <v>140</v>
       </c>
       <c r="B52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8276599000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4851836E-2</v>
       </c>
       <c r="C52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8211731000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4793120999999999E-2</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8183723999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4760192E-2</v>
       </c>
       <c r="E52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8214551000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4817568E-2</v>
       </c>
       <c r="F52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8033926999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4763116E-2</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8261302999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4817163E-2</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7958731999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4719731E-2</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8058986999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4800363E-2</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2851,36 +3290,36 @@
         <v>180</v>
       </c>
       <c r="B53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8189270999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4627967E-2</v>
       </c>
       <c r="C53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8318962999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4622161E-2</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8207859999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4561447999999999E-2</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8289783000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4641372E-2</v>
       </c>
       <c r="F53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7948356999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4519815E-2</v>
       </c>
       <c r="G53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.8168800999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4588353E-2</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7867324000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.448259E-2</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="7"/>
-        <v>4.7957743999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4555444000000001E-2</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2888,36 +3327,36 @@
         <v>210</v>
       </c>
       <c r="B54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6276849000000002E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3947795000000001E-2</v>
       </c>
       <c r="C54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6639359999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4004518000000001E-2</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6467979E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3934732999999999E-2</v>
       </c>
       <c r="E54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6619814000000002E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4033811E-2</v>
       </c>
       <c r="F54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6057787000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.38382E-2</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6232268E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3909871000000001E-2</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6032666999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3834123E-2</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="7"/>
-        <v>4.6071521999999997E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.387715E-2</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2925,54 +3364,54 @@
         <v>250</v>
       </c>
       <c r="B55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.773278E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1283257999999999E-2</v>
       </c>
       <c r="C55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.8503263000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1460112E-2</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.8305044000000003E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1402773E-2</v>
       </c>
       <c r="E55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.8606066000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1532779999999999E-2</v>
       </c>
       <c r="F55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.7645034000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1205911000000001E-2</v>
       </c>
       <c r="G55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.7717618000000001E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1256657999999999E-2</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.7844087999999998E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1291907E-2</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="7"/>
-        <v>3.7688381999999999E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.1257814E-2</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -3004,36 +3443,36 @@
         <v>50</v>
       </c>
       <c r="B59" s="2">
-        <f>20*LOG(((B48/5)*B$40)/(B37*(B$51/5)), 10)</f>
-        <v>-4.2512604757775998</v>
+        <f>20*LOG(((B48)*B$40)/(B37*(B$51)), 10)</f>
+        <v>-4.2654968799696338</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" ref="C59:I59" si="8">20*LOG(((C48/5)*C$40)/(C37*(C$51/5)), 10)</f>
-        <v>-4.2119425558997037</v>
+        <f t="shared" ref="C59:I59" si="14">20*LOG(((C48)*C$40)/(C37*(C$51)), 10)</f>
+        <v>-4.2098289290829154</v>
       </c>
       <c r="D59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.303440874323444</v>
+        <f t="shared" si="14"/>
+        <v>-4.2990370493015977</v>
       </c>
       <c r="E59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.1668374312319019</v>
+        <f t="shared" si="14"/>
+        <v>-4.1710421143814145</v>
       </c>
       <c r="F59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.2799650356324319</v>
+        <f t="shared" si="14"/>
+        <v>-4.2624484300838459</v>
       </c>
       <c r="G59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.2378481613927343</v>
+        <f t="shared" si="14"/>
+        <v>-4.2606664242852208</v>
       </c>
       <c r="H59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.319753736495028</v>
+        <f t="shared" si="14"/>
+        <v>-4.300207043987271</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="8"/>
-        <v>-4.2955915856446421</v>
+        <f t="shared" si="14"/>
+        <v>-4.2885733226482001</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -3041,36 +3480,36 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <f>20*LOG(((B49/5)*B$40)/(B38*(B$51/5)), 10)</f>
-        <v>-1.1563091239938286</v>
+        <f t="shared" ref="B60:I60" si="15">20*LOG(((B49)*B$40)/(B38*(B$51)), 10)</f>
+        <v>-1.1119149352399647</v>
       </c>
       <c r="C60" s="2">
-        <f t="shared" ref="B60:I66" si="9">20*LOG(((C49/5)*C$40)/(C38*(C$51/5)), 10)</f>
-        <v>-1.1410405638778733</v>
+        <f t="shared" si="15"/>
+        <v>-1.105752609042755</v>
       </c>
       <c r="D60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1804105284525974</v>
+        <f t="shared" si="15"/>
+        <v>-1.1377990636925017</v>
       </c>
       <c r="E60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1282999275693146</v>
+        <f t="shared" si="15"/>
+        <v>-1.0786817421153898</v>
       </c>
       <c r="F60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1637837146774619</v>
+        <f t="shared" si="15"/>
+        <v>-1.1048898295484253</v>
       </c>
       <c r="G60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1601005685389358</v>
+        <f t="shared" si="15"/>
+        <v>-1.1341674341296986</v>
       </c>
       <c r="H60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1022770578239145</v>
+        <f t="shared" si="15"/>
+        <v>-1.0499425195161873</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.152272520017745</v>
+        <f t="shared" si="15"/>
+        <v>-1.1127070958342009</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -3078,36 +3517,36 @@
         <v>70</v>
       </c>
       <c r="B61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.27966238012919686</v>
+        <f t="shared" ref="B61:I61" si="16">20*LOG(((B50)*B$40)/(B39*(B$51)), 10)</f>
+        <v>-0.23647237571139026</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.28680121624987681</v>
+        <f t="shared" si="16"/>
+        <v>-0.24126571118478349</v>
       </c>
       <c r="D61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.30015047276556456</v>
+        <f t="shared" si="16"/>
+        <v>-0.25093578433764785</v>
       </c>
       <c r="E61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.27567553490286822</v>
+        <f t="shared" si="16"/>
+        <v>-0.22908194301156495</v>
       </c>
       <c r="F61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.27958593233965273</v>
+        <f t="shared" si="16"/>
+        <v>-0.22617467266786442</v>
       </c>
       <c r="G61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.28824215183900626</v>
+        <f t="shared" si="16"/>
+        <v>-0.25380803980157118</v>
       </c>
       <c r="H61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.21369971867084728</v>
+        <f t="shared" si="16"/>
+        <v>-0.16327999679422434</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.26840303284533251</v>
+        <f t="shared" si="16"/>
+        <v>-0.22396433028092649</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -3115,35 +3554,35 @@
         <v>100</v>
       </c>
       <c r="B62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B62:I62" si="17">20*LOG(((B51)*B$40)/(B40*(B$51)), 10)</f>
         <v>0</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -3152,36 +3591,36 @@
         <v>140</v>
       </c>
       <c r="B63" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.9929915796243292E-2</v>
+        <f t="shared" ref="B63:I63" si="18">20*LOG(((B52)*B$40)/(B41*(B$51)), 10)</f>
+        <v>-0.11423817956787033</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.862485481217329E-2</v>
+        <f t="shared" si="18"/>
+        <v>-8.0840502263680572E-2</v>
       </c>
       <c r="D63" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.4836360073065434E-2</v>
+        <f t="shared" si="18"/>
+        <v>-0.10521623704753053</v>
       </c>
       <c r="E63" s="2">
-        <f t="shared" si="9"/>
-        <v>-3.3142166270806461E-2</v>
+        <f t="shared" si="18"/>
+        <v>-9.2015813337581354E-2</v>
       </c>
       <c r="F63" s="2">
-        <f t="shared" si="9"/>
-        <v>-5.886666113072276E-2</v>
+        <f t="shared" si="18"/>
+        <v>-0.11252491312416757</v>
       </c>
       <c r="G63" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.3099989531053803E-2</v>
+        <f t="shared" si="18"/>
+        <v>-0.10363807857629201</v>
       </c>
       <c r="H63" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.11428395074971918</v>
+        <f t="shared" si="18"/>
+        <v>-0.1593077862742352</v>
       </c>
       <c r="I63" s="2">
-        <f t="shared" si="9"/>
-        <v>-6.2532312032946416E-2</v>
+        <f t="shared" si="18"/>
+        <v>-0.13285203310628235</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -3189,36 +3628,36 @@
         <v>180</v>
       </c>
       <c r="B64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.13831475068627341</v>
+        <f t="shared" ref="B64:I64" si="19">20*LOG(((B53)*B$40)/(B42*(B$51)), 10)</f>
+        <v>-0.25803532867222251</v>
       </c>
       <c r="C64" s="2">
-        <f t="shared" si="9"/>
-        <v>-6.8666429434634621E-2</v>
+        <f t="shared" si="19"/>
+        <v>-0.19137929152437383</v>
       </c>
       <c r="D64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.11478712814124864</v>
+        <f t="shared" si="19"/>
+        <v>-0.23729402614241527</v>
       </c>
       <c r="E64" s="2">
-        <f t="shared" si="9"/>
-        <v>-9.1370132493666933E-2</v>
+        <f t="shared" si="19"/>
+        <v>-0.20590619632505355</v>
       </c>
       <c r="F64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.14705227823998435</v>
+        <f t="shared" si="19"/>
+        <v>-0.26993231353223779</v>
       </c>
       <c r="G64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.12964310126400039</v>
+        <f t="shared" si="19"/>
+        <v>-0.25026570636793816</v>
       </c>
       <c r="H64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.21406159136937486</v>
+        <f t="shared" si="19"/>
+        <v>-0.32022405779744989</v>
       </c>
       <c r="I64" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.16430984508211882</v>
+        <f t="shared" si="19"/>
+        <v>-0.29503771900938008</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -3226,36 +3665,36 @@
         <v>210</v>
       </c>
       <c r="B65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.5148168802359594</v>
+        <f t="shared" ref="B65:I65" si="20">20*LOG(((B54)*B$40)/(B43*(B$51)), 10)</f>
+        <v>-0.68144473517418902</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.39868301615561424</v>
+        <f t="shared" si="20"/>
+        <v>-0.57439395007896776</v>
       </c>
       <c r="D65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.45399947691547737</v>
+        <f t="shared" si="20"/>
+        <v>-0.63100691296028044</v>
       </c>
       <c r="E65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.41581373885821088</v>
+        <f t="shared" si="20"/>
+        <v>-0.58368694257675002</v>
       </c>
       <c r="F65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.51499074569666836</v>
+        <f t="shared" si="20"/>
+        <v>-0.69691791130587344</v>
       </c>
       <c r="G65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.5021365207235069</v>
+        <f t="shared" si="20"/>
+        <v>-0.67436919646040028</v>
       </c>
       <c r="H65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.58114588203316442</v>
+        <f t="shared" si="20"/>
+        <v>-0.72976638587884768</v>
       </c>
       <c r="I65" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.54064941225164287</v>
+        <f t="shared" si="20"/>
+        <v>-0.72367664473947479</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3263,40 +3702,1057 @@
         <v>250</v>
       </c>
       <c r="B66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.2971497750240975</v>
+        <f t="shared" ref="B66:I66" si="21">20*LOG(((B55)*B$40)/(B44*(B$51)), 10)</f>
+        <v>-2.5377749675011021</v>
       </c>
       <c r="C66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.0704719947769181</v>
+        <f t="shared" si="21"/>
+        <v>-2.3300620378644945</v>
       </c>
       <c r="D66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.1503971659897818</v>
+        <f t="shared" si="21"/>
+        <v>-2.3846333776682389</v>
       </c>
       <c r="E66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.0699450008812925</v>
+        <f t="shared" si="21"/>
+        <v>-2.3024046549445085</v>
       </c>
       <c r="F66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.2832128718802882</v>
+        <f t="shared" si="21"/>
+        <v>-2.5443833683513462</v>
       </c>
       <c r="G66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.2834850769386446</v>
+        <f t="shared" si="21"/>
+        <v>-2.5247765560818278</v>
       </c>
       <c r="H66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.2998170741948947</v>
+        <f t="shared" si="21"/>
+        <v>-2.508879826380837</v>
       </c>
       <c r="I66" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.3019924279176678</v>
+        <f t="shared" si="21"/>
+        <v>-2.5555299646883531</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <v>7</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>50</v>
+      </c>
+      <c r="B70" s="1">
+        <f>M33</f>
+        <v>1.5380922E-2</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" ref="C70:I70" si="22">N33</f>
+        <v>1.5383163E-2</v>
+      </c>
+      <c r="D70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.539715E-2</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5370943999999999E-2</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5370253E-2</v>
+      </c>
+      <c r="G70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5403902000000001E-2</v>
+      </c>
+      <c r="H70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5296475E-2</v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5350206999999999E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>60</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" ref="B71:B77" si="23">M34</f>
+        <v>1.5313413E-2</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" ref="C71:C77" si="24">N34</f>
+        <v>1.5338276E-2</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" ref="D71:D77" si="25">O34</f>
+        <v>1.5325737000000001E-2</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" ref="E71:E77" si="26">P34</f>
+        <v>1.5325640999999999E-2</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" ref="F71:F77" si="27">Q34</f>
+        <v>1.5296034E-2</v>
+      </c>
+      <c r="G71" s="1">
+        <f t="shared" ref="G71:G77" si="28">R34</f>
+        <v>1.5345457999999999E-2</v>
+      </c>
+      <c r="H71" s="1">
+        <f t="shared" ref="H71:H77" si="29">S34</f>
+        <v>1.5182747999999999E-2</v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" ref="I71:I77" si="30">T34</f>
+        <v>1.5267711999999999E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5326503E-2</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5348766E-2</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5326907000000001E-2</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" si="26"/>
+        <v>1.5345444999999999E-2</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5301830000000001E-2</v>
+      </c>
+      <c r="G72" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5350822E-2</v>
+      </c>
+      <c r="H72" s="1">
+        <f t="shared" si="29"/>
+        <v>1.5191023999999999E-2</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="30"/>
+        <v>1.5273738E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>100</v>
+      </c>
+      <c r="B73" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5392706000000001E-2</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5397447999999999E-2</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5381127E-2</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="26"/>
+        <v>1.539577E-2</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5362136E-2</v>
+      </c>
+      <c r="G73" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5398012000000001E-2</v>
+      </c>
+      <c r="H73" s="1">
+        <f t="shared" si="29"/>
+        <v>1.5310169E-2</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="30"/>
+        <v>1.5349612E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>140</v>
+      </c>
+      <c r="B74" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5429739E-2</v>
+      </c>
+      <c r="C74" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5421574E-2</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5421126E-2</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="26"/>
+        <v>1.5419791E-2</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5398075000000001E-2</v>
+      </c>
+      <c r="G74" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5423998E-2</v>
+      </c>
+      <c r="H74" s="1">
+        <f t="shared" si="29"/>
+        <v>1.5375206000000001E-2</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="30"/>
+        <v>1.5397058E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>180</v>
+      </c>
+      <c r="B75" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5449902E-2</v>
+      </c>
+      <c r="C75" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5437565E-2</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5448257E-2</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="26"/>
+        <v>1.5439754999999999E-2</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5422119E-2</v>
+      </c>
+      <c r="G75" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5447664E-2</v>
+      </c>
+      <c r="H75" s="1">
+        <f t="shared" si="29"/>
+        <v>1.5410841E-2</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="30"/>
+        <v>1.5427445E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>210</v>
+      </c>
+      <c r="B76" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5468647E-2</v>
+      </c>
+      <c r="C76" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5454557000000001E-2</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5464772E-2</v>
+      </c>
+      <c r="E76" s="1">
+        <f t="shared" si="26"/>
+        <v>1.5451281000000001E-2</v>
+      </c>
+      <c r="F76" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5439167E-2</v>
+      </c>
+      <c r="G76" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5462383999999999E-2</v>
+      </c>
+      <c r="H76" s="1">
+        <f t="shared" si="29"/>
+        <v>1.5435552999999999E-2</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="30"/>
+        <v>1.5447021999999999E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>250</v>
+      </c>
+      <c r="B77" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5492574E-2</v>
+      </c>
+      <c r="C77" s="1">
+        <f t="shared" si="24"/>
+        <v>1.5474836E-2</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" si="25"/>
+        <v>1.5491540999999999E-2</v>
+      </c>
+      <c r="E77" s="1">
+        <f t="shared" si="26"/>
+        <v>1.5473674999999999E-2</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" si="27"/>
+        <v>1.5459815999999999E-2</v>
+      </c>
+      <c r="G77" s="1">
+        <f t="shared" si="28"/>
+        <v>1.5482315E-2</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="29"/>
+        <v>1.545941E-2</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="30"/>
+        <v>1.547053E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>7</v>
+      </c>
+      <c r="I80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>50</v>
+      </c>
+      <c r="B81" s="1">
+        <f>M41</f>
+        <v>4.5960542E-2</v>
+      </c>
+      <c r="C81" s="1">
+        <f t="shared" ref="C81:I81" si="31">N41</f>
+        <v>4.5977580999999997E-2</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5643758E-2</v>
+      </c>
+      <c r="E81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.6246134000000001E-2</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5710128000000003E-2</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5984231E-2</v>
+      </c>
+      <c r="H81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5665773999999999E-2</v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5674807999999997E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>60</v>
+      </c>
+      <c r="B82" s="1">
+        <f t="shared" ref="B82:B88" si="32">M42</f>
+        <v>6.5592742999999995E-2</v>
+      </c>
+      <c r="C82" s="1">
+        <f t="shared" ref="C82:C88" si="33">N42</f>
+        <v>6.5440811000000002E-2</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" ref="D82:D88" si="34">O42</f>
+        <v>6.5263182000000003E-2</v>
+      </c>
+      <c r="E82" s="1">
+        <f t="shared" ref="E82:E88" si="35">P42</f>
+        <v>6.5762229000000005E-2</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" ref="F82:F88" si="36">Q42</f>
+        <v>6.5361470000000005E-2</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" ref="G82:G88" si="37">R42</f>
+        <v>6.5536610999999995E-2</v>
+      </c>
+      <c r="H82" s="1">
+        <f t="shared" ref="H82:H88" si="38">S42</f>
+        <v>6.5749921000000003E-2</v>
+      </c>
+      <c r="I82" s="1">
+        <f t="shared" ref="I82:I88" si="39">T42</f>
+        <v>6.5409816999999995E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>70</v>
+      </c>
+      <c r="B83" s="1">
+        <f t="shared" si="32"/>
+        <v>7.2610959000000003E-2</v>
+      </c>
+      <c r="C83" s="1">
+        <f t="shared" si="33"/>
+        <v>7.2274594999999997E-2</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="34"/>
+        <v>7.2271787000000004E-2</v>
+      </c>
+      <c r="E83" s="1">
+        <f t="shared" si="35"/>
+        <v>7.2546862000000004E-2</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="36"/>
+        <v>7.2342478000000002E-2</v>
+      </c>
+      <c r="G83" s="1">
+        <f t="shared" si="37"/>
+        <v>7.2500274000000003E-2</v>
+      </c>
+      <c r="H83" s="1">
+        <f t="shared" si="38"/>
+        <v>7.2896904999999998E-2</v>
+      </c>
+      <c r="I83" s="1">
+        <f t="shared" si="39"/>
+        <v>7.2430580999999994E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>100</v>
+      </c>
+      <c r="B84" s="1">
+        <f t="shared" si="32"/>
+        <v>7.4945994000000002E-2</v>
+      </c>
+      <c r="C84" s="1">
+        <f t="shared" si="33"/>
+        <v>7.4669205000000002E-2</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="34"/>
+        <v>7.4766494000000003E-2</v>
+      </c>
+      <c r="E84" s="1">
+        <f t="shared" si="35"/>
+        <v>7.4819839999999999E-2</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="36"/>
+        <v>7.4683114999999994E-2</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="37"/>
+        <v>7.4932343999999998E-2</v>
+      </c>
+      <c r="H84" s="1">
+        <f t="shared" si="38"/>
+        <v>7.4944884000000003E-2</v>
+      </c>
+      <c r="I84" s="1">
+        <f t="shared" si="39"/>
+        <v>7.4783987999999996E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>140</v>
+      </c>
+      <c r="B85" s="1">
+        <f t="shared" si="32"/>
+        <v>7.4408165999999998E-2</v>
+      </c>
+      <c r="C85" s="1">
+        <f t="shared" si="33"/>
+        <v>7.4323311000000003E-2</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="34"/>
+        <v>7.4282467000000005E-2</v>
+      </c>
+      <c r="E85" s="1">
+        <f t="shared" si="35"/>
+        <v>7.4351132E-2</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="36"/>
+        <v>7.4117905999999997E-2</v>
+      </c>
+      <c r="G85" s="1">
+        <f t="shared" si="37"/>
+        <v>7.4391946E-2</v>
+      </c>
+      <c r="H85" s="1">
+        <f t="shared" si="38"/>
+        <v>7.4059725000000007E-2</v>
+      </c>
+      <c r="I85" s="1">
+        <f t="shared" si="39"/>
+        <v>7.4131608000000002E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>180</v>
+      </c>
+      <c r="B86" s="1">
+        <f t="shared" si="32"/>
+        <v>7.3590039999999995E-2</v>
+      </c>
+      <c r="C86" s="1">
+        <f t="shared" si="33"/>
+        <v>7.3822409000000005E-2</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="34"/>
+        <v>7.3630102000000003E-2</v>
+      </c>
+      <c r="E86" s="1">
+        <f t="shared" si="35"/>
+        <v>7.3788062000000001E-2</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="36"/>
+        <v>7.3336445E-2</v>
+      </c>
+      <c r="G86" s="1">
+        <f t="shared" si="37"/>
+        <v>7.3570370999999996E-2</v>
+      </c>
+      <c r="H86" s="1">
+        <f t="shared" si="38"/>
+        <v>7.3163575999999994E-2</v>
+      </c>
+      <c r="I86" s="1">
+        <f t="shared" si="39"/>
+        <v>7.3288045999999996E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>210</v>
+      </c>
+      <c r="B87" s="1">
+        <f t="shared" si="32"/>
+        <v>7.0452951E-2</v>
+      </c>
+      <c r="C87" s="1">
+        <f t="shared" si="33"/>
+        <v>7.1054018999999996E-2</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="34"/>
+        <v>7.0731550000000004E-2</v>
+      </c>
+      <c r="E87" s="1">
+        <f t="shared" si="35"/>
+        <v>7.1036756000000006E-2</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="36"/>
+        <v>7.0240363E-2</v>
+      </c>
+      <c r="G87" s="1">
+        <f t="shared" si="37"/>
+        <v>7.0420838999999999E-2</v>
+      </c>
+      <c r="H87" s="1">
+        <f t="shared" si="38"/>
+        <v>7.0151231999999994E-2</v>
+      </c>
+      <c r="I87" s="1">
+        <f t="shared" si="39"/>
+        <v>7.0192254999999995E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>250</v>
+      </c>
+      <c r="B88" s="1">
+        <f t="shared" si="32"/>
+        <v>5.7374074999999997E-2</v>
+      </c>
+      <c r="C88" s="1">
+        <f t="shared" si="33"/>
+        <v>5.8583143999999997E-2</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="34"/>
+        <v>5.8242376999999998E-2</v>
+      </c>
+      <c r="E88" s="1">
+        <f t="shared" si="35"/>
+        <v>5.8739059000000003E-2</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="36"/>
+        <v>5.7329547000000002E-2</v>
+      </c>
+      <c r="G88" s="1">
+        <f t="shared" si="37"/>
+        <v>5.7384297000000001E-2</v>
+      </c>
+      <c r="H88" s="1">
+        <f t="shared" si="38"/>
+        <v>5.7602301000000002E-2</v>
+      </c>
+      <c r="I88" s="1">
+        <f t="shared" si="39"/>
+        <v>5.7346570999999999E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91">
+        <v>5</v>
+      </c>
+      <c r="G91">
+        <v>6</v>
+      </c>
+      <c r="H91">
+        <v>7</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>50</v>
+      </c>
+      <c r="B92" s="2">
+        <f>20*LOG(((B81/5)*B$73)/(B70*(B$84/5)), 10)</f>
+        <v>-4.2406135545266102</v>
+      </c>
+      <c r="C92" s="2">
+        <f t="shared" ref="C92:I92" si="40">20*LOG(((C81/5)*C$73)/(C70*(C$84/5)), 10)</f>
+        <v>-4.203846100845575</v>
+      </c>
+      <c r="D92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.2955560884875501</v>
+      </c>
+      <c r="E92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.1648093552128431</v>
+      </c>
+      <c r="F92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.2687879418630414</v>
+      </c>
+      <c r="G92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.2445296662841745</v>
+      </c>
+      <c r="H92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.2952509065758768</v>
+      </c>
+      <c r="I92" s="2">
+        <f t="shared" si="40"/>
+        <v>-4.2829744984920364</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>60</v>
+      </c>
+      <c r="B93" s="2">
+        <f t="shared" ref="B93:I93" si="41">20*LOG(((B82/5)*B$73)/(B71*(B$84/5)), 10)</f>
+        <v>-1.1129930431311517</v>
+      </c>
+      <c r="C93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.1124131358917917</v>
+      </c>
+      <c r="D93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.149439633805756</v>
+      </c>
+      <c r="E93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.0811496724674079</v>
+      </c>
+      <c r="F93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.1205569508592288</v>
+      </c>
+      <c r="G93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.1340107956512817</v>
+      </c>
+      <c r="H93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.0643431100340415</v>
+      </c>
+      <c r="I93" s="2">
+        <f t="shared" si="41"/>
+        <v>-1.1168448795796759</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>70</v>
+      </c>
+      <c r="B94" s="2">
+        <f t="shared" ref="B94:I94" si="42">20*LOG(((B83/5)*B$73)/(B72*(B$84/5)), 10)</f>
+        <v>-0.23748702781467856</v>
+      </c>
+      <c r="C94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.25561159468528444</v>
+      </c>
+      <c r="D94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.26409173525171648</v>
+      </c>
+      <c r="E94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.2395243157863387</v>
+      </c>
+      <c r="F94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.24241620327778021</v>
+      </c>
+      <c r="G94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.25993304877200535</v>
+      </c>
+      <c r="H94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.17279934371787392</v>
+      </c>
+      <c r="I94" s="2">
+        <f t="shared" si="42"/>
+        <v>-0.23469173329795087</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>100</v>
+      </c>
+      <c r="B95" s="2">
+        <f t="shared" ref="B95:I95" si="43">20*LOG(((B84/5)*B$73)/(B73*(B$84/5)), 10)</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="E95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="2">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>140</v>
+      </c>
+      <c r="B96" s="2">
+        <f t="shared" ref="B96:I96" si="44">20*LOG(((B85/5)*B$73)/(B74*(B$84/5)), 10)</f>
+        <v>-8.3428582766037498E-2</v>
+      </c>
+      <c r="C96" s="2">
+        <f t="shared" si="44"/>
+        <v>-5.3928697875541075E-2</v>
+      </c>
+      <c r="D96" s="2">
+        <f t="shared" si="44"/>
+        <v>-7.8972495004594717E-2</v>
+      </c>
+      <c r="E96" s="2">
+        <f t="shared" si="44"/>
+        <v>-6.8125258451934026E-2</v>
+      </c>
+      <c r="F96" s="2">
+        <f t="shared" si="44"/>
+        <v>-8.6282158749385274E-2</v>
+      </c>
+      <c r="G96" s="2">
+        <f t="shared" si="44"/>
+        <v>-7.7514105132569441E-2</v>
+      </c>
+      <c r="H96" s="2">
+        <f t="shared" si="44"/>
+        <v>-0.1400171050082773</v>
+      </c>
+      <c r="I96" s="2">
+        <f t="shared" si="44"/>
+        <v>-0.10291088256986433</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>180</v>
+      </c>
+      <c r="B97" s="2">
+        <f t="shared" ref="B97:I97" si="45">20*LOG(((B86/5)*B$73)/(B75*(B$84/5)), 10)</f>
+        <v>-0.19080279080498433</v>
+      </c>
+      <c r="C97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.12166734848817468</v>
+      </c>
+      <c r="D97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.17085883074012542</v>
+      </c>
+      <c r="E97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.14539322546073682</v>
+      </c>
+      <c r="F97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.19190029197578945</v>
+      </c>
+      <c r="G97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.18729065917088672</v>
+      </c>
+      <c r="H97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.26586845041545021</v>
+      </c>
+      <c r="I97" s="2">
+        <f t="shared" si="45"/>
+        <v>-0.21944166060391979</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>210</v>
+      </c>
+      <c r="B98" s="2">
+        <f t="shared" ref="B98:I98" si="46">20*LOG(((B87/5)*B$73)/(B76*(B$84/5)), 10)</f>
+        <v>-0.57973179216900805</v>
+      </c>
+      <c r="C98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.4632138848958034</v>
+      </c>
+      <c r="D98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.52898408131093322</v>
+      </c>
+      <c r="E98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.48193461824585232</v>
+      </c>
+      <c r="F98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.57615871666031537</v>
+      </c>
+      <c r="G98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.57559848038608596</v>
+      </c>
+      <c r="H98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.64497795695904914</v>
+      </c>
+      <c r="I98" s="2">
+        <f t="shared" si="46"/>
+        <v>-0.60533578464958049</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>250</v>
+      </c>
+      <c r="B99" s="2">
+        <f t="shared" ref="B99:I99" si="47">20*LOG(((B88/5)*B$73)/(B77*(B$84/5)), 10)</f>
+        <v>-2.3768266391809099</v>
+      </c>
+      <c r="C99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.15092322206679</v>
+      </c>
+      <c r="D99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.2314877477775079</v>
+      </c>
+      <c r="E99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.1456369354496103</v>
+      </c>
+      <c r="F99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.3519325780196474</v>
+      </c>
+      <c r="G99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.3649499632631681</v>
+      </c>
+      <c r="H99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.3703018027305038</v>
+      </c>
+      <c r="I99" s="2">
+        <f t="shared" si="47"/>
+        <v>-2.3741791320699881</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A90:I90"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A12:I12"/>
@@ -3304,43 +4760,57 @@
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A46:I46"/>
   </mergeCells>
-  <conditionalFormatting sqref="B25:I25 B32:I32">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="B25:I32">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="lessThan">
       <formula>-5.5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25:I32">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:I26 B31:I31">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
       <formula>-2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:I30">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59:I59 B66:I66">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="B59:I66">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
       <formula>-5.5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59:I66">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:I60 B65:I65">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="lessThan">
       <formula>-2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:I64">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92:I99">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>-5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93:I93 B98:I98">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>-2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B94:I97">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/АЧХ_result.xlsx
+++ b/АЧХ_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A84B767-40C5-4C51-BA3A-94F82940D0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E81F01E-53AB-48B9-9215-351B9BB93222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="2010" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="3945" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +91,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -137,6 +145,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -557,28 +566,28 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="M1" s="3">
-        <v>1.5376035E-2</v>
+        <v>1.5463451E-2</v>
       </c>
       <c r="N1" s="3">
-        <v>1.537591E-2</v>
+        <v>1.5190327E-2</v>
       </c>
       <c r="O1" s="3">
-        <v>1.5391224E-2</v>
+        <v>1.5175681999999999E-2</v>
       </c>
       <c r="P1" s="3">
-        <v>1.5368181999999999E-2</v>
+        <v>1.5258344E-2</v>
       </c>
       <c r="Q1" s="3">
-        <v>1.5366306E-2</v>
+        <v>1.5222704E-2</v>
       </c>
       <c r="R1" s="3">
-        <v>1.5395584E-2</v>
+        <v>1.5261749E-2</v>
       </c>
       <c r="S1" s="3">
-        <v>1.528886E-2</v>
+        <v>1.5157653E-2</v>
       </c>
       <c r="T1" s="3">
-        <v>1.5344295000000001E-2</v>
+        <v>1.5212643E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -610,28 +619,28 @@
         <v>8</v>
       </c>
       <c r="M2" s="3">
-        <v>1.5305892999999999E-2</v>
+        <v>1.539593E-2</v>
       </c>
       <c r="N2" s="3">
-        <v>1.5330559000000001E-2</v>
+        <v>1.5074811E-2</v>
       </c>
       <c r="O2" s="3">
-        <v>1.5318595000000001E-2</v>
+        <v>1.5097622999999999E-2</v>
       </c>
       <c r="P2" s="3">
-        <v>1.5323323E-2</v>
+        <v>1.5198011000000001E-2</v>
       </c>
       <c r="Q2" s="3">
-        <v>1.5290596E-2</v>
+        <v>1.5099638E-2</v>
       </c>
       <c r="R2" s="3">
-        <v>1.5335092999999999E-2</v>
+        <v>1.5205282000000001E-2</v>
       </c>
       <c r="S2" s="3">
-        <v>1.5176845E-2</v>
+        <v>1.5051475E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>1.5262398E-2</v>
+        <v>1.5099606E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -640,59 +649,59 @@
       </c>
       <c r="B3" s="1">
         <f>M1</f>
-        <v>1.5376035E-2</v>
+        <v>1.5463451E-2</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:I10" si="0">N1</f>
-        <v>1.537591E-2</v>
+        <v>1.5190327E-2</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5391224E-2</v>
+        <v>1.5175681999999999E-2</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5368181999999999E-2</v>
+        <v>1.5258344E-2</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5366306E-2</v>
+        <v>1.5222704E-2</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5395584E-2</v>
+        <v>1.5261749E-2</v>
       </c>
       <c r="H3" s="1">
         <f t="shared" si="0"/>
-        <v>1.528886E-2</v>
+        <v>1.5157653E-2</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5344295000000001E-2</v>
+        <v>1.5212643E-2</v>
       </c>
       <c r="M3" s="3">
-        <v>1.5320057999999999E-2</v>
+        <v>1.5393377E-2</v>
       </c>
       <c r="N3" s="3">
-        <v>1.5341385000000001E-2</v>
+        <v>1.5104261000000001E-2</v>
       </c>
       <c r="O3" s="3">
-        <v>1.5318424000000001E-2</v>
+        <v>1.5129914E-2</v>
       </c>
       <c r="P3" s="3">
-        <v>1.5333683000000001E-2</v>
+        <v>1.5230858E-2</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.5292973E-2</v>
+        <v>1.5121265E-2</v>
       </c>
       <c r="R3" s="3">
-        <v>1.5344165E-2</v>
+        <v>1.5229763E-2</v>
       </c>
       <c r="S3" s="3">
-        <v>1.5187617E-2</v>
+        <v>1.5097911E-2</v>
       </c>
       <c r="T3" s="3">
-        <v>1.5265819999999999E-2</v>
+        <v>1.5132652999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -701,59 +710,59 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B10" si="1">M2</f>
-        <v>1.5305892999999999E-2</v>
+        <v>1.539593E-2</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5330559000000001E-2</v>
+        <v>1.5074811E-2</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5318595000000001E-2</v>
+        <v>1.5097622999999999E-2</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5323323E-2</v>
+        <v>1.5198011000000001E-2</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5290596E-2</v>
+        <v>1.5099638E-2</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5335092999999999E-2</v>
+        <v>1.5205282000000001E-2</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5176845E-2</v>
+        <v>1.5051475E-2</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5262398E-2</v>
+        <v>1.5099606E-2</v>
       </c>
       <c r="M4" s="3">
-        <v>1.5387424E-2</v>
+        <v>1.543451E-2</v>
       </c>
       <c r="N4" s="3">
-        <v>1.5394990000000001E-2</v>
+        <v>1.5267509E-2</v>
       </c>
       <c r="O4" s="3">
-        <v>1.5376333000000001E-2</v>
+        <v>1.5277885E-2</v>
       </c>
       <c r="P4" s="3">
-        <v>1.5391624E-2</v>
+        <v>1.5348919000000001E-2</v>
       </c>
       <c r="Q4" s="3">
-        <v>1.5357696000000001E-2</v>
+        <v>1.5270183999999999E-2</v>
       </c>
       <c r="R4" s="3">
-        <v>1.5393785E-2</v>
+        <v>1.5333728E-2</v>
       </c>
       <c r="S4" s="3">
-        <v>1.5307537E-2</v>
+        <v>1.5276692999999999E-2</v>
       </c>
       <c r="T4" s="3">
-        <v>1.5342791999999999E-2</v>
+        <v>1.5297659E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -762,59 +771,59 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="1"/>
-        <v>1.5320057999999999E-2</v>
+        <v>1.5393377E-2</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5341385000000001E-2</v>
+        <v>1.5104261000000001E-2</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5318424000000001E-2</v>
+        <v>1.5129914E-2</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5333683000000001E-2</v>
+        <v>1.5230858E-2</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5292973E-2</v>
+        <v>1.5121265E-2</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5344165E-2</v>
+        <v>1.5229763E-2</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5187617E-2</v>
+        <v>1.5097911E-2</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5265819999999999E-2</v>
+        <v>1.5132652999999999E-2</v>
       </c>
       <c r="M5" s="3">
-        <v>1.5424235E-2</v>
+        <v>1.5445716999999999E-2</v>
       </c>
       <c r="N5" s="3">
-        <v>1.5416251000000001E-2</v>
+        <v>1.5353E-2</v>
       </c>
       <c r="O5" s="3">
-        <v>1.5419547E-2</v>
+        <v>1.5349242000000001E-2</v>
       </c>
       <c r="P5" s="3">
-        <v>1.5417858E-2</v>
+        <v>1.5394351000000001E-2</v>
       </c>
       <c r="Q5" s="3">
-        <v>1.5395139E-2</v>
+        <v>1.5349619E-2</v>
       </c>
       <c r="R5" s="3">
-        <v>1.5422699E-2</v>
+        <v>1.5384365000000001E-2</v>
       </c>
       <c r="S5" s="3">
-        <v>1.5376453999999999E-2</v>
+        <v>1.5362894E-2</v>
       </c>
       <c r="T5" s="3">
-        <v>1.5395277000000001E-2</v>
+        <v>1.5374937999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -823,59 +832,59 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="1"/>
-        <v>1.5387424E-2</v>
+        <v>1.543451E-2</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5394990000000001E-2</v>
+        <v>1.5267509E-2</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5376333000000001E-2</v>
+        <v>1.5277885E-2</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5391624E-2</v>
+        <v>1.5348919000000001E-2</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5357696000000001E-2</v>
+        <v>1.5270183999999999E-2</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5393785E-2</v>
+        <v>1.5333728E-2</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5307537E-2</v>
+        <v>1.5276692999999999E-2</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5342791999999999E-2</v>
+        <v>1.5297659E-2</v>
       </c>
       <c r="M6" s="3">
-        <v>1.5450648000000001E-2</v>
+        <v>1.5453516E-2</v>
       </c>
       <c r="N6" s="3">
-        <v>1.5437126000000001E-2</v>
+        <v>1.5384033E-2</v>
       </c>
       <c r="O6" s="3">
-        <v>1.5445314999999999E-2</v>
+        <v>1.5383015999999999E-2</v>
       </c>
       <c r="P6" s="3">
-        <v>1.5436627E-2</v>
+        <v>1.5414821E-2</v>
       </c>
       <c r="Q6" s="3">
-        <v>1.5418896E-2</v>
+        <v>1.5384274999999999E-2</v>
       </c>
       <c r="R6" s="3">
-        <v>1.5444869E-2</v>
+        <v>1.5409056000000001E-2</v>
       </c>
       <c r="S6" s="3">
-        <v>1.5412613E-2</v>
+        <v>1.5402664E-2</v>
       </c>
       <c r="T6" s="3">
-        <v>1.542731E-2</v>
+        <v>1.5412227000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -884,59 +893,59 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="1"/>
-        <v>1.5424235E-2</v>
+        <v>1.5445716999999999E-2</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5416251000000001E-2</v>
+        <v>1.5353E-2</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5419547E-2</v>
+        <v>1.5349242000000001E-2</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5417858E-2</v>
+        <v>1.5394351000000001E-2</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5395139E-2</v>
+        <v>1.5349619E-2</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5422699E-2</v>
+        <v>1.5384365000000001E-2</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5376453999999999E-2</v>
+        <v>1.5362894E-2</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5395277000000001E-2</v>
+        <v>1.5374937999999999E-2</v>
       </c>
       <c r="M7" s="3">
-        <v>1.5467297E-2</v>
+        <v>1.5458253E-2</v>
       </c>
       <c r="N7" s="3">
-        <v>1.5453483E-2</v>
+        <v>1.5402229E-2</v>
       </c>
       <c r="O7" s="3">
-        <v>1.5465311000000001E-2</v>
+        <v>1.5401457E-2</v>
       </c>
       <c r="P7" s="3">
-        <v>1.5453695999999999E-2</v>
+        <v>1.5421743999999999E-2</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.5434441E-2</v>
+        <v>1.5399829E-2</v>
       </c>
       <c r="R7" s="3">
-        <v>1.546058E-2</v>
+        <v>1.5420698E-2</v>
       </c>
       <c r="S7" s="3">
-        <v>1.5431287E-2</v>
+        <v>1.5415862000000001E-2</v>
       </c>
       <c r="T7" s="3">
-        <v>1.544688E-2</v>
+        <v>1.542376E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -945,59 +954,59 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="1"/>
-        <v>1.5450648000000001E-2</v>
+        <v>1.5453516E-2</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5437126000000001E-2</v>
+        <v>1.5384033E-2</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5445314999999999E-2</v>
+        <v>1.5383015999999999E-2</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5436627E-2</v>
+        <v>1.5414821E-2</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5418896E-2</v>
+        <v>1.5384274999999999E-2</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5444869E-2</v>
+        <v>1.5409056000000001E-2</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5412613E-2</v>
+        <v>1.5402664E-2</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="0"/>
-        <v>1.542731E-2</v>
+        <v>1.5412227000000001E-2</v>
       </c>
       <c r="M8" s="3">
-        <v>1.5490632000000001E-2</v>
+        <v>1.5469834999999999E-2</v>
       </c>
       <c r="N8" s="3">
-        <v>1.5474174E-2</v>
+        <v>1.5423177999999999E-2</v>
       </c>
       <c r="O8" s="3">
-        <v>1.5484538000000001E-2</v>
+        <v>1.5425324000000001E-2</v>
       </c>
       <c r="P8" s="3">
-        <v>1.5475826999999999E-2</v>
+        <v>1.5443406E-2</v>
       </c>
       <c r="Q8" s="3">
-        <v>1.5462731E-2</v>
+        <v>1.5424228999999999E-2</v>
       </c>
       <c r="R8" s="3">
-        <v>1.5482434999999999E-2</v>
+        <v>1.544208E-2</v>
       </c>
       <c r="S8" s="3">
-        <v>1.5458355999999999E-2</v>
+        <v>1.5441109999999999E-2</v>
       </c>
       <c r="T8" s="3">
-        <v>1.5470955999999999E-2</v>
+        <v>1.5449595999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -1006,59 +1015,59 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="1"/>
-        <v>1.5467297E-2</v>
+        <v>1.5458253E-2</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5453483E-2</v>
+        <v>1.5402229E-2</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5465311000000001E-2</v>
+        <v>1.5401457E-2</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5453695999999999E-2</v>
+        <v>1.5421743999999999E-2</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5434441E-2</v>
+        <v>1.5399829E-2</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>1.546058E-2</v>
+        <v>1.5420698E-2</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5431287E-2</v>
+        <v>1.5415862000000001E-2</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="0"/>
-        <v>1.544688E-2</v>
+        <v>1.542376E-2</v>
       </c>
       <c r="M9" s="3">
-        <v>8.985916E-3</v>
+        <v>9.5857879999999996E-3</v>
       </c>
       <c r="N9" s="3">
-        <v>8.9683349999999992E-3</v>
+        <v>9.5079710000000005E-3</v>
       </c>
       <c r="O9" s="3">
-        <v>8.8729020000000002E-3</v>
+        <v>9.4704880000000009E-3</v>
       </c>
       <c r="P9" s="3">
-        <v>9.0172989999999995E-3</v>
+        <v>9.6113629999999995E-3</v>
       </c>
       <c r="Q9" s="3">
-        <v>8.9233200000000002E-3</v>
+        <v>9.4009109999999996E-3</v>
       </c>
       <c r="R9" s="3">
-        <v>8.9655870000000006E-3</v>
+        <v>9.5508899999999994E-3</v>
       </c>
       <c r="S9" s="3">
-        <v>8.8888860000000004E-3</v>
+        <v>9.5773260000000006E-3</v>
       </c>
       <c r="T9" s="3">
-        <v>8.9290859999999993E-3</v>
+        <v>9.4803200000000004E-3</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1067,85 +1076,85 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="1"/>
-        <v>1.5490632000000001E-2</v>
+        <v>1.5469834999999999E-2</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5474174E-2</v>
+        <v>1.5423177999999999E-2</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5484538000000001E-2</v>
+        <v>1.5425324000000001E-2</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5475826999999999E-2</v>
+        <v>1.5443406E-2</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5462731E-2</v>
+        <v>1.5424228999999999E-2</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5482434999999999E-2</v>
+        <v>1.544208E-2</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5458355999999999E-2</v>
+        <v>1.5441109999999999E-2</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5470955999999999E-2</v>
+        <v>1.5449595999999999E-2</v>
       </c>
       <c r="M10" s="3">
-        <v>1.2896555000000001E-2</v>
+        <v>1.3243167E-2</v>
       </c>
       <c r="N10" s="3">
-        <v>1.2819697E-2</v>
+        <v>1.3283092E-2</v>
       </c>
       <c r="O10" s="3">
-        <v>1.2756648000000001E-2</v>
+        <v>1.3171778E-2</v>
       </c>
       <c r="P10" s="3">
-        <v>1.2875129000000001E-2</v>
+        <v>1.3254002000000001E-2</v>
       </c>
       <c r="Q10" s="3">
-        <v>1.2809541000000001E-2</v>
+        <v>1.3168598E-2</v>
       </c>
       <c r="R10" s="3">
-        <v>1.2843141000000001E-2</v>
+        <v>1.3172807999999999E-2</v>
       </c>
       <c r="S10" s="3">
-        <v>1.2857366E-2</v>
+        <v>1.3273307999999999E-2</v>
       </c>
       <c r="T10" s="3">
-        <v>1.2847195E-2</v>
+        <v>1.3218651E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M11" s="3">
-        <v>1.4292417E-2</v>
+        <v>1.4398592999999999E-2</v>
       </c>
       <c r="N11" s="3">
-        <v>1.4190101E-2</v>
+        <v>1.4412874000000001E-2</v>
       </c>
       <c r="O11" s="3">
-        <v>1.4151115000000001E-2</v>
+        <v>1.4301707E-2</v>
       </c>
       <c r="P11" s="3">
-        <v>1.4236709E-2</v>
+        <v>1.4372822E-2</v>
       </c>
       <c r="Q11" s="3">
-        <v>1.4195940000000001E-2</v>
+        <v>1.4317292000000001E-2</v>
       </c>
       <c r="R11" s="3">
-        <v>1.4232452E-2</v>
+        <v>1.4291422E-2</v>
       </c>
       <c r="S11" s="3">
-        <v>1.4270338E-2</v>
+        <v>1.4440583E-2</v>
       </c>
       <c r="T11" s="3">
-        <v>1.425939E-2</v>
+        <v>1.4366152E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -1161,28 +1170,28 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="M12" s="3">
-        <v>1.4789633E-2</v>
+        <v>1.4702112999999999E-2</v>
       </c>
       <c r="N12" s="3">
-        <v>1.4681454E-2</v>
+        <v>1.4584512000000001E-2</v>
       </c>
       <c r="O12" s="3">
-        <v>1.4664734E-2</v>
+        <v>1.4508119E-2</v>
       </c>
       <c r="P12" s="3">
-        <v>1.4720458000000001E-2</v>
+        <v>1.4570873999999999E-2</v>
       </c>
       <c r="Q12" s="3">
-        <v>1.4680418000000001E-2</v>
+        <v>1.4505763E-2</v>
       </c>
       <c r="R12" s="3">
-        <v>1.4744762999999999E-2</v>
+        <v>1.4571235E-2</v>
       </c>
       <c r="S12" s="3">
-        <v>1.4699577E-2</v>
+        <v>1.4568578E-2</v>
       </c>
       <c r="T12" s="3">
-        <v>1.4753726E-2</v>
+        <v>1.4606920000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -1214,28 +1223,28 @@
         <v>8</v>
       </c>
       <c r="M13" s="3">
-        <v>1.4701643E-2</v>
+        <v>1.4575025E-2</v>
       </c>
       <c r="N13" s="3">
-        <v>1.4636616999999999E-2</v>
+        <v>1.4372538000000001E-2</v>
       </c>
       <c r="O13" s="3">
-        <v>1.460235E-2</v>
+        <v>1.4340105000000001E-2</v>
       </c>
       <c r="P13" s="3">
-        <v>1.4660184E-2</v>
+        <v>1.4466662999999999E-2</v>
       </c>
       <c r="Q13" s="3">
-        <v>1.4591923999999999E-2</v>
+        <v>1.4373998000000001E-2</v>
       </c>
       <c r="R13" s="3">
-        <v>1.4672404E-2</v>
+        <v>1.4446616000000001E-2</v>
       </c>
       <c r="S13" s="3">
-        <v>1.4565448999999999E-2</v>
+        <v>1.4405522E-2</v>
       </c>
       <c r="T13" s="3">
-        <v>1.464184E-2</v>
+        <v>1.4441905999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -1244,59 +1253,59 @@
       </c>
       <c r="B14" s="1">
         <f>M9</f>
-        <v>8.985916E-3</v>
+        <v>9.5857879999999996E-3</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" ref="C14:I21" si="2">N9</f>
-        <v>8.9683349999999992E-3</v>
+        <v>9.5079710000000005E-3</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="2"/>
-        <v>8.8729020000000002E-3</v>
+        <v>9.4704880000000009E-3</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="2"/>
-        <v>9.0172989999999995E-3</v>
+        <v>9.6113629999999995E-3</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="2"/>
-        <v>8.9233200000000002E-3</v>
+        <v>9.4009109999999996E-3</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="2"/>
-        <v>8.9655870000000006E-3</v>
+        <v>9.5508899999999994E-3</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v>8.8888860000000004E-3</v>
+        <v>9.5773260000000006E-3</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>8.9290859999999993E-3</v>
+        <v>9.4803200000000004E-3</v>
       </c>
       <c r="M14" s="3">
-        <v>1.4582238000000001E-2</v>
+        <v>1.4516436000000001E-2</v>
       </c>
       <c r="N14" s="3">
-        <v>1.4572541E-2</v>
+        <v>1.4223157E-2</v>
       </c>
       <c r="O14" s="3">
-        <v>1.4506811E-2</v>
+        <v>1.4168887999999999E-2</v>
       </c>
       <c r="P14" s="3">
-        <v>1.457554E-2</v>
+        <v>1.4440203E-2</v>
       </c>
       <c r="Q14" s="3">
-        <v>1.4458726999999999E-2</v>
+        <v>1.4163705E-2</v>
       </c>
       <c r="R14" s="3">
-        <v>1.4538061E-2</v>
+        <v>1.4325831000000001E-2</v>
       </c>
       <c r="S14" s="3">
-        <v>1.4420420999999999E-2</v>
+        <v>1.4271053000000001E-2</v>
       </c>
       <c r="T14" s="3">
-        <v>1.4504530999999999E-2</v>
+        <v>1.438797E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -1305,59 +1314,59 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" ref="B15:B21" si="3">M10</f>
-        <v>1.2896555000000001E-2</v>
+        <v>1.3243167E-2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2819697E-2</v>
+        <v>1.3283092E-2</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2756648000000001E-2</v>
+        <v>1.3171778E-2</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2875129000000001E-2</v>
+        <v>1.3254002000000001E-2</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2809541000000001E-2</v>
+        <v>1.3168598E-2</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2843141000000001E-2</v>
+        <v>1.3172807999999999E-2</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2857366E-2</v>
+        <v>1.3273307999999999E-2</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>1.2847195E-2</v>
+        <v>1.3218651E-2</v>
       </c>
       <c r="M15" s="3">
-        <v>1.3981667E-2</v>
+        <v>1.3876304000000001E-2</v>
       </c>
       <c r="N15" s="3">
-        <v>1.4047521E-2</v>
+        <v>1.3623939999999999E-2</v>
       </c>
       <c r="O15" s="3">
-        <v>1.3962280000000001E-2</v>
+        <v>1.3633045E-2</v>
       </c>
       <c r="P15" s="3">
-        <v>1.4055382999999999E-2</v>
+        <v>1.3937110000000001E-2</v>
       </c>
       <c r="Q15" s="3">
-        <v>1.3871331000000001E-2</v>
+        <v>1.3616359E-2</v>
       </c>
       <c r="R15" s="3">
-        <v>1.3936169E-2</v>
+        <v>1.3776525E-2</v>
       </c>
       <c r="S15" s="3">
-        <v>1.3855258000000001E-2</v>
+        <v>1.3746171E-2</v>
       </c>
       <c r="T15" s="3">
-        <v>1.3912627E-2</v>
+        <v>1.3879752E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -1366,59 +1375,59 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="3"/>
-        <v>1.4292417E-2</v>
+        <v>1.4398592999999999E-2</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4190101E-2</v>
+        <v>1.4412874000000001E-2</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4151115000000001E-2</v>
+        <v>1.4301707E-2</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4236709E-2</v>
+        <v>1.4372822E-2</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4195940000000001E-2</v>
+        <v>1.4317292000000001E-2</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4232452E-2</v>
+        <v>1.4291422E-2</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4270338E-2</v>
+        <v>1.4440583E-2</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>1.425939E-2</v>
+        <v>1.4366152E-2</v>
       </c>
       <c r="M16" s="3">
-        <v>1.1421339000000001E-2</v>
+        <v>1.136701E-2</v>
       </c>
       <c r="N16" s="3">
-        <v>1.1611799000000001E-2</v>
+        <v>1.1102363000000001E-2</v>
       </c>
       <c r="O16" s="3">
-        <v>1.1520239E-2</v>
+        <v>1.1227157E-2</v>
       </c>
       <c r="P16" s="3">
-        <v>1.1648794000000001E-2</v>
+        <v>1.1634211E-2</v>
       </c>
       <c r="Q16" s="3">
-        <v>1.1346047E-2</v>
+        <v>1.1162033999999999E-2</v>
       </c>
       <c r="R16" s="3">
-        <v>1.1378055E-2</v>
+        <v>1.1302520999999999E-2</v>
       </c>
       <c r="S16" s="3">
-        <v>1.1398449E-2</v>
+        <v>1.1383008999999999E-2</v>
       </c>
       <c r="T16" s="3">
-        <v>1.1392868E-2</v>
+        <v>1.1516579000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -1427,59 +1436,59 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="3"/>
-        <v>1.4789633E-2</v>
+        <v>1.4702112999999999E-2</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4681454E-2</v>
+        <v>1.4584512000000001E-2</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4664734E-2</v>
+        <v>1.4508119E-2</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4720458000000001E-2</v>
+        <v>1.4570873999999999E-2</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4680418000000001E-2</v>
+        <v>1.4505763E-2</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4744762999999999E-2</v>
+        <v>1.4571235E-2</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4699577E-2</v>
+        <v>1.4568578E-2</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4753726E-2</v>
+        <v>1.4606920000000001E-2</v>
       </c>
       <c r="M17" s="3">
-        <v>1.5375669999999999E-2</v>
+        <v>1.5460606999999999E-2</v>
       </c>
       <c r="N17" s="3">
-        <v>1.5377666E-2</v>
+        <v>1.5185120999999999E-2</v>
       </c>
       <c r="O17" s="3">
-        <v>1.5388990999999999E-2</v>
+        <v>1.51734E-2</v>
       </c>
       <c r="P17" s="3">
-        <v>1.5366177999999999E-2</v>
+        <v>1.5256438000000001E-2</v>
       </c>
       <c r="Q17" s="3">
-        <v>1.5365943999999999E-2</v>
+        <v>1.5223633E-2</v>
       </c>
       <c r="R17" s="3">
-        <v>1.5399579E-2</v>
+        <v>1.5263499E-2</v>
       </c>
       <c r="S17" s="3">
-        <v>1.5290356999999999E-2</v>
+        <v>1.5157435E-2</v>
       </c>
       <c r="T17" s="3">
-        <v>1.534628E-2</v>
+        <v>1.5210446000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -1488,59 +1497,59 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="3"/>
-        <v>1.4701643E-2</v>
+        <v>1.4575025E-2</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4636616999999999E-2</v>
+        <v>1.4372538000000001E-2</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="2"/>
-        <v>1.460235E-2</v>
+        <v>1.4340105000000001E-2</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4660184E-2</v>
+        <v>1.4466662999999999E-2</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4591923999999999E-2</v>
+        <v>1.4373998000000001E-2</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4672404E-2</v>
+        <v>1.4446616000000001E-2</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4565448999999999E-2</v>
+        <v>1.4405522E-2</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>1.464184E-2</v>
+        <v>1.4441905999999999E-2</v>
       </c>
       <c r="M18" s="3">
-        <v>1.5309168E-2</v>
+        <v>1.5388021E-2</v>
       </c>
       <c r="N18" s="3">
-        <v>1.5330808E-2</v>
+        <v>1.5064731E-2</v>
       </c>
       <c r="O18" s="3">
-        <v>1.5316252000000001E-2</v>
+        <v>1.5090933000000001E-2</v>
       </c>
       <c r="P18" s="3">
-        <v>1.532235E-2</v>
+        <v>1.5193577999999999E-2</v>
       </c>
       <c r="Q18" s="3">
-        <v>1.5290758999999999E-2</v>
+        <v>1.5099306E-2</v>
       </c>
       <c r="R18" s="3">
-        <v>1.5338831000000001E-2</v>
+        <v>1.5197777000000001E-2</v>
       </c>
       <c r="S18" s="3">
-        <v>1.517571E-2</v>
+        <v>1.5053834E-2</v>
       </c>
       <c r="T18" s="3">
-        <v>1.5264967000000001E-2</v>
+        <v>1.5098501E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -1549,59 +1558,59 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="3"/>
-        <v>1.4582238000000001E-2</v>
+        <v>1.4516436000000001E-2</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4572541E-2</v>
+        <v>1.4223157E-2</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4506811E-2</v>
+        <v>1.4168887999999999E-2</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="2"/>
-        <v>1.457554E-2</v>
+        <v>1.4440203E-2</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4458726999999999E-2</v>
+        <v>1.4163705E-2</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4538061E-2</v>
+        <v>1.4325831000000001E-2</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4420420999999999E-2</v>
+        <v>1.4271053000000001E-2</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4504530999999999E-2</v>
+        <v>1.438797E-2</v>
       </c>
       <c r="M19" s="3">
-        <v>1.5318884E-2</v>
+        <v>1.5380532000000001E-2</v>
       </c>
       <c r="N19" s="3">
-        <v>1.5343228E-2</v>
+        <v>1.5098355000000001E-2</v>
       </c>
       <c r="O19" s="3">
-        <v>1.5319531000000001E-2</v>
+        <v>1.5121018E-2</v>
       </c>
       <c r="P19" s="3">
-        <v>1.5340347000000001E-2</v>
+        <v>1.5226099999999999E-2</v>
       </c>
       <c r="Q19" s="3">
-        <v>1.5297453000000001E-2</v>
+        <v>1.5116743E-2</v>
       </c>
       <c r="R19" s="3">
-        <v>1.5346501E-2</v>
+        <v>1.5222526E-2</v>
       </c>
       <c r="S19" s="3">
-        <v>1.5188333E-2</v>
+        <v>1.5093499E-2</v>
       </c>
       <c r="T19" s="3">
-        <v>1.5267694E-2</v>
+        <v>1.5124186E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1610,59 +1619,59 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="3"/>
-        <v>1.3981667E-2</v>
+        <v>1.3876304000000001E-2</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="2"/>
-        <v>1.4047521E-2</v>
+        <v>1.3623939999999999E-2</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3962280000000001E-2</v>
+        <v>1.3633045E-2</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>1.4055382999999999E-2</v>
+        <v>1.3937110000000001E-2</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3871331000000001E-2</v>
+        <v>1.3616359E-2</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3936169E-2</v>
+        <v>1.3776525E-2</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3855258000000001E-2</v>
+        <v>1.3746171E-2</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3912627E-2</v>
+        <v>1.3879752E-2</v>
       </c>
       <c r="M20" s="3">
-        <v>1.5390482E-2</v>
+        <v>1.5417725E-2</v>
       </c>
       <c r="N20" s="3">
-        <v>1.5396429999999999E-2</v>
+        <v>1.5260350000000001E-2</v>
       </c>
       <c r="O20" s="3">
-        <v>1.5377711000000001E-2</v>
+        <v>1.5265997E-2</v>
       </c>
       <c r="P20" s="3">
-        <v>1.5394699E-2</v>
+        <v>1.5337414000000001E-2</v>
       </c>
       <c r="Q20" s="3">
-        <v>1.536245E-2</v>
+        <v>1.5259754E-2</v>
       </c>
       <c r="R20" s="3">
-        <v>1.5398093E-2</v>
+        <v>1.5325841E-2</v>
       </c>
       <c r="S20" s="3">
-        <v>1.5310285E-2</v>
+        <v>1.5267584000000001E-2</v>
       </c>
       <c r="T20" s="3">
-        <v>1.5347315E-2</v>
+        <v>1.528624E-2</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1671,85 +1680,85 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="3"/>
-        <v>1.1421339000000001E-2</v>
+        <v>1.136701E-2</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1611799000000001E-2</v>
+        <v>1.1102363000000001E-2</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1520239E-2</v>
+        <v>1.1227157E-2</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1648794000000001E-2</v>
+        <v>1.1634211E-2</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1346047E-2</v>
+        <v>1.1162033999999999E-2</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1378055E-2</v>
+        <v>1.1302520999999999E-2</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1398449E-2</v>
+        <v>1.1383008999999999E-2</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1392868E-2</v>
+        <v>1.1516579000000001E-2</v>
       </c>
       <c r="M21" s="3">
-        <v>1.5428266E-2</v>
+        <v>1.5429371000000001E-2</v>
       </c>
       <c r="N21" s="3">
-        <v>1.5419347E-2</v>
+        <v>1.5339591E-2</v>
       </c>
       <c r="O21" s="3">
-        <v>1.5418766E-2</v>
+        <v>1.5337886E-2</v>
       </c>
       <c r="P21" s="3">
-        <v>1.5418616E-2</v>
+        <v>1.5381308999999999E-2</v>
       </c>
       <c r="Q21" s="3">
-        <v>1.539627E-2</v>
+        <v>1.5336654E-2</v>
       </c>
       <c r="R21" s="3">
-        <v>1.5424863E-2</v>
+        <v>1.5372050999999999E-2</v>
       </c>
       <c r="S21" s="3">
-        <v>1.5377003E-2</v>
+        <v>1.5352174999999999E-2</v>
       </c>
       <c r="T21" s="3">
-        <v>1.5394955E-2</v>
+        <v>1.5363714000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M22" s="3">
-        <v>1.5449371E-2</v>
+        <v>1.5438189E-2</v>
       </c>
       <c r="N22" s="3">
-        <v>1.5436352E-2</v>
+        <v>1.5372445E-2</v>
       </c>
       <c r="O22" s="3">
-        <v>1.5444223E-2</v>
+        <v>1.5371027000000001E-2</v>
       </c>
       <c r="P22" s="3">
-        <v>1.5436355000000001E-2</v>
+        <v>1.5398904E-2</v>
       </c>
       <c r="Q22" s="3">
-        <v>1.5419452E-2</v>
+        <v>1.5368715E-2</v>
       </c>
       <c r="R22" s="3">
-        <v>1.5445212999999999E-2</v>
+        <v>1.5396452999999999E-2</v>
       </c>
       <c r="S22" s="3">
-        <v>1.5412172999999999E-2</v>
+        <v>1.5389172E-2</v>
       </c>
       <c r="T22" s="3">
-        <v>1.5425555000000001E-2</v>
+        <v>1.5395835E-2</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -1765,28 +1774,28 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="M23" s="3">
-        <v>1.5466885E-2</v>
+        <v>1.5438093E-2</v>
       </c>
       <c r="N23" s="3">
-        <v>1.5450837E-2</v>
+        <v>1.5384689999999999E-2</v>
       </c>
       <c r="O23" s="3">
-        <v>1.5464853000000001E-2</v>
+        <v>1.5387779000000001E-2</v>
       </c>
       <c r="P23" s="3">
-        <v>1.5453527999999999E-2</v>
+        <v>1.5409419000000001E-2</v>
       </c>
       <c r="Q23" s="3">
-        <v>1.543607E-2</v>
+        <v>1.5384178E-2</v>
       </c>
       <c r="R23" s="3">
-        <v>1.5463789E-2</v>
+        <v>1.5408744E-2</v>
       </c>
       <c r="S23" s="3">
-        <v>1.5432859E-2</v>
+        <v>1.5400811E-2</v>
       </c>
       <c r="T23" s="3">
-        <v>1.5450679E-2</v>
+        <v>1.5408893E-2</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1818,28 +1827,28 @@
         <v>8</v>
       </c>
       <c r="M24" s="3">
-        <v>1.5493457E-2</v>
+        <v>1.545443E-2</v>
       </c>
       <c r="N24" s="3">
-        <v>1.5475907000000001E-2</v>
+        <v>1.5409826999999999E-2</v>
       </c>
       <c r="O24" s="3">
-        <v>1.5485989E-2</v>
+        <v>1.5409910000000001E-2</v>
       </c>
       <c r="P24" s="3">
-        <v>1.5478252E-2</v>
+        <v>1.5426683E-2</v>
       </c>
       <c r="Q24" s="3">
-        <v>1.5462424000000001E-2</v>
+        <v>1.5407743999999999E-2</v>
       </c>
       <c r="R24" s="3">
-        <v>1.5485408000000001E-2</v>
+        <v>1.5426611999999999E-2</v>
       </c>
       <c r="S24" s="3">
-        <v>1.5460293E-2</v>
+        <v>1.5426082000000001E-2</v>
       </c>
       <c r="T24" s="3">
-        <v>1.5477258000000001E-2</v>
+        <v>1.5429859000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1848,59 +1857,59 @@
       </c>
       <c r="B25" s="2">
         <f>20*LOG(((B14)*B$6)/(B3*(B$17)), 10)</f>
-        <v>-4.3214696143988984</v>
+        <v>-3.7313102512266716</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25:I25" si="4">20*LOG(((C14)*C$6)/(C3*(C$17)), 10)</f>
-        <v>-4.2703732696348879</v>
+        <v>-3.6720598398462116</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.372577760992753</v>
+        <v>-3.646474637238204</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.2436580321311199</v>
+        <v>-3.5626046085475642</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.3291072945240909</v>
+        <v>-3.7403633791838917</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.3221963623064061</v>
+        <v>-3.6281814145943736</v>
       </c>
       <c r="H25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.3585457422889924</v>
+        <v>-3.5755100504911672</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
-        <v>-4.3627449953402806</v>
+        <v>-3.7063070340580824</v>
       </c>
       <c r="M25" s="3">
-        <v>9.1777060000000008E-3</v>
+        <v>9.7773419999999996E-3</v>
       </c>
       <c r="N25" s="3">
-        <v>9.171383E-3</v>
+        <v>9.7637880000000007E-3</v>
       </c>
       <c r="O25" s="3">
-        <v>9.0899499999999994E-3</v>
+        <v>9.8411220000000008E-3</v>
       </c>
       <c r="P25" s="3">
-        <v>9.233069E-3</v>
+        <v>9.8550749999999996E-3</v>
       </c>
       <c r="Q25" s="3">
-        <v>9.1374620000000007E-3</v>
+        <v>9.7710999999999996E-3</v>
       </c>
       <c r="R25" s="3">
-        <v>9.1664499999999996E-3</v>
+        <v>9.8427540000000004E-3</v>
       </c>
       <c r="S25" s="3">
-        <v>9.0865879999999996E-3</v>
+        <v>9.8370479999999993E-3</v>
       </c>
       <c r="T25" s="3">
-        <v>9.1434689999999996E-3</v>
+        <v>9.7172249999999995E-3</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1909,59 +1918,59 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" ref="B26:I26" si="5">20*LOG(((B15)*B$6)/(B4*(B$17)), 10)</f>
-        <v>-1.1435286932881064</v>
+        <v>-0.88601964216684748</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1413977584423898</v>
+        <v>-0.70152825464386037</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1780755254095265</v>
+        <v>-0.73624093076836683</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.124764881614712</v>
+        <v>-0.73695062390219845</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1460640117069705</v>
+        <v>-0.74246605755747608</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.1661508654714874</v>
+        <v>-0.80329448933223424</v>
       </c>
       <c r="H26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.0885802325635594</v>
+        <v>-0.67975403753787922</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="5"/>
-        <v>-1.156235494201634</v>
+        <v>-0.75424307266107493</v>
       </c>
       <c r="M26" s="3">
-        <v>1.3138046E-2</v>
+        <v>1.3472259E-2</v>
       </c>
       <c r="N26" s="3">
-        <v>1.3071134E-2</v>
+        <v>1.3613867999999999E-2</v>
       </c>
       <c r="O26" s="3">
-        <v>1.3018643999999999E-2</v>
+        <v>1.3554066E-2</v>
       </c>
       <c r="P26" s="3">
-        <v>1.3143881E-2</v>
+        <v>1.3572486999999999E-2</v>
       </c>
       <c r="Q26" s="3">
-        <v>1.3078963000000001E-2</v>
+        <v>1.3506873000000001E-2</v>
       </c>
       <c r="R26" s="3">
-        <v>1.3086079E-2</v>
+        <v>1.3530873000000001E-2</v>
       </c>
       <c r="S26" s="3">
-        <v>1.3111291000000001E-2</v>
+        <v>1.3602635E-2</v>
       </c>
       <c r="T26" s="3">
-        <v>1.3109829999999999E-2</v>
+        <v>1.3586007000000001E-2</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -1970,59 +1979,59 @@
       </c>
       <c r="B27" s="2">
         <f t="shared" ref="B27:I27" si="6">20*LOG(((B16)*B$6)/(B5*(B$17)), 10)</f>
-        <v>-0.25892413988106289</v>
+        <v>-0.15801519860075486</v>
       </c>
       <c r="C27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.26537479758349675</v>
+        <v>-9.4521815251235944E-3</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.27689679918788113</v>
+        <v>-3.9929110859919729E-2</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.25747499080257219</v>
+        <v>-5.1802610352136208E-2</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.25480243170557026</v>
+        <v>-2.8470987591029413E-2</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.27911823675154684</v>
+        <v>-0.10932617866061028</v>
       </c>
       <c r="H27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.18909793132738123</v>
+        <v>2.5601075183208543E-2</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.25233012468488153</v>
+        <v>-5.016582602582173E-2</v>
       </c>
       <c r="M27" s="3">
-        <v>1.454047E-2</v>
+        <v>1.4641395E-2</v>
       </c>
       <c r="N27" s="3">
-        <v>1.4450714E-2</v>
+        <v>1.4792606999999999E-2</v>
       </c>
       <c r="O27" s="3">
-        <v>1.4421216000000001E-2</v>
+        <v>1.4695919E-2</v>
       </c>
       <c r="P27" s="3">
-        <v>1.4511537E-2</v>
+        <v>1.4671152E-2</v>
       </c>
       <c r="Q27" s="3">
-        <v>1.4477686E-2</v>
+        <v>1.4683015000000001E-2</v>
       </c>
       <c r="R27" s="3">
-        <v>1.4489207E-2</v>
+        <v>1.466275E-2</v>
       </c>
       <c r="S27" s="3">
-        <v>1.4532478E-2</v>
+        <v>1.47735E-2</v>
       </c>
       <c r="T27" s="3">
-        <v>1.4524854E-2</v>
+        <v>1.4697029E-2</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -2062,28 +2071,28 @@
         <v>0</v>
       </c>
       <c r="M28" s="3">
-        <v>1.5011606E-2</v>
+        <v>1.4925163999999999E-2</v>
       </c>
       <c r="N28" s="3">
-        <v>1.4909253000000001E-2</v>
+        <v>1.490814E-2</v>
       </c>
       <c r="O28" s="3">
-        <v>1.4900296E-2</v>
+        <v>1.4847898999999999E-2</v>
       </c>
       <c r="P28" s="3">
-        <v>1.4952145999999999E-2</v>
+        <v>1.4876749999999999E-2</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.4922763E-2</v>
+        <v>1.4882256E-2</v>
       </c>
       <c r="R28" s="3">
-        <v>1.4968993E-2</v>
+        <v>1.4855302000000001E-2</v>
       </c>
       <c r="S28" s="3">
-        <v>1.4927147999999999E-2</v>
+        <v>1.4888268E-2</v>
       </c>
       <c r="T28" s="3">
-        <v>1.4981971E-2</v>
+        <v>1.4903115E-2</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -2092,59 +2101,59 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29:I29" si="8">20*LOG(((B18)*B$6)/(B7*(B$17)), 10)</f>
-        <v>-7.2584743588500464E-2</v>
+        <v>-8.1713497966003287E-2</v>
       </c>
       <c r="C29" s="2">
         <f t="shared" si="8"/>
-        <v>-3.8554431463447197E-2</v>
+        <v>-0.17567003636583928</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="8"/>
-        <v>-6.1405507627318862E-2</v>
+        <v>-0.14164949009851607</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="8"/>
-        <v>-5.0429945501508866E-2</v>
+        <v>-8.8016565146174994E-2</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="8"/>
-        <v>-7.3668206303857134E-2</v>
+        <v>-0.12432654782394886</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
-        <v>-5.902971444548117E-2</v>
+        <v>-0.10324106514750692</v>
       </c>
       <c r="H29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.11863672256063537</v>
+        <v>-0.1466369274411341</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="8"/>
-        <v>-9.5783337271758764E-2</v>
+        <v>-0.14245068181638851</v>
       </c>
       <c r="M29" s="3">
-        <v>1.4851836E-2</v>
+        <v>1.4766206E-2</v>
       </c>
       <c r="N29" s="3">
-        <v>1.4793120999999999E-2</v>
+        <v>1.4670516E-2</v>
       </c>
       <c r="O29" s="3">
-        <v>1.4760192E-2</v>
+        <v>1.4656508E-2</v>
       </c>
       <c r="P29" s="3">
-        <v>1.4817568E-2</v>
+        <v>1.4688618000000001E-2</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.4763116E-2</v>
+        <v>1.4647568E-2</v>
       </c>
       <c r="R29" s="3">
-        <v>1.4817163E-2</v>
+        <v>1.4706597E-2</v>
       </c>
       <c r="S29" s="3">
-        <v>1.4719731E-2</v>
+        <v>1.4677529E-2</v>
       </c>
       <c r="T29" s="3">
-        <v>1.4800363E-2</v>
+        <v>1.4668687E-2</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2153,59 +2162,59 @@
       </c>
       <c r="B30" s="2">
         <f t="shared" ref="B30:I30" si="9">20*LOG(((B19)*B$6)/(B8*(B$17)), 10)</f>
-        <v>-0.15827985207385914</v>
+        <v>-0.12108424675943605</v>
       </c>
       <c r="C30" s="2">
         <f t="shared" si="9"/>
-        <v>-8.8416412850498713E-2</v>
+        <v>-0.28395832673165861</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.13292462110536857</v>
+        <v>-0.26507193706097654</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.11129267295693045</v>
+        <v>-0.11545991753305658</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.16671152638702819</v>
+        <v>-0.27192938203339645</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.15140243965818517</v>
+        <v>-0.19009634359910116</v>
       </c>
       <c r="H30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.2259570744142321</v>
+        <v>-0.25055269966333671</v>
       </c>
       <c r="I30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.19567664202728607</v>
+        <v>-0.19599096353314246</v>
       </c>
       <c r="M30" s="3">
-        <v>1.4627967E-2</v>
+        <v>1.4539389999999999E-2</v>
       </c>
       <c r="N30" s="3">
-        <v>1.4622161E-2</v>
+        <v>1.4393131E-2</v>
       </c>
       <c r="O30" s="3">
-        <v>1.4561447999999999E-2</v>
+        <v>1.4454369E-2</v>
       </c>
       <c r="P30" s="3">
-        <v>1.4641372E-2</v>
+        <v>1.4580408E-2</v>
       </c>
       <c r="Q30" s="3">
-        <v>1.4519815E-2</v>
+        <v>1.4406587E-2</v>
       </c>
       <c r="R30" s="3">
-        <v>1.4588353E-2</v>
+        <v>1.451565E-2</v>
       </c>
       <c r="S30" s="3">
-        <v>1.448259E-2</v>
+        <v>1.4451637999999999E-2</v>
       </c>
       <c r="T30" s="3">
-        <v>1.4555444000000001E-2</v>
+        <v>1.4554111999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -2214,59 +2223,59 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" ref="B31:I31" si="10">20*LOG(((B20)*B$6)/(B9*(B$17)), 10)</f>
-        <v>-0.53293893621245836</v>
+        <v>-0.51547030331790711</v>
       </c>
       <c r="C31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.41632692605474098</v>
+        <v>-0.66809142650989128</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.47647457603601273</v>
+        <v>-0.61033623787013713</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.43653114674231724</v>
+        <v>-0.42737140594206013</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.53570249620754318</v>
+        <v>-0.62302425190445465</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.52749515548907044</v>
+        <v>-0.53625909138843453</v>
       </c>
       <c r="H31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.58374102086030355</v>
+        <v>-0.58347768306695058</v>
       </c>
       <c r="I31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.56857894385884045</v>
+        <v>-0.51484454710816929</v>
       </c>
       <c r="M31" s="3">
-        <v>1.3947795000000001E-2</v>
+        <v>1.3876416000000001E-2</v>
       </c>
       <c r="N31" s="3">
-        <v>1.4004518000000001E-2</v>
+        <v>1.3730727999999999E-2</v>
       </c>
       <c r="O31" s="3">
-        <v>1.3934732999999999E-2</v>
+        <v>1.378098E-2</v>
       </c>
       <c r="P31" s="3">
-        <v>1.4033811E-2</v>
+        <v>1.404476E-2</v>
       </c>
       <c r="Q31" s="3">
-        <v>1.38382E-2</v>
+        <v>1.3730674E-2</v>
       </c>
       <c r="R31" s="3">
-        <v>1.3909871000000001E-2</v>
+        <v>1.3871333E-2</v>
       </c>
       <c r="S31" s="3">
-        <v>1.3834123E-2</v>
+        <v>1.384909E-2</v>
       </c>
       <c r="T31" s="3">
-        <v>1.387715E-2</v>
+        <v>1.3953897999999999E-2</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -2275,111 +2284,111 @@
       </c>
       <c r="B32" s="2">
         <f t="shared" ref="B32:I32" si="11">20*LOG(((B21)*B$6)/(B10*(B$17)), 10)</f>
-        <v>-2.3028718204946403</v>
+        <v>-2.2545269888378296</v>
       </c>
       <c r="C32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.0819524795615081</v>
+        <v>-2.4576433098595691</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.1571635423992195</v>
+        <v>-2.3102474305827765</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.0801955607375753</v>
+        <v>-2.0082792300476706</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.2970795466652123</v>
+        <v>-2.363128615561588</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.3012723264040917</v>
+        <v>-2.2675816530691213</v>
       </c>
       <c r="H32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.2943412795830391</v>
+        <v>-2.236184999367834</v>
       </c>
       <c r="I32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.3176280327801888</v>
+        <v>-2.1505462221511942</v>
       </c>
       <c r="M32" s="3">
-        <v>1.1283257999999999E-2</v>
+        <v>1.127977E-2</v>
       </c>
       <c r="N32" s="3">
-        <v>1.1460112E-2</v>
+        <v>1.1121809E-2</v>
       </c>
       <c r="O32" s="3">
-        <v>1.1402773E-2</v>
+        <v>1.1278541E-2</v>
       </c>
       <c r="P32" s="3">
-        <v>1.1532779999999999E-2</v>
+        <v>1.1598567000000001E-2</v>
       </c>
       <c r="Q32" s="3">
-        <v>1.1205911000000001E-2</v>
+        <v>1.12041E-2</v>
       </c>
       <c r="R32" s="3">
-        <v>1.1256657999999999E-2</v>
+        <v>1.1327940999999999E-2</v>
       </c>
       <c r="S32" s="3">
-        <v>1.1291907E-2</v>
+        <v>1.1388987E-2</v>
       </c>
       <c r="T32" s="3">
-        <v>1.1257814E-2</v>
+        <v>1.1515795000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M33" s="3">
-        <v>1.5380922E-2</v>
+        <v>1.5456351E-2</v>
       </c>
       <c r="N33" s="3">
-        <v>1.5383163E-2</v>
+        <v>1.5186470000000001E-2</v>
       </c>
       <c r="O33" s="3">
-        <v>1.539715E-2</v>
+        <v>1.5170253E-2</v>
       </c>
       <c r="P33" s="3">
-        <v>1.5370943999999999E-2</v>
+        <v>1.5258571E-2</v>
       </c>
       <c r="Q33" s="3">
-        <v>1.5370253E-2</v>
+        <v>1.5220925E-2</v>
       </c>
       <c r="R33" s="3">
-        <v>1.5403902000000001E-2</v>
+        <v>1.5265224000000001E-2</v>
       </c>
       <c r="S33" s="3">
-        <v>1.5296475E-2</v>
+        <v>1.5154994999999999E-2</v>
       </c>
       <c r="T33" s="3">
-        <v>1.5350206999999999E-2</v>
+        <v>1.5214017999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M34" s="3">
-        <v>1.5313413E-2</v>
+        <v>1.5379199E-2</v>
       </c>
       <c r="N34" s="3">
-        <v>1.5338276E-2</v>
+        <v>1.5056742E-2</v>
       </c>
       <c r="O34" s="3">
-        <v>1.5325737000000001E-2</v>
+        <v>1.5084901E-2</v>
       </c>
       <c r="P34" s="3">
-        <v>1.5325640999999999E-2</v>
+        <v>1.5190164000000001E-2</v>
       </c>
       <c r="Q34" s="3">
-        <v>1.5296034E-2</v>
+        <v>1.5094196000000001E-2</v>
       </c>
       <c r="R34" s="3">
-        <v>1.5345457999999999E-2</v>
+        <v>1.5195800000000001E-2</v>
       </c>
       <c r="S34" s="3">
-        <v>1.5182747999999999E-2</v>
+        <v>1.504753E-2</v>
       </c>
       <c r="T34" s="3">
-        <v>1.5267711999999999E-2</v>
+        <v>1.5094394000000001E-2</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -2395,28 +2404,28 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="M35" s="3">
-        <v>1.5326503E-2</v>
+        <v>1.5373443000000001E-2</v>
       </c>
       <c r="N35" s="3">
-        <v>1.5348766E-2</v>
+        <v>1.5092080000000001E-2</v>
       </c>
       <c r="O35" s="3">
-        <v>1.5326907000000001E-2</v>
+        <v>1.5114818E-2</v>
       </c>
       <c r="P35" s="3">
-        <v>1.5345444999999999E-2</v>
+        <v>1.5218784000000001E-2</v>
       </c>
       <c r="Q35" s="3">
-        <v>1.5301830000000001E-2</v>
+        <v>1.5115544E-2</v>
       </c>
       <c r="R35" s="3">
-        <v>1.5350822E-2</v>
+        <v>1.5218046000000001E-2</v>
       </c>
       <c r="S35" s="3">
-        <v>1.5191023999999999E-2</v>
+        <v>1.5087816E-2</v>
       </c>
       <c r="T35" s="3">
-        <v>1.5273738E-2</v>
+        <v>1.5121875E-2</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -2448,28 +2457,28 @@
         <v>8</v>
       </c>
       <c r="M36" s="3">
-        <v>1.5392706000000001E-2</v>
+        <v>1.5406510999999999E-2</v>
       </c>
       <c r="N36" s="3">
-        <v>1.5397447999999999E-2</v>
+        <v>1.5250400000000001E-2</v>
       </c>
       <c r="O36" s="3">
-        <v>1.5381127E-2</v>
+        <v>1.5250825000000001E-2</v>
       </c>
       <c r="P36" s="3">
-        <v>1.539577E-2</v>
+        <v>1.5326559E-2</v>
       </c>
       <c r="Q36" s="3">
-        <v>1.5362136E-2</v>
+        <v>1.5252496000000001E-2</v>
       </c>
       <c r="R36" s="3">
-        <v>1.5398012000000001E-2</v>
+        <v>1.5317608E-2</v>
       </c>
       <c r="S36" s="3">
-        <v>1.5310169E-2</v>
+        <v>1.5258776E-2</v>
       </c>
       <c r="T36" s="3">
-        <v>1.5349612E-2</v>
+        <v>1.5274411E-2</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -2478,59 +2487,59 @@
       </c>
       <c r="B37" s="1">
         <f t="shared" ref="B37:I44" si="12">M17</f>
-        <v>1.5375669999999999E-2</v>
+        <v>1.5460606999999999E-2</v>
       </c>
       <c r="C37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5377666E-2</v>
+        <v>1.5185120999999999E-2</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5388990999999999E-2</v>
+        <v>1.51734E-2</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5366177999999999E-2</v>
+        <v>1.5256438000000001E-2</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5365943999999999E-2</v>
+        <v>1.5223633E-2</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5399579E-2</v>
+        <v>1.5263499E-2</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5290356999999999E-2</v>
+        <v>1.5157435E-2</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="12"/>
-        <v>1.534628E-2</v>
+        <v>1.5210446000000001E-2</v>
       </c>
       <c r="M37" s="3">
-        <v>1.5429739E-2</v>
+        <v>1.5417923E-2</v>
       </c>
       <c r="N37" s="3">
-        <v>1.5421574E-2</v>
+        <v>1.5326576999999999E-2</v>
       </c>
       <c r="O37" s="3">
-        <v>1.5421126E-2</v>
+        <v>1.5325893E-2</v>
       </c>
       <c r="P37" s="3">
-        <v>1.5419791E-2</v>
+        <v>1.5367877E-2</v>
       </c>
       <c r="Q37" s="3">
-        <v>1.5398075000000001E-2</v>
+        <v>1.5325834E-2</v>
       </c>
       <c r="R37" s="3">
-        <v>1.5423998E-2</v>
+        <v>1.5358261E-2</v>
       </c>
       <c r="S37" s="3">
-        <v>1.5375206000000001E-2</v>
+        <v>1.5337750000000001E-2</v>
       </c>
       <c r="T37" s="3">
-        <v>1.5397058E-2</v>
+        <v>1.5349091E-2</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -2539,59 +2548,59 @@
       </c>
       <c r="B38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5309168E-2</v>
+        <v>1.5388021E-2</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5330808E-2</v>
+        <v>1.5064731E-2</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5316252000000001E-2</v>
+        <v>1.5090933000000001E-2</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="12"/>
-        <v>1.532235E-2</v>
+        <v>1.5193577999999999E-2</v>
       </c>
       <c r="F38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5290758999999999E-2</v>
+        <v>1.5099306E-2</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5338831000000001E-2</v>
+        <v>1.5197777000000001E-2</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="12"/>
-        <v>1.517571E-2</v>
+        <v>1.5053834E-2</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5264967000000001E-2</v>
+        <v>1.5098501E-2</v>
       </c>
       <c r="M38" s="3">
-        <v>1.5449902E-2</v>
+        <v>1.5422623999999999E-2</v>
       </c>
       <c r="N38" s="3">
-        <v>1.5437565E-2</v>
+        <v>1.5359256999999999E-2</v>
       </c>
       <c r="O38" s="3">
-        <v>1.5448257E-2</v>
+        <v>1.5359533E-2</v>
       </c>
       <c r="P38" s="3">
-        <v>1.5439754999999999E-2</v>
+        <v>1.5389976E-2</v>
       </c>
       <c r="Q38" s="3">
-        <v>1.5422119E-2</v>
+        <v>1.5360478E-2</v>
       </c>
       <c r="R38" s="3">
-        <v>1.5447664E-2</v>
+        <v>1.5382511E-2</v>
       </c>
       <c r="S38" s="3">
-        <v>1.5410841E-2</v>
+        <v>1.5375088E-2</v>
       </c>
       <c r="T38" s="3">
-        <v>1.5427445E-2</v>
+        <v>1.5383152000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -2600,59 +2609,59 @@
       </c>
       <c r="B39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5318884E-2</v>
+        <v>1.5380532000000001E-2</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5343228E-2</v>
+        <v>1.5098355000000001E-2</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5319531000000001E-2</v>
+        <v>1.5121018E-2</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5340347000000001E-2</v>
+        <v>1.5226099999999999E-2</v>
       </c>
       <c r="F39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5297453000000001E-2</v>
+        <v>1.5116743E-2</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5346501E-2</v>
+        <v>1.5222526E-2</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5188333E-2</v>
+        <v>1.5093499E-2</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5267694E-2</v>
+        <v>1.5124186E-2</v>
       </c>
       <c r="M39" s="3">
-        <v>1.5468647E-2</v>
+        <v>1.5426034999999999E-2</v>
       </c>
       <c r="N39" s="3">
-        <v>1.5454557000000001E-2</v>
+        <v>1.5373392E-2</v>
       </c>
       <c r="O39" s="3">
-        <v>1.5464772E-2</v>
+        <v>1.5372200000000001E-2</v>
       </c>
       <c r="P39" s="3">
-        <v>1.5451281000000001E-2</v>
+        <v>1.5396236000000001E-2</v>
       </c>
       <c r="Q39" s="3">
-        <v>1.5439167E-2</v>
+        <v>1.5369041999999999E-2</v>
       </c>
       <c r="R39" s="3">
-        <v>1.5462383999999999E-2</v>
+        <v>1.5391066E-2</v>
       </c>
       <c r="S39" s="3">
-        <v>1.5435552999999999E-2</v>
+        <v>1.5389130000000001E-2</v>
       </c>
       <c r="T39" s="3">
-        <v>1.5447021999999999E-2</v>
+        <v>1.5398926E-2</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -2661,59 +2670,59 @@
       </c>
       <c r="B40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5390482E-2</v>
+        <v>1.5417725E-2</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5396429999999999E-2</v>
+        <v>1.5260350000000001E-2</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5377711000000001E-2</v>
+        <v>1.5265997E-2</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5394699E-2</v>
+        <v>1.5337414000000001E-2</v>
       </c>
       <c r="F40" s="1">
         <f t="shared" si="12"/>
-        <v>1.536245E-2</v>
+        <v>1.5259754E-2</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5398093E-2</v>
+        <v>1.5325841E-2</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5310285E-2</v>
+        <v>1.5267584000000001E-2</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5347315E-2</v>
+        <v>1.528624E-2</v>
       </c>
       <c r="M40" s="3">
-        <v>1.5492574E-2</v>
+        <v>1.5442566E-2</v>
       </c>
       <c r="N40" s="3">
-        <v>1.5474836E-2</v>
+        <v>1.5396356E-2</v>
       </c>
       <c r="O40" s="3">
-        <v>1.5491540999999999E-2</v>
+        <v>1.5397286E-2</v>
       </c>
       <c r="P40" s="3">
-        <v>1.5473674999999999E-2</v>
+        <v>1.5415491999999999E-2</v>
       </c>
       <c r="Q40" s="3">
-        <v>1.5459815999999999E-2</v>
+        <v>1.5393258999999999E-2</v>
       </c>
       <c r="R40" s="3">
-        <v>1.5482315E-2</v>
+        <v>1.5412945000000001E-2</v>
       </c>
       <c r="S40" s="3">
-        <v>1.545941E-2</v>
+        <v>1.5411213999999999E-2</v>
       </c>
       <c r="T40" s="3">
-        <v>1.547053E-2</v>
+        <v>1.5420672E-2</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -2722,59 +2731,59 @@
       </c>
       <c r="B41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5428266E-2</v>
+        <v>1.5429371000000001E-2</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5419347E-2</v>
+        <v>1.5339591E-2</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5418766E-2</v>
+        <v>1.5337886E-2</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5418616E-2</v>
+        <v>1.5381308999999999E-2</v>
       </c>
       <c r="F41" s="1">
         <f t="shared" si="12"/>
-        <v>1.539627E-2</v>
+        <v>1.5336654E-2</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5424863E-2</v>
+        <v>1.5372050999999999E-2</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5377003E-2</v>
+        <v>1.5352174999999999E-2</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5394955E-2</v>
+        <v>1.5363714000000001E-2</v>
       </c>
       <c r="M41" s="3">
-        <v>4.5960542E-2</v>
+        <v>4.8893674999999998E-2</v>
       </c>
       <c r="N41" s="3">
-        <v>4.5977580999999997E-2</v>
+        <v>4.8400595999999997E-2</v>
       </c>
       <c r="O41" s="3">
-        <v>4.5643758E-2</v>
+        <v>4.8553981000000003E-2</v>
       </c>
       <c r="P41" s="3">
-        <v>4.6246134000000001E-2</v>
+        <v>4.8901728999999998E-2</v>
       </c>
       <c r="Q41" s="3">
-        <v>4.5710128000000003E-2</v>
+        <v>4.8554952999999998E-2</v>
       </c>
       <c r="R41" s="3">
-        <v>4.5984231E-2</v>
+        <v>4.8802707000000001E-2</v>
       </c>
       <c r="S41" s="3">
-        <v>4.5665773999999999E-2</v>
+        <v>4.8563343000000002E-2</v>
       </c>
       <c r="T41" s="3">
-        <v>4.5674807999999997E-2</v>
+        <v>4.8299680999999997E-2</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -2783,59 +2792,59 @@
       </c>
       <c r="B42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5449371E-2</v>
+        <v>1.5438189E-2</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5436352E-2</v>
+        <v>1.5372445E-2</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5444223E-2</v>
+        <v>1.5371027000000001E-2</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5436355000000001E-2</v>
+        <v>1.5398904E-2</v>
       </c>
       <c r="F42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5419452E-2</v>
+        <v>1.5368715E-2</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5445212999999999E-2</v>
+        <v>1.5396452999999999E-2</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5412172999999999E-2</v>
+        <v>1.5389172E-2</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5425555000000001E-2</v>
+        <v>1.5395835E-2</v>
       </c>
       <c r="M42" s="3">
-        <v>6.5592742999999995E-2</v>
+        <v>6.7720040999999995E-2</v>
       </c>
       <c r="N42" s="3">
-        <v>6.5440811000000002E-2</v>
+        <v>6.7619525E-2</v>
       </c>
       <c r="O42" s="3">
-        <v>6.5263182000000003E-2</v>
+        <v>6.7129247000000003E-2</v>
       </c>
       <c r="P42" s="3">
-        <v>6.5762229000000005E-2</v>
+        <v>6.7505783999999999E-2</v>
       </c>
       <c r="Q42" s="3">
-        <v>6.5361470000000005E-2</v>
+        <v>6.7328595000000005E-2</v>
       </c>
       <c r="R42" s="3">
-        <v>6.5536610999999995E-2</v>
+        <v>6.7247323999999997E-2</v>
       </c>
       <c r="S42" s="3">
-        <v>6.5749921000000003E-2</v>
+        <v>6.7851111000000006E-2</v>
       </c>
       <c r="T42" s="3">
-        <v>6.5409816999999995E-2</v>
+        <v>6.7479364999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -2844,59 +2853,59 @@
       </c>
       <c r="B43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5466885E-2</v>
+        <v>1.5438093E-2</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5450837E-2</v>
+        <v>1.5384689999999999E-2</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5464853000000001E-2</v>
+        <v>1.5387779000000001E-2</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5453527999999999E-2</v>
+        <v>1.5409419000000001E-2</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" si="12"/>
-        <v>1.543607E-2</v>
+        <v>1.5384178E-2</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5463789E-2</v>
+        <v>1.5408744E-2</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5432859E-2</v>
+        <v>1.5400811E-2</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5450679E-2</v>
+        <v>1.5408893E-2</v>
       </c>
       <c r="M43" s="3">
-        <v>7.2610959000000003E-2</v>
+        <v>7.3252185999999997E-2</v>
       </c>
       <c r="N43" s="3">
-        <v>7.2274594999999997E-2</v>
+        <v>7.3296040000000007E-2</v>
       </c>
       <c r="O43" s="3">
-        <v>7.2271787000000004E-2</v>
+        <v>7.2994805999999995E-2</v>
       </c>
       <c r="P43" s="3">
-        <v>7.2546862000000004E-2</v>
+        <v>7.3272466999999994E-2</v>
       </c>
       <c r="Q43" s="3">
-        <v>7.2342478000000002E-2</v>
+        <v>7.2891787E-2</v>
       </c>
       <c r="R43" s="3">
-        <v>7.2500274000000003E-2</v>
+        <v>7.2940654999999993E-2</v>
       </c>
       <c r="S43" s="3">
-        <v>7.2896904999999998E-2</v>
+        <v>7.3257751999999995E-2</v>
       </c>
       <c r="T43" s="3">
-        <v>7.2430580999999994E-2</v>
+        <v>7.3206119E-2</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -2905,85 +2914,85 @@
       </c>
       <c r="B44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5493457E-2</v>
+        <v>1.545443E-2</v>
       </c>
       <c r="C44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5475907000000001E-2</v>
+        <v>1.5409826999999999E-2</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5485989E-2</v>
+        <v>1.5409910000000001E-2</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5478252E-2</v>
+        <v>1.5426683E-2</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5462424000000001E-2</v>
+        <v>1.5407743999999999E-2</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5485408000000001E-2</v>
+        <v>1.5426611999999999E-2</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5460293E-2</v>
+        <v>1.5426082000000001E-2</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5477258000000001E-2</v>
+        <v>1.5429859000000001E-2</v>
       </c>
       <c r="M44" s="3">
-        <v>7.4945994000000002E-2</v>
+        <v>7.4525810999999997E-2</v>
       </c>
       <c r="N44" s="3">
-        <v>7.4669205000000002E-2</v>
+        <v>7.3929942999999998E-2</v>
       </c>
       <c r="O44" s="3">
-        <v>7.4766494000000003E-2</v>
+        <v>7.3795400999999997E-2</v>
       </c>
       <c r="P44" s="3">
-        <v>7.4819839999999999E-2</v>
+        <v>7.4281535999999995E-2</v>
       </c>
       <c r="Q44" s="3">
-        <v>7.4683114999999994E-2</v>
+        <v>7.3930033000000006E-2</v>
       </c>
       <c r="R44" s="3">
-        <v>7.4932343999999998E-2</v>
+        <v>7.3860325000000004E-2</v>
       </c>
       <c r="S44" s="3">
-        <v>7.4944884000000003E-2</v>
+        <v>7.3983974999999993E-2</v>
       </c>
       <c r="T44" s="3">
-        <v>7.4783987999999996E-2</v>
+        <v>7.4154221000000006E-2</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M45" s="3">
-        <v>7.4408165999999998E-2</v>
+        <v>7.4060424999999999E-2</v>
       </c>
       <c r="N45" s="3">
-        <v>7.4323311000000003E-2</v>
+        <v>7.2829335999999995E-2</v>
       </c>
       <c r="O45" s="3">
-        <v>7.4282467000000005E-2</v>
+        <v>7.2868265000000002E-2</v>
       </c>
       <c r="P45" s="3">
-        <v>7.4351132E-2</v>
+        <v>7.3500827000000005E-2</v>
       </c>
       <c r="Q45" s="3">
-        <v>7.4117905999999997E-2</v>
+        <v>7.2823256000000003E-2</v>
       </c>
       <c r="R45" s="3">
-        <v>7.4391946E-2</v>
+        <v>7.3190346000000003E-2</v>
       </c>
       <c r="S45" s="3">
-        <v>7.4059725000000007E-2</v>
+        <v>7.2956398000000006E-2</v>
       </c>
       <c r="T45" s="3">
-        <v>7.4131608000000002E-2</v>
+        <v>7.3363669000000006E-2</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -2999,28 +3008,28 @@
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="M46" s="3">
-        <v>7.3590039999999995E-2</v>
+        <v>7.3310606E-2</v>
       </c>
       <c r="N46" s="3">
-        <v>7.3822409000000005E-2</v>
+        <v>7.1946762999999997E-2</v>
       </c>
       <c r="O46" s="3">
-        <v>7.3630102000000003E-2</v>
+        <v>7.2069384E-2</v>
       </c>
       <c r="P46" s="3">
-        <v>7.3788062000000001E-2</v>
+        <v>7.3216870000000003E-2</v>
       </c>
       <c r="Q46" s="3">
-        <v>7.3336445E-2</v>
+        <v>7.2059235999999999E-2</v>
       </c>
       <c r="R46" s="3">
-        <v>7.3570370999999996E-2</v>
+        <v>7.2695039000000003E-2</v>
       </c>
       <c r="S46" s="3">
-        <v>7.3163575999999994E-2</v>
+        <v>7.2240911000000005E-2</v>
       </c>
       <c r="T46" s="3">
-        <v>7.3288045999999996E-2</v>
+        <v>7.2916083000000007E-2</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -3052,28 +3061,28 @@
         <v>8</v>
       </c>
       <c r="M47" s="3">
-        <v>7.0452951E-2</v>
+        <v>7.0239446999999997E-2</v>
       </c>
       <c r="N47" s="3">
-        <v>7.1054018999999996E-2</v>
+        <v>6.8778678999999995E-2</v>
       </c>
       <c r="O47" s="3">
-        <v>7.0731550000000004E-2</v>
+        <v>6.9237999999999994E-2</v>
       </c>
       <c r="P47" s="3">
-        <v>7.1036756000000006E-2</v>
+        <v>7.0637718000000002E-2</v>
       </c>
       <c r="Q47" s="3">
-        <v>7.0240363E-2</v>
+        <v>6.9006965000000003E-2</v>
       </c>
       <c r="R47" s="3">
-        <v>7.0420838999999999E-2</v>
+        <v>6.9739640000000006E-2</v>
       </c>
       <c r="S47" s="3">
-        <v>7.0151231999999994E-2</v>
+        <v>6.9361254999999997E-2</v>
       </c>
       <c r="T47" s="3">
-        <v>7.0192254999999995E-2</v>
+        <v>7.0175751999999994E-2</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -3082,321 +3091,515 @@
       </c>
       <c r="B48" s="1">
         <f t="shared" ref="B48:I55" si="13">M25</f>
-        <v>9.1777060000000008E-3</v>
+        <v>9.7773419999999996E-3</v>
       </c>
       <c r="C48" s="1">
         <f t="shared" si="13"/>
-        <v>9.171383E-3</v>
+        <v>9.7637880000000007E-3</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" si="13"/>
-        <v>9.0899499999999994E-3</v>
+        <v>9.8411220000000008E-3</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="13"/>
-        <v>9.233069E-3</v>
+        <v>9.8550749999999996E-3</v>
       </c>
       <c r="F48" s="1">
         <f t="shared" si="13"/>
-        <v>9.1374620000000007E-3</v>
+        <v>9.7710999999999996E-3</v>
       </c>
       <c r="G48" s="1">
         <f t="shared" si="13"/>
-        <v>9.1664499999999996E-3</v>
+        <v>9.8427540000000004E-3</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="13"/>
-        <v>9.0865879999999996E-3</v>
+        <v>9.8370479999999993E-3</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="13"/>
-        <v>9.1434689999999996E-3</v>
+        <v>9.7172249999999995E-3</v>
       </c>
       <c r="M48" s="3">
-        <v>5.7374074999999997E-2</v>
+        <v>5.7371872999999997E-2</v>
       </c>
       <c r="N48" s="3">
-        <v>5.8583143999999997E-2</v>
+        <v>5.6134224000000003E-2</v>
       </c>
       <c r="O48" s="3">
-        <v>5.8242376999999998E-2</v>
+        <v>5.6891110000000002E-2</v>
       </c>
       <c r="P48" s="3">
-        <v>5.8739059000000003E-2</v>
+        <v>5.8820426000000002E-2</v>
       </c>
       <c r="Q48" s="3">
-        <v>5.7329547000000002E-2</v>
+        <v>5.6537110000000002E-2</v>
       </c>
       <c r="R48" s="3">
-        <v>5.7384297000000001E-2</v>
+        <v>5.7187389999999998E-2</v>
       </c>
       <c r="S48" s="3">
-        <v>5.7602301000000002E-2</v>
+        <v>5.7378247E-2</v>
       </c>
       <c r="T48" s="3">
-        <v>5.7346570999999999E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.8160684999999997E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>60</v>
       </c>
       <c r="B49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3138046E-2</v>
+        <v>1.3472259E-2</v>
       </c>
       <c r="C49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3071134E-2</v>
+        <v>1.3613867999999999E-2</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3018643999999999E-2</v>
+        <v>1.3554066E-2</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3143881E-2</v>
+        <v>1.3572486999999999E-2</v>
       </c>
       <c r="F49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3078963000000001E-2</v>
+        <v>1.3506873000000001E-2</v>
       </c>
       <c r="G49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3086079E-2</v>
+        <v>1.3530873000000001E-2</v>
       </c>
       <c r="H49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3111291000000001E-2</v>
+        <v>1.3602635E-2</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3109829999999999E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.3586007000000001E-2</v>
+      </c>
+      <c r="M49" s="6">
+        <v>1.5458105999999999E-2</v>
+      </c>
+      <c r="N49" s="6">
+        <v>1.518369E-2</v>
+      </c>
+      <c r="O49" s="6">
+        <v>1.5167762E-2</v>
+      </c>
+      <c r="P49" s="6">
+        <v>1.5258224000000001E-2</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>1.522163E-2</v>
+      </c>
+      <c r="R49" s="6">
+        <v>1.5264764E-2</v>
+      </c>
+      <c r="S49" s="6">
+        <v>1.5151697E-2</v>
+      </c>
+      <c r="T49" s="6">
+        <v>1.5213450999999999E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>70</v>
       </c>
       <c r="B50" s="1">
         <f t="shared" si="13"/>
-        <v>1.454047E-2</v>
+        <v>1.4641395E-2</v>
       </c>
       <c r="C50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4450714E-2</v>
+        <v>1.4792606999999999E-2</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4421216000000001E-2</v>
+        <v>1.4695919E-2</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4511537E-2</v>
+        <v>1.4671152E-2</v>
       </c>
       <c r="F50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4477686E-2</v>
+        <v>1.4683015000000001E-2</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4489207E-2</v>
+        <v>1.466275E-2</v>
       </c>
       <c r="H50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4532478E-2</v>
+        <v>1.47735E-2</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4524854E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.4697029E-2</v>
+      </c>
+      <c r="M50" s="6">
+        <v>1.5376584E-2</v>
+      </c>
+      <c r="N50" s="6">
+        <v>1.5061064000000001E-2</v>
+      </c>
+      <c r="O50" s="6">
+        <v>1.5079922000000001E-2</v>
+      </c>
+      <c r="P50" s="6">
+        <v>1.5188978000000001E-2</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>1.5093535999999999E-2</v>
+      </c>
+      <c r="R50" s="6">
+        <v>1.5197492999999999E-2</v>
+      </c>
+      <c r="S50" s="6">
+        <v>1.5047131E-2</v>
+      </c>
+      <c r="T50" s="6">
+        <v>1.5096561999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>100</v>
       </c>
       <c r="B51" s="1">
         <f t="shared" si="13"/>
-        <v>1.5011606E-2</v>
+        <v>1.4925163999999999E-2</v>
       </c>
       <c r="C51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4909253000000001E-2</v>
+        <v>1.490814E-2</v>
       </c>
       <c r="D51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4900296E-2</v>
+        <v>1.4847898999999999E-2</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4952145999999999E-2</v>
+        <v>1.4876749999999999E-2</v>
       </c>
       <c r="F51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4922763E-2</v>
+        <v>1.4882256E-2</v>
       </c>
       <c r="G51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4968993E-2</v>
+        <v>1.4855302000000001E-2</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4927147999999999E-2</v>
+        <v>1.4888268E-2</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4981971E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.4903115E-2</v>
+      </c>
+      <c r="M51" s="6">
+        <v>1.5368214999999999E-2</v>
+      </c>
+      <c r="N51" s="6">
+        <v>1.508789E-2</v>
+      </c>
+      <c r="O51" s="6">
+        <v>1.5111299E-2</v>
+      </c>
+      <c r="P51" s="6">
+        <v>1.5212384000000001E-2</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>1.5112672000000001E-2</v>
+      </c>
+      <c r="R51" s="6">
+        <v>1.5215317000000001E-2</v>
+      </c>
+      <c r="S51" s="6">
+        <v>1.5086145E-2</v>
+      </c>
+      <c r="T51" s="6">
+        <v>1.5120635E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>140</v>
       </c>
       <c r="B52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4851836E-2</v>
+        <v>1.4766206E-2</v>
       </c>
       <c r="C52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4793120999999999E-2</v>
+        <v>1.4670516E-2</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4760192E-2</v>
+        <v>1.4656508E-2</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4817568E-2</v>
+        <v>1.4688618000000001E-2</v>
       </c>
       <c r="F52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4763116E-2</v>
+        <v>1.4647568E-2</v>
       </c>
       <c r="G52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4817163E-2</v>
+        <v>1.4706597E-2</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4719731E-2</v>
+        <v>1.4677529E-2</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4800363E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.4668687E-2</v>
+      </c>
+      <c r="M52" s="6">
+        <v>1.5399909E-2</v>
+      </c>
+      <c r="N52" s="6">
+        <v>1.5244442E-2</v>
+      </c>
+      <c r="O52" s="6">
+        <v>1.5247925000000001E-2</v>
+      </c>
+      <c r="P52" s="6">
+        <v>1.5319309999999999E-2</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>1.524943E-2</v>
+      </c>
+      <c r="R52" s="6">
+        <v>1.5309053E-2</v>
+      </c>
+      <c r="S52" s="6">
+        <v>1.5255037000000001E-2</v>
+      </c>
+      <c r="T52" s="6">
+        <v>1.5268432E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>180</v>
       </c>
       <c r="B53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4627967E-2</v>
+        <v>1.4539389999999999E-2</v>
       </c>
       <c r="C53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4622161E-2</v>
+        <v>1.4393131E-2</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4561447999999999E-2</v>
+        <v>1.4454369E-2</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4641372E-2</v>
+        <v>1.4580408E-2</v>
       </c>
       <c r="F53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4519815E-2</v>
+        <v>1.4406587E-2</v>
       </c>
       <c r="G53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4588353E-2</v>
+        <v>1.451565E-2</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="13"/>
-        <v>1.448259E-2</v>
+        <v>1.4451637999999999E-2</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4555444000000001E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.4554111999999999E-2</v>
+      </c>
+      <c r="M53" s="6">
+        <v>1.5408434E-2</v>
+      </c>
+      <c r="N53" s="6">
+        <v>1.5317936000000001E-2</v>
+      </c>
+      <c r="O53" s="6">
+        <v>1.5318429E-2</v>
+      </c>
+      <c r="P53" s="6">
+        <v>1.5362005E-2</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>1.5319121999999999E-2</v>
+      </c>
+      <c r="R53" s="6">
+        <v>1.5354639999999999E-2</v>
+      </c>
+      <c r="S53" s="6">
+        <v>1.5335807999999999E-2</v>
+      </c>
+      <c r="T53" s="6">
+        <v>1.534428E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>210</v>
       </c>
       <c r="B54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3947795000000001E-2</v>
+        <v>1.3876416000000001E-2</v>
       </c>
       <c r="C54" s="1">
         <f t="shared" si="13"/>
-        <v>1.4004518000000001E-2</v>
+        <v>1.3730727999999999E-2</v>
       </c>
       <c r="D54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3934732999999999E-2</v>
+        <v>1.378098E-2</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="13"/>
-        <v>1.4033811E-2</v>
+        <v>1.404476E-2</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="13"/>
-        <v>1.38382E-2</v>
+        <v>1.3730674E-2</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3909871000000001E-2</v>
+        <v>1.3871333E-2</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3834123E-2</v>
+        <v>1.384909E-2</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="13"/>
-        <v>1.387715E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.3953897999999999E-2</v>
+      </c>
+      <c r="M54" s="6">
+        <v>1.5420224E-2</v>
+      </c>
+      <c r="N54" s="6">
+        <v>1.5356537999999999E-2</v>
+      </c>
+      <c r="O54" s="6">
+        <v>1.5353924E-2</v>
+      </c>
+      <c r="P54" s="6">
+        <v>1.5384284999999999E-2</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>1.5356013999999999E-2</v>
+      </c>
+      <c r="R54" s="6">
+        <v>1.5376562999999999E-2</v>
+      </c>
+      <c r="S54" s="6">
+        <v>1.5371108E-2</v>
+      </c>
+      <c r="T54" s="6">
+        <v>1.5375493E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>250</v>
       </c>
       <c r="B55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1283257999999999E-2</v>
+        <v>1.127977E-2</v>
       </c>
       <c r="C55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1460112E-2</v>
+        <v>1.1121809E-2</v>
       </c>
       <c r="D55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1402773E-2</v>
+        <v>1.1278541E-2</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1532779999999999E-2</v>
+        <v>1.1598567000000001E-2</v>
       </c>
       <c r="F55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1205911000000001E-2</v>
+        <v>1.12041E-2</v>
       </c>
       <c r="G55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1256657999999999E-2</v>
+        <v>1.1327940999999999E-2</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1291907E-2</v>
+        <v>1.1388987E-2</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1257814E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1.1515795000000001E-2</v>
+      </c>
+      <c r="M55" s="6">
+        <v>1.5419894999999999E-2</v>
+      </c>
+      <c r="N55" s="6">
+        <v>1.5366869999999999E-2</v>
+      </c>
+      <c r="O55" s="6">
+        <v>1.5362082000000001E-2</v>
+      </c>
+      <c r="P55" s="6">
+        <v>1.5388957E-2</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>1.5367093E-2</v>
+      </c>
+      <c r="R55" s="6">
+        <v>1.5391864E-2</v>
+      </c>
+      <c r="S55" s="6">
+        <v>1.5381381E-2</v>
+      </c>
+      <c r="T55" s="6">
+        <v>1.5389238E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M56" s="6">
+        <v>1.5434586E-2</v>
+      </c>
+      <c r="N56" s="6">
+        <v>1.5390067E-2</v>
+      </c>
+      <c r="O56" s="6">
+        <v>1.5389442999999999E-2</v>
+      </c>
+      <c r="P56" s="6">
+        <v>1.5407472E-2</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>1.5389874E-2</v>
+      </c>
+      <c r="R56" s="6">
+        <v>1.5408707000000001E-2</v>
+      </c>
+      <c r="S56" s="6">
+        <v>1.5404196E-2</v>
+      </c>
+      <c r="T56" s="6">
+        <v>1.5411829E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>7</v>
       </c>
@@ -3408,8 +3611,32 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M57" s="6">
+        <v>4.9540217999999997E-2</v>
+      </c>
+      <c r="N57" s="6">
+        <v>4.9637806E-2</v>
+      </c>
+      <c r="O57" s="6">
+        <v>4.9648370999999997E-2</v>
+      </c>
+      <c r="P57" s="6">
+        <v>4.9901268999999998E-2</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>4.9295380999999999E-2</v>
+      </c>
+      <c r="R57" s="6">
+        <v>4.9923967999999999E-2</v>
+      </c>
+      <c r="S57" s="6">
+        <v>4.9807835000000002E-2</v>
+      </c>
+      <c r="T57" s="6">
+        <v>4.9401298000000003E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -3437,119 +3664,215 @@
       <c r="I58">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M58" s="6">
+        <v>6.8212852000000004E-2</v>
+      </c>
+      <c r="N58" s="6">
+        <v>6.8477012000000004E-2</v>
+      </c>
+      <c r="O58" s="6">
+        <v>6.8461551999999995E-2</v>
+      </c>
+      <c r="P58" s="6">
+        <v>6.8622321E-2</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>6.8436555999999996E-2</v>
+      </c>
+      <c r="R58" s="6">
+        <v>6.8514145999999998E-2</v>
+      </c>
+      <c r="S58" s="6">
+        <v>6.8813345999999997E-2</v>
+      </c>
+      <c r="T58" s="6">
+        <v>6.8445474000000006E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>50</v>
       </c>
       <c r="B59" s="2">
         <f>20*LOG(((B48)*B$40)/(B37*(B$51)), 10)</f>
-        <v>-4.2654968799696338</v>
+        <v>-3.6980910216122687</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59:I59" si="14">20*LOG(((C48)*C$40)/(C37*(C$51)), 10)</f>
-        <v>-4.2098289290829154</v>
+        <v>-3.63317767823062</v>
       </c>
       <c r="D59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.2990370493015977</v>
+        <v>-3.5195624603742126</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.1710421143814145</v>
+        <v>-3.5309827804767608</v>
       </c>
       <c r="F59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.2624484300838459</v>
+        <v>-3.633921722954903</v>
       </c>
       <c r="G59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.2606664242852208</v>
+        <v>-3.5398928249956256</v>
       </c>
       <c r="H59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.300207043987271</v>
+        <v>-3.5366956739335449</v>
       </c>
       <c r="I59" s="2">
         <f t="shared" si="14"/>
-        <v>-4.2885733226482001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-3.671521371546814</v>
+      </c>
+      <c r="M59" s="6">
+        <v>7.3851809000000004E-2</v>
+      </c>
+      <c r="N59" s="6">
+        <v>7.4448108999999998E-2</v>
+      </c>
+      <c r="O59" s="6">
+        <v>7.4213736000000002E-2</v>
+      </c>
+      <c r="P59" s="6">
+        <v>7.4221156999999996E-2</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>7.4111752000000003E-2</v>
+      </c>
+      <c r="R59" s="6">
+        <v>7.4011266000000006E-2</v>
+      </c>
+      <c r="S59" s="6">
+        <v>7.4454658000000007E-2</v>
+      </c>
+      <c r="T59" s="6">
+        <v>7.4084647000000003E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>60</v>
       </c>
       <c r="B60" s="2">
         <f t="shared" ref="B60:I60" si="15">20*LOG(((B49)*B$40)/(B38*(B$51)), 10)</f>
-        <v>-1.1119149352399647</v>
+        <v>-0.87282327528582226</v>
       </c>
       <c r="C60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.105752609042755</v>
+        <v>-0.67677627859035083</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.1377990636925017</v>
+        <v>-0.69172653744626644</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.0786817421153898</v>
+        <v>-0.71513099401081859</v>
       </c>
       <c r="F60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.1048898295484253</v>
+        <v>-0.75046817098444873</v>
       </c>
       <c r="G60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.1341674341296986</v>
+        <v>-0.73822839058796452</v>
       </c>
       <c r="H60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.0499425195161873</v>
+        <v>-0.6619587533027198</v>
       </c>
       <c r="I60" s="2">
         <f t="shared" si="15"/>
-        <v>-1.1127070958342009</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-0.69636753728764456</v>
+      </c>
+      <c r="M60" s="6">
+        <v>7.4848792999999997E-2</v>
+      </c>
+      <c r="N60" s="6">
+        <v>7.5100801999999994E-2</v>
+      </c>
+      <c r="O60" s="6">
+        <v>7.4987634999999997E-2</v>
+      </c>
+      <c r="P60" s="6">
+        <v>7.4915684999999996E-2</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>7.5086242999999997E-2</v>
+      </c>
+      <c r="R60" s="6">
+        <v>7.4831612000000006E-2</v>
+      </c>
+      <c r="S60" s="6">
+        <v>7.4999629999999998E-2</v>
+      </c>
+      <c r="T60" s="6">
+        <v>7.4865936999999994E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>70</v>
       </c>
       <c r="B61" s="2">
         <f t="shared" ref="B61:I61" si="16">20*LOG(((B50)*B$40)/(B39*(B$51)), 10)</f>
-        <v>-0.23647237571139026</v>
+        <v>-0.14575434314041386</v>
       </c>
       <c r="C61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.24126571118478349</v>
+        <v>2.512237507926917E-2</v>
       </c>
       <c r="D61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.25093578433764785</v>
+        <v>-6.4822553784038136E-3</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.22908194301156495</v>
+        <v>-5.7607709160747714E-2</v>
       </c>
       <c r="F61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.22617467266786442</v>
+        <v>-3.5284512205711716E-2</v>
       </c>
       <c r="G61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.25380803980157118</v>
+        <v>-5.4569283709857502E-2</v>
       </c>
       <c r="H61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.16327999679422434</v>
+        <v>3.239212937290132E-2</v>
       </c>
       <c r="I61" s="2">
         <f t="shared" si="16"/>
-        <v>-0.22396433028092649</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-2.8376748792804329E-2</v>
+      </c>
+      <c r="M61" s="6">
+        <v>7.4073501E-2</v>
+      </c>
+      <c r="N61" s="6">
+        <v>7.3739886000000004E-2</v>
+      </c>
+      <c r="O61" s="6">
+        <v>7.3732017999999996E-2</v>
+      </c>
+      <c r="P61" s="6">
+        <v>7.4109419999999995E-2</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>7.3733293000000005E-2</v>
+      </c>
+      <c r="R61" s="6">
+        <v>7.3868430999999998E-2</v>
+      </c>
+      <c r="S61" s="6">
+        <v>7.3617630000000003E-2</v>
+      </c>
+      <c r="T61" s="6">
+        <v>7.3978594999999994E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>100</v>
       </c>
@@ -3585,79 +3908,151 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M62" s="6">
+        <v>7.2855771E-2</v>
+      </c>
+      <c r="N62" s="6">
+        <v>7.2293072999999999E-2</v>
+      </c>
+      <c r="O62" s="6">
+        <v>7.2535679000000006E-2</v>
+      </c>
+      <c r="P62" s="6">
+        <v>7.3320642000000005E-2</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>7.2364739999999997E-2</v>
+      </c>
+      <c r="R62" s="6">
+        <v>7.2964914000000006E-2</v>
+      </c>
+      <c r="S62" s="6">
+        <v>7.2494417000000005E-2</v>
+      </c>
+      <c r="T62" s="6">
+        <v>7.2973556999999994E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>140</v>
       </c>
       <c r="B63" s="2">
         <f t="shared" ref="B63:I63" si="18">20*LOG(((B52)*B$40)/(B41*(B$51)), 10)</f>
-        <v>-0.11423817956787033</v>
+        <v>-9.9562315739595564E-2</v>
       </c>
       <c r="C63" s="2">
         <f t="shared" si="18"/>
-        <v>-8.0840502263680572E-2</v>
+        <v>-0.18454717784804869</v>
       </c>
       <c r="D63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.10521623704753053</v>
+        <v>-0.1534965621188156</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="18"/>
-        <v>-9.2015813337581354E-2</v>
+        <v>-0.1353656948555827</v>
       </c>
       <c r="F63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.11252491312416757</v>
+        <v>-0.18172670764775553</v>
       </c>
       <c r="G63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.10363807857629201</v>
+        <v>-0.11353588996866029</v>
       </c>
       <c r="H63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.1593077862742352</v>
+        <v>-0.17181649762953038</v>
       </c>
       <c r="I63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.13285203310628235</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-0.18162702287941113</v>
+      </c>
+      <c r="M63" s="6">
+        <v>6.9480291999999999E-2</v>
+      </c>
+      <c r="N63" s="6">
+        <v>6.8796702000000001E-2</v>
+      </c>
+      <c r="O63" s="6">
+        <v>6.9327644999999993E-2</v>
+      </c>
+      <c r="P63" s="6">
+        <v>7.0328526000000002E-2</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>6.9095232000000006E-2</v>
+      </c>
+      <c r="R63" s="6">
+        <v>6.9613330000000001E-2</v>
+      </c>
+      <c r="S63" s="6">
+        <v>6.9358185000000003E-2</v>
+      </c>
+      <c r="T63" s="6">
+        <v>6.9980472000000002E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>180</v>
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64:I64" si="19">20*LOG(((B53)*B$40)/(B42*(B$51)), 10)</f>
-        <v>-0.25803532867222251</v>
+        <v>-0.23897968394121738</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.19137929152437383</v>
+        <v>-0.36893275645620427</v>
       </c>
       <c r="D64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.23729402614241527</v>
+        <v>-0.29287159892476944</v>
       </c>
       <c r="E64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.20590619632505355</v>
+        <v>-0.20952117793528841</v>
       </c>
       <c r="F64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.26993231353223779</v>
+        <v>-0.34395378368504392</v>
       </c>
       <c r="G64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.25026570636793816</v>
+        <v>-0.24082724378657663</v>
       </c>
       <c r="H64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.32022405779744989</v>
+        <v>-0.32744078021360401</v>
       </c>
       <c r="I64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.29503771900938008</v>
+        <v>-0.26787828323755325</v>
+      </c>
+      <c r="M64" s="6">
+        <v>5.6386000999999998E-2</v>
+      </c>
+      <c r="N64" s="6">
+        <v>5.5701266999999999E-2</v>
+      </c>
+      <c r="O64" s="6">
+        <v>5.6465998000000003E-2</v>
+      </c>
+      <c r="P64" s="6">
+        <v>5.8106456000000001E-2</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>5.6130592E-2</v>
+      </c>
+      <c r="R64" s="6">
+        <v>5.6656115E-2</v>
+      </c>
+      <c r="S64" s="6">
+        <v>5.6843578999999998E-2</v>
+      </c>
+      <c r="T64" s="6">
+        <v>5.7500194999999997E-2</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -3666,35 +4061,35 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65:I65" si="20">20*LOG(((B54)*B$40)/(B43*(B$51)), 10)</f>
-        <v>-0.68144473517418902</v>
+        <v>-0.64430317265970904</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.57439395007896776</v>
+        <v>-0.78508307491504226</v>
       </c>
       <c r="D65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.63100691296028044</v>
+        <v>-0.71671339726616667</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.58368694257675002</v>
+        <v>-0.54055732631082476</v>
       </c>
       <c r="F65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.69691791130587344</v>
+        <v>-0.77007357042859015</v>
       </c>
       <c r="G65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.67436919646040028</v>
+        <v>-0.64212423593933909</v>
       </c>
       <c r="H65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.72976638587884768</v>
+        <v>-0.70392426653946005</v>
       </c>
       <c r="I65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.72367664473947479</v>
+        <v>-0.64104548330058131</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3703,35 +4098,35 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66:I66" si="21">20*LOG(((B55)*B$40)/(B44*(B$51)), 10)</f>
-        <v>-2.5377749675011021</v>
+        <v>-2.4530312874357705</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.3300620378644945</v>
+        <v>-2.6296259747106059</v>
       </c>
       <c r="D66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.3846333776682389</v>
+        <v>-2.4697402322349356</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.3024046549445085</v>
+        <v>-2.2124828821942129</v>
       </c>
       <c r="F66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.5443833683513462</v>
+        <v>-2.5496663206052301</v>
       </c>
       <c r="G66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.5247765560818278</v>
+        <v>-2.4115349555571464</v>
       </c>
       <c r="H66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.508879826380837</v>
+        <v>-2.4168879619286261</v>
       </c>
       <c r="I66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.5555299646883531</v>
+        <v>-2.3208882225237479</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -3782,35 +4177,35 @@
       </c>
       <c r="B70" s="1">
         <f>M33</f>
-        <v>1.5380922E-2</v>
+        <v>1.5456351E-2</v>
       </c>
       <c r="C70" s="1">
         <f t="shared" ref="C70:I70" si="22">N33</f>
-        <v>1.5383163E-2</v>
+        <v>1.5186470000000001E-2</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="22"/>
-        <v>1.539715E-2</v>
+        <v>1.5170253E-2</v>
       </c>
       <c r="E70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5370943999999999E-2</v>
+        <v>1.5258571E-2</v>
       </c>
       <c r="F70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5370253E-2</v>
+        <v>1.5220925E-2</v>
       </c>
       <c r="G70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5403902000000001E-2</v>
+        <v>1.5265224000000001E-2</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5296475E-2</v>
+        <v>1.5154994999999999E-2</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5350206999999999E-2</v>
+        <v>1.5214017999999999E-2</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -3819,35 +4214,35 @@
       </c>
       <c r="B71" s="1">
         <f t="shared" ref="B71:B77" si="23">M34</f>
-        <v>1.5313413E-2</v>
+        <v>1.5379199E-2</v>
       </c>
       <c r="C71" s="1">
         <f t="shared" ref="C71:C77" si="24">N34</f>
-        <v>1.5338276E-2</v>
+        <v>1.5056742E-2</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" ref="D71:D77" si="25">O34</f>
-        <v>1.5325737000000001E-2</v>
+        <v>1.5084901E-2</v>
       </c>
       <c r="E71" s="1">
         <f t="shared" ref="E71:E77" si="26">P34</f>
-        <v>1.5325640999999999E-2</v>
+        <v>1.5190164000000001E-2</v>
       </c>
       <c r="F71" s="1">
         <f t="shared" ref="F71:F77" si="27">Q34</f>
-        <v>1.5296034E-2</v>
+        <v>1.5094196000000001E-2</v>
       </c>
       <c r="G71" s="1">
         <f t="shared" ref="G71:G77" si="28">R34</f>
-        <v>1.5345457999999999E-2</v>
+        <v>1.5195800000000001E-2</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" ref="H71:H77" si="29">S34</f>
-        <v>1.5182747999999999E-2</v>
+        <v>1.504753E-2</v>
       </c>
       <c r="I71" s="1">
         <f t="shared" ref="I71:I77" si="30">T34</f>
-        <v>1.5267711999999999E-2</v>
+        <v>1.5094394000000001E-2</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -3856,35 +4251,35 @@
       </c>
       <c r="B72" s="1">
         <f t="shared" si="23"/>
-        <v>1.5326503E-2</v>
+        <v>1.5373443000000001E-2</v>
       </c>
       <c r="C72" s="1">
         <f t="shared" si="24"/>
-        <v>1.5348766E-2</v>
+        <v>1.5092080000000001E-2</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="25"/>
-        <v>1.5326907000000001E-2</v>
+        <v>1.5114818E-2</v>
       </c>
       <c r="E72" s="1">
         <f t="shared" si="26"/>
-        <v>1.5345444999999999E-2</v>
+        <v>1.5218784000000001E-2</v>
       </c>
       <c r="F72" s="1">
         <f t="shared" si="27"/>
-        <v>1.5301830000000001E-2</v>
+        <v>1.5115544E-2</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="28"/>
-        <v>1.5350822E-2</v>
+        <v>1.5218046000000001E-2</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="29"/>
-        <v>1.5191023999999999E-2</v>
+        <v>1.5087816E-2</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="30"/>
-        <v>1.5273738E-2</v>
+        <v>1.5121875E-2</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -3893,35 +4288,35 @@
       </c>
       <c r="B73" s="1">
         <f t="shared" si="23"/>
-        <v>1.5392706000000001E-2</v>
+        <v>1.5406510999999999E-2</v>
       </c>
       <c r="C73" s="1">
         <f t="shared" si="24"/>
-        <v>1.5397447999999999E-2</v>
+        <v>1.5250400000000001E-2</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="25"/>
-        <v>1.5381127E-2</v>
+        <v>1.5250825000000001E-2</v>
       </c>
       <c r="E73" s="1">
         <f t="shared" si="26"/>
-        <v>1.539577E-2</v>
+        <v>1.5326559E-2</v>
       </c>
       <c r="F73" s="1">
         <f t="shared" si="27"/>
-        <v>1.5362136E-2</v>
+        <v>1.5252496000000001E-2</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="28"/>
-        <v>1.5398012000000001E-2</v>
+        <v>1.5317608E-2</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="29"/>
-        <v>1.5310169E-2</v>
+        <v>1.5258776E-2</v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="30"/>
-        <v>1.5349612E-2</v>
+        <v>1.5274411E-2</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3930,35 +4325,35 @@
       </c>
       <c r="B74" s="1">
         <f t="shared" si="23"/>
-        <v>1.5429739E-2</v>
+        <v>1.5417923E-2</v>
       </c>
       <c r="C74" s="1">
         <f t="shared" si="24"/>
-        <v>1.5421574E-2</v>
+        <v>1.5326576999999999E-2</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="25"/>
-        <v>1.5421126E-2</v>
+        <v>1.5325893E-2</v>
       </c>
       <c r="E74" s="1">
         <f t="shared" si="26"/>
-        <v>1.5419791E-2</v>
+        <v>1.5367877E-2</v>
       </c>
       <c r="F74" s="1">
         <f t="shared" si="27"/>
-        <v>1.5398075000000001E-2</v>
+        <v>1.5325834E-2</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="28"/>
-        <v>1.5423998E-2</v>
+        <v>1.5358261E-2</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="29"/>
-        <v>1.5375206000000001E-2</v>
+        <v>1.5337750000000001E-2</v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="30"/>
-        <v>1.5397058E-2</v>
+        <v>1.5349091E-2</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3967,35 +4362,35 @@
       </c>
       <c r="B75" s="1">
         <f t="shared" si="23"/>
-        <v>1.5449902E-2</v>
+        <v>1.5422623999999999E-2</v>
       </c>
       <c r="C75" s="1">
         <f t="shared" si="24"/>
-        <v>1.5437565E-2</v>
+        <v>1.5359256999999999E-2</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" si="25"/>
-        <v>1.5448257E-2</v>
+        <v>1.5359533E-2</v>
       </c>
       <c r="E75" s="1">
         <f t="shared" si="26"/>
-        <v>1.5439754999999999E-2</v>
+        <v>1.5389976E-2</v>
       </c>
       <c r="F75" s="1">
         <f t="shared" si="27"/>
-        <v>1.5422119E-2</v>
+        <v>1.5360478E-2</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="28"/>
-        <v>1.5447664E-2</v>
+        <v>1.5382511E-2</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="29"/>
-        <v>1.5410841E-2</v>
+        <v>1.5375088E-2</v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="30"/>
-        <v>1.5427445E-2</v>
+        <v>1.5383152000000001E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -4004,35 +4399,35 @@
       </c>
       <c r="B76" s="1">
         <f t="shared" si="23"/>
-        <v>1.5468647E-2</v>
+        <v>1.5426034999999999E-2</v>
       </c>
       <c r="C76" s="1">
         <f t="shared" si="24"/>
-        <v>1.5454557000000001E-2</v>
+        <v>1.5373392E-2</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="25"/>
-        <v>1.5464772E-2</v>
+        <v>1.5372200000000001E-2</v>
       </c>
       <c r="E76" s="1">
         <f t="shared" si="26"/>
-        <v>1.5451281000000001E-2</v>
+        <v>1.5396236000000001E-2</v>
       </c>
       <c r="F76" s="1">
         <f t="shared" si="27"/>
-        <v>1.5439167E-2</v>
+        <v>1.5369041999999999E-2</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="28"/>
-        <v>1.5462383999999999E-2</v>
+        <v>1.5391066E-2</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="29"/>
-        <v>1.5435552999999999E-2</v>
+        <v>1.5389130000000001E-2</v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="30"/>
-        <v>1.5447021999999999E-2</v>
+        <v>1.5398926E-2</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -4041,35 +4436,35 @@
       </c>
       <c r="B77" s="1">
         <f t="shared" si="23"/>
-        <v>1.5492574E-2</v>
+        <v>1.5442566E-2</v>
       </c>
       <c r="C77" s="1">
         <f t="shared" si="24"/>
-        <v>1.5474836E-2</v>
+        <v>1.5396356E-2</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="25"/>
-        <v>1.5491540999999999E-2</v>
+        <v>1.5397286E-2</v>
       </c>
       <c r="E77" s="1">
         <f t="shared" si="26"/>
-        <v>1.5473674999999999E-2</v>
+        <v>1.5415491999999999E-2</v>
       </c>
       <c r="F77" s="1">
         <f t="shared" si="27"/>
-        <v>1.5459815999999999E-2</v>
+        <v>1.5393258999999999E-2</v>
       </c>
       <c r="G77" s="1">
         <f t="shared" si="28"/>
-        <v>1.5482315E-2</v>
+        <v>1.5412945000000001E-2</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="29"/>
-        <v>1.545941E-2</v>
+        <v>1.5411213999999999E-2</v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="30"/>
-        <v>1.547053E-2</v>
+        <v>1.5420672E-2</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -4120,35 +4515,35 @@
       </c>
       <c r="B81" s="1">
         <f>M41</f>
-        <v>4.5960542E-2</v>
+        <v>4.8893674999999998E-2</v>
       </c>
       <c r="C81" s="1">
         <f t="shared" ref="C81:I81" si="31">N41</f>
-        <v>4.5977580999999997E-2</v>
+        <v>4.8400595999999997E-2</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="31"/>
-        <v>4.5643758E-2</v>
+        <v>4.8553981000000003E-2</v>
       </c>
       <c r="E81" s="1">
         <f t="shared" si="31"/>
-        <v>4.6246134000000001E-2</v>
+        <v>4.8901728999999998E-2</v>
       </c>
       <c r="F81" s="1">
         <f t="shared" si="31"/>
-        <v>4.5710128000000003E-2</v>
+        <v>4.8554952999999998E-2</v>
       </c>
       <c r="G81" s="1">
         <f t="shared" si="31"/>
-        <v>4.5984231E-2</v>
+        <v>4.8802707000000001E-2</v>
       </c>
       <c r="H81" s="1">
         <f t="shared" si="31"/>
-        <v>4.5665773999999999E-2</v>
+        <v>4.8563343000000002E-2</v>
       </c>
       <c r="I81" s="1">
         <f t="shared" si="31"/>
-        <v>4.5674807999999997E-2</v>
+        <v>4.8299680999999997E-2</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -4157,35 +4552,35 @@
       </c>
       <c r="B82" s="1">
         <f t="shared" ref="B82:B88" si="32">M42</f>
-        <v>6.5592742999999995E-2</v>
+        <v>6.7720040999999995E-2</v>
       </c>
       <c r="C82" s="1">
         <f t="shared" ref="C82:C88" si="33">N42</f>
-        <v>6.5440811000000002E-2</v>
+        <v>6.7619525E-2</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" ref="D82:D88" si="34">O42</f>
-        <v>6.5263182000000003E-2</v>
+        <v>6.7129247000000003E-2</v>
       </c>
       <c r="E82" s="1">
         <f t="shared" ref="E82:E88" si="35">P42</f>
-        <v>6.5762229000000005E-2</v>
+        <v>6.7505783999999999E-2</v>
       </c>
       <c r="F82" s="1">
         <f t="shared" ref="F82:F88" si="36">Q42</f>
-        <v>6.5361470000000005E-2</v>
+        <v>6.7328595000000005E-2</v>
       </c>
       <c r="G82" s="1">
         <f t="shared" ref="G82:G88" si="37">R42</f>
-        <v>6.5536610999999995E-2</v>
+        <v>6.7247323999999997E-2</v>
       </c>
       <c r="H82" s="1">
         <f t="shared" ref="H82:H88" si="38">S42</f>
-        <v>6.5749921000000003E-2</v>
+        <v>6.7851111000000006E-2</v>
       </c>
       <c r="I82" s="1">
         <f t="shared" ref="I82:I88" si="39">T42</f>
-        <v>6.5409816999999995E-2</v>
+        <v>6.7479364999999999E-2</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -4194,35 +4589,35 @@
       </c>
       <c r="B83" s="1">
         <f t="shared" si="32"/>
-        <v>7.2610959000000003E-2</v>
+        <v>7.3252185999999997E-2</v>
       </c>
       <c r="C83" s="1">
         <f t="shared" si="33"/>
-        <v>7.2274594999999997E-2</v>
+        <v>7.3296040000000007E-2</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="34"/>
-        <v>7.2271787000000004E-2</v>
+        <v>7.2994805999999995E-2</v>
       </c>
       <c r="E83" s="1">
         <f t="shared" si="35"/>
-        <v>7.2546862000000004E-2</v>
+        <v>7.3272466999999994E-2</v>
       </c>
       <c r="F83" s="1">
         <f t="shared" si="36"/>
-        <v>7.2342478000000002E-2</v>
+        <v>7.2891787E-2</v>
       </c>
       <c r="G83" s="1">
         <f t="shared" si="37"/>
-        <v>7.2500274000000003E-2</v>
+        <v>7.2940654999999993E-2</v>
       </c>
       <c r="H83" s="1">
         <f t="shared" si="38"/>
-        <v>7.2896904999999998E-2</v>
+        <v>7.3257751999999995E-2</v>
       </c>
       <c r="I83" s="1">
         <f t="shared" si="39"/>
-        <v>7.2430580999999994E-2</v>
+        <v>7.3206119E-2</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -4231,35 +4626,35 @@
       </c>
       <c r="B84" s="1">
         <f t="shared" si="32"/>
-        <v>7.4945994000000002E-2</v>
+        <v>7.4525810999999997E-2</v>
       </c>
       <c r="C84" s="1">
         <f t="shared" si="33"/>
-        <v>7.4669205000000002E-2</v>
+        <v>7.3929942999999998E-2</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="34"/>
-        <v>7.4766494000000003E-2</v>
+        <v>7.3795400999999997E-2</v>
       </c>
       <c r="E84" s="1">
         <f t="shared" si="35"/>
-        <v>7.4819839999999999E-2</v>
+        <v>7.4281535999999995E-2</v>
       </c>
       <c r="F84" s="1">
         <f t="shared" si="36"/>
-        <v>7.4683114999999994E-2</v>
+        <v>7.3930033000000006E-2</v>
       </c>
       <c r="G84" s="1">
         <f t="shared" si="37"/>
-        <v>7.4932343999999998E-2</v>
+        <v>7.3860325000000004E-2</v>
       </c>
       <c r="H84" s="1">
         <f t="shared" si="38"/>
-        <v>7.4944884000000003E-2</v>
+        <v>7.3983974999999993E-2</v>
       </c>
       <c r="I84" s="1">
         <f t="shared" si="39"/>
-        <v>7.4783987999999996E-2</v>
+        <v>7.4154221000000006E-2</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -4268,35 +4663,35 @@
       </c>
       <c r="B85" s="1">
         <f t="shared" si="32"/>
-        <v>7.4408165999999998E-2</v>
+        <v>7.4060424999999999E-2</v>
       </c>
       <c r="C85" s="1">
         <f t="shared" si="33"/>
-        <v>7.4323311000000003E-2</v>
+        <v>7.2829335999999995E-2</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="34"/>
-        <v>7.4282467000000005E-2</v>
+        <v>7.2868265000000002E-2</v>
       </c>
       <c r="E85" s="1">
         <f t="shared" si="35"/>
-        <v>7.4351132E-2</v>
+        <v>7.3500827000000005E-2</v>
       </c>
       <c r="F85" s="1">
         <f t="shared" si="36"/>
-        <v>7.4117905999999997E-2</v>
+        <v>7.2823256000000003E-2</v>
       </c>
       <c r="G85" s="1">
         <f t="shared" si="37"/>
-        <v>7.4391946E-2</v>
+        <v>7.3190346000000003E-2</v>
       </c>
       <c r="H85" s="1">
         <f t="shared" si="38"/>
-        <v>7.4059725000000007E-2</v>
+        <v>7.2956398000000006E-2</v>
       </c>
       <c r="I85" s="1">
         <f t="shared" si="39"/>
-        <v>7.4131608000000002E-2</v>
+        <v>7.3363669000000006E-2</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -4305,35 +4700,35 @@
       </c>
       <c r="B86" s="1">
         <f t="shared" si="32"/>
-        <v>7.3590039999999995E-2</v>
+        <v>7.3310606E-2</v>
       </c>
       <c r="C86" s="1">
         <f t="shared" si="33"/>
-        <v>7.3822409000000005E-2</v>
+        <v>7.1946762999999997E-2</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="34"/>
-        <v>7.3630102000000003E-2</v>
+        <v>7.2069384E-2</v>
       </c>
       <c r="E86" s="1">
         <f t="shared" si="35"/>
-        <v>7.3788062000000001E-2</v>
+        <v>7.3216870000000003E-2</v>
       </c>
       <c r="F86" s="1">
         <f t="shared" si="36"/>
-        <v>7.3336445E-2</v>
+        <v>7.2059235999999999E-2</v>
       </c>
       <c r="G86" s="1">
         <f t="shared" si="37"/>
-        <v>7.3570370999999996E-2</v>
+        <v>7.2695039000000003E-2</v>
       </c>
       <c r="H86" s="1">
         <f t="shared" si="38"/>
-        <v>7.3163575999999994E-2</v>
+        <v>7.2240911000000005E-2</v>
       </c>
       <c r="I86" s="1">
         <f t="shared" si="39"/>
-        <v>7.3288045999999996E-2</v>
+        <v>7.2916083000000007E-2</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -4342,35 +4737,35 @@
       </c>
       <c r="B87" s="1">
         <f t="shared" si="32"/>
-        <v>7.0452951E-2</v>
+        <v>7.0239446999999997E-2</v>
       </c>
       <c r="C87" s="1">
         <f t="shared" si="33"/>
-        <v>7.1054018999999996E-2</v>
+        <v>6.8778678999999995E-2</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="34"/>
-        <v>7.0731550000000004E-2</v>
+        <v>6.9237999999999994E-2</v>
       </c>
       <c r="E87" s="1">
         <f t="shared" si="35"/>
-        <v>7.1036756000000006E-2</v>
+        <v>7.0637718000000002E-2</v>
       </c>
       <c r="F87" s="1">
         <f t="shared" si="36"/>
-        <v>7.0240363E-2</v>
+        <v>6.9006965000000003E-2</v>
       </c>
       <c r="G87" s="1">
         <f t="shared" si="37"/>
-        <v>7.0420838999999999E-2</v>
+        <v>6.9739640000000006E-2</v>
       </c>
       <c r="H87" s="1">
         <f t="shared" si="38"/>
-        <v>7.0151231999999994E-2</v>
+        <v>6.9361254999999997E-2</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="39"/>
-        <v>7.0192254999999995E-2</v>
+        <v>7.0175751999999994E-2</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -4379,35 +4774,35 @@
       </c>
       <c r="B88" s="1">
         <f t="shared" si="32"/>
-        <v>5.7374074999999997E-2</v>
+        <v>5.7371872999999997E-2</v>
       </c>
       <c r="C88" s="1">
         <f t="shared" si="33"/>
-        <v>5.8583143999999997E-2</v>
+        <v>5.6134224000000003E-2</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="34"/>
-        <v>5.8242376999999998E-2</v>
+        <v>5.6891110000000002E-2</v>
       </c>
       <c r="E88" s="1">
         <f t="shared" si="35"/>
-        <v>5.8739059000000003E-2</v>
+        <v>5.8820426000000002E-2</v>
       </c>
       <c r="F88" s="1">
         <f t="shared" si="36"/>
-        <v>5.7329547000000002E-2</v>
+        <v>5.6537110000000002E-2</v>
       </c>
       <c r="G88" s="1">
         <f t="shared" si="37"/>
-        <v>5.7384297000000001E-2</v>
+        <v>5.7187389999999998E-2</v>
       </c>
       <c r="H88" s="1">
         <f t="shared" si="38"/>
-        <v>5.7602301000000002E-2</v>
+        <v>5.7378247E-2</v>
       </c>
       <c r="I88" s="1">
         <f t="shared" si="39"/>
-        <v>5.7346570999999999E-2</v>
+        <v>5.8160684999999997E-2</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -4458,35 +4853,35 @@
       </c>
       <c r="B92" s="2">
         <f>20*LOG(((B81/5)*B$73)/(B70*(B$84/5)), 10)</f>
-        <v>-4.2406135545266102</v>
+        <v>-3.6891340528825909</v>
       </c>
       <c r="C92" s="2">
         <f t="shared" ref="C92:I92" si="40">20*LOG(((C81/5)*C$73)/(C70*(C$84/5)), 10)</f>
-        <v>-4.203846100845575</v>
+        <v>-3.6429052702734128</v>
       </c>
       <c r="D92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.2955560884875501</v>
+        <v>-3.5900787810789625</v>
       </c>
       <c r="E92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.1648093552128431</v>
+        <v>-3.5925172487574679</v>
       </c>
       <c r="F92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.2687879418630414</v>
+        <v>-3.6337497643784462</v>
       </c>
       <c r="G92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.2445296662841745</v>
+        <v>-3.5695906489463964</v>
       </c>
       <c r="H92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.2952509065758768</v>
+        <v>-3.5973037222666071</v>
       </c>
       <c r="I92" s="2">
         <f t="shared" si="40"/>
-        <v>-4.2829744984920364</v>
+        <v>-3.6894213590209581</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -4495,35 +4890,35 @@
       </c>
       <c r="B93" s="2">
         <f t="shared" ref="B93:I93" si="41">20*LOG(((B82/5)*B$73)/(B71*(B$84/5)), 10)</f>
-        <v>-1.1129930431311517</v>
+        <v>-0.81637833205311994</v>
       </c>
       <c r="C93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.1124131358917917</v>
+        <v>-0.66396059094300885</v>
       </c>
       <c r="D93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.149439633805756</v>
+        <v>-0.72733296005432446</v>
       </c>
       <c r="E93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.0811496724674079</v>
+        <v>-0.75315382896561045</v>
       </c>
       <c r="F93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.1205569508592288</v>
+        <v>-0.72180827105102974</v>
       </c>
       <c r="G93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.1340107956512817</v>
+        <v>-0.74537650358771079</v>
       </c>
       <c r="H93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.0643431100340415</v>
+        <v>-0.63052436673401879</v>
       </c>
       <c r="I93" s="2">
         <f t="shared" si="41"/>
-        <v>-1.1168448795796759</v>
+        <v>-0.71632198924392643</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -4532,35 +4927,35 @@
       </c>
       <c r="B94" s="2">
         <f t="shared" ref="B94:I94" si="42">20*LOG(((B83/5)*B$73)/(B72*(B$84/5)), 10)</f>
-        <v>-0.23748702781467856</v>
+        <v>-0.1310592980541696</v>
       </c>
       <c r="C94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.25561159468528444</v>
+        <v>1.5845526152597406E-2</v>
       </c>
       <c r="D94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.26409173525171648</v>
+        <v>-1.6938456298792346E-2</v>
       </c>
       <c r="E94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.2395243157863387</v>
+        <v>-5.7507066553697445E-2</v>
       </c>
       <c r="F94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.24241620327778021</v>
+        <v>-4.4503293226553095E-2</v>
       </c>
       <c r="G94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.25993304877200535</v>
+        <v>-5.2189936086409816E-2</v>
       </c>
       <c r="H94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.17279934371787392</v>
+        <v>1.2184897752901727E-2</v>
       </c>
       <c r="I94" s="2">
         <f t="shared" si="42"/>
-        <v>-0.23469173329795087</v>
+        <v>-2.459329887802017E-2</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -4606,35 +5001,35 @@
       </c>
       <c r="B96" s="2">
         <f t="shared" ref="B96:I96" si="44">20*LOG(((B85/5)*B$73)/(B74*(B$84/5)), 10)</f>
-        <v>-8.3428582766037498E-2</v>
+        <v>-6.0841697509282644E-2</v>
       </c>
       <c r="C96" s="2">
         <f t="shared" si="44"/>
-        <v>-5.3928697875541075E-2</v>
+        <v>-0.17355914989785776</v>
       </c>
       <c r="D96" s="2">
         <f t="shared" si="44"/>
-        <v>-7.8972495004594717E-2</v>
+        <v>-0.15246638869571233</v>
       </c>
       <c r="E96" s="2">
         <f t="shared" si="44"/>
-        <v>-6.8125258451934026E-2</v>
+        <v>-0.11515728917063225</v>
       </c>
       <c r="F96" s="2">
         <f t="shared" si="44"/>
-        <v>-8.6282158749385274E-2</v>
+        <v>-0.17268009499094422</v>
       </c>
       <c r="G96" s="2">
         <f t="shared" si="44"/>
-        <v>-7.7514105132569441E-2</v>
+        <v>-0.10217013439304393</v>
       </c>
       <c r="H96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.1400171050082773</v>
+        <v>-0.1663246896651224</v>
       </c>
       <c r="I96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.10291088256986433</v>
+        <v>-0.13546045526462047</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -4643,35 +5038,35 @@
       </c>
       <c r="B97" s="2">
         <f t="shared" ref="B97:I97" si="45">20*LOG(((B86/5)*B$73)/(B75*(B$84/5)), 10)</f>
-        <v>-0.19080279080498433</v>
+        <v>-0.15187747318385247</v>
       </c>
       <c r="C97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.12166734848817468</v>
+        <v>-0.29796169413545126</v>
       </c>
       <c r="D97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.17085883074012542</v>
+        <v>-0.2672632137824536</v>
       </c>
       <c r="E97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.14539322546073682</v>
+        <v>-0.16125995510145749</v>
       </c>
       <c r="F97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.19190029197578945</v>
+        <v>-0.28390115339424138</v>
       </c>
       <c r="G97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.18729065917088672</v>
+        <v>-0.17485447291505984</v>
       </c>
       <c r="H97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.26586845041545021</v>
+        <v>-0.2730471967009343</v>
       </c>
       <c r="I97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.21944166060391979</v>
+        <v>-0.207868106228773</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -4680,35 +5075,35 @@
       </c>
       <c r="B98" s="2">
         <f t="shared" ref="B98:I98" si="46">20*LOG(((B87/5)*B$73)/(B76*(B$84/5)), 10)</f>
-        <v>-0.57973179216900805</v>
+        <v>-0.52551282282004774</v>
       </c>
       <c r="C98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.4632138848958034</v>
+        <v>-0.69710014885339522</v>
       </c>
       <c r="D98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.52898408131093322</v>
+        <v>-0.62254942318667972</v>
       </c>
       <c r="E98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.48193461824585232</v>
+        <v>-0.47628226146856145</v>
       </c>
       <c r="F98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.57615871666031537</v>
+        <v>-0.66467701229760368</v>
       </c>
       <c r="G98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.57559848038608596</v>
+        <v>-0.54018525069118173</v>
       </c>
       <c r="H98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.64497795695904914</v>
+        <v>-0.63430179156361266</v>
       </c>
       <c r="I98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.60533578464958049</v>
+        <v>-0.54949522779650595</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -4717,35 +5112,35 @@
       </c>
       <c r="B99" s="2">
         <f t="shared" ref="B99:I99" si="47">20*LOG(((B88/5)*B$73)/(B77*(B$84/5)), 10)</f>
-        <v>-2.3768266391809099</v>
+        <v>-2.2924570038981433</v>
       </c>
       <c r="C99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.15092322206679</v>
+        <v>-2.4745871521877834</v>
       </c>
       <c r="D99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.2314877477775079</v>
+        <v>-2.3427145747948637</v>
       </c>
       <c r="E99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.1456369354496103</v>
+        <v>-2.07730877718142</v>
       </c>
       <c r="F99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.3519325780196474</v>
+        <v>-2.4095390402903285</v>
       </c>
       <c r="G99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.3649499632631681</v>
+        <v>-2.2761123163895123</v>
       </c>
       <c r="H99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.3703018027305038</v>
+        <v>-2.2941507823686766</v>
       </c>
       <c r="I99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.3741791320699881</v>
+        <v>-2.1929038301309696</v>
       </c>
     </row>
   </sheetData>

--- a/АЧХ_result.xlsx
+++ b/АЧХ_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E81F01E-53AB-48B9-9215-351B9BB93222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E92A995-4CB9-40C7-BBE5-433FB0CBBEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6030" yWindow="3945" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,28 +566,28 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="M1" s="3">
-        <v>1.5463451E-2</v>
+        <v>1.5373744E-2</v>
       </c>
       <c r="N1" s="3">
-        <v>1.5190327E-2</v>
+        <v>1.5230230000000001E-2</v>
       </c>
       <c r="O1" s="3">
-        <v>1.5175681999999999E-2</v>
+        <v>1.5256321999999999E-2</v>
       </c>
       <c r="P1" s="3">
-        <v>1.5258344E-2</v>
+        <v>1.5320613E-2</v>
       </c>
       <c r="Q1" s="3">
-        <v>1.5222704E-2</v>
+        <v>1.5249057999999999E-2</v>
       </c>
       <c r="R1" s="3">
-        <v>1.5261749E-2</v>
+        <v>1.5353848999999999E-2</v>
       </c>
       <c r="S1" s="3">
-        <v>1.5157653E-2</v>
+        <v>1.5118700000000001E-2</v>
       </c>
       <c r="T1" s="3">
-        <v>1.5212643E-2</v>
+        <v>1.5184838000000001E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -619,28 +619,28 @@
         <v>8</v>
       </c>
       <c r="M2" s="3">
-        <v>1.539593E-2</v>
+        <v>1.5280185E-2</v>
       </c>
       <c r="N2" s="3">
-        <v>1.5074811E-2</v>
+        <v>1.5095388E-2</v>
       </c>
       <c r="O2" s="3">
-        <v>1.5097622999999999E-2</v>
+        <v>1.5136573E-2</v>
       </c>
       <c r="P2" s="3">
-        <v>1.5198011000000001E-2</v>
+        <v>1.5245296E-2</v>
       </c>
       <c r="Q2" s="3">
-        <v>1.5099638E-2</v>
+        <v>1.5152631999999999E-2</v>
       </c>
       <c r="R2" s="3">
-        <v>1.5205282000000001E-2</v>
+        <v>1.5254953999999999E-2</v>
       </c>
       <c r="S2" s="3">
-        <v>1.5051475E-2</v>
+        <v>1.5035247999999999E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>1.5099606E-2</v>
+        <v>1.5090304000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -649,59 +649,59 @@
       </c>
       <c r="B3" s="1">
         <f>M1</f>
-        <v>1.5463451E-2</v>
+        <v>1.5373744E-2</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:I10" si="0">N1</f>
-        <v>1.5190327E-2</v>
+        <v>1.5230230000000001E-2</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5175681999999999E-2</v>
+        <v>1.5256321999999999E-2</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5258344E-2</v>
+        <v>1.5320613E-2</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5222704E-2</v>
+        <v>1.5249057999999999E-2</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5261749E-2</v>
+        <v>1.5353848999999999E-2</v>
       </c>
       <c r="H3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5157653E-2</v>
+        <v>1.5118700000000001E-2</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" si="0"/>
-        <v>1.5212643E-2</v>
+        <v>1.5184838000000001E-2</v>
       </c>
       <c r="M3" s="3">
-        <v>1.5393377E-2</v>
+        <v>1.5315468E-2</v>
       </c>
       <c r="N3" s="3">
-        <v>1.5104261000000001E-2</v>
+        <v>1.5138286000000001E-2</v>
       </c>
       <c r="O3" s="3">
-        <v>1.5129914E-2</v>
+        <v>1.5171762E-2</v>
       </c>
       <c r="P3" s="3">
-        <v>1.5230858E-2</v>
+        <v>1.5291423E-2</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.5121265E-2</v>
+        <v>1.5203187E-2</v>
       </c>
       <c r="R3" s="3">
-        <v>1.5229763E-2</v>
+        <v>1.5284904E-2</v>
       </c>
       <c r="S3" s="3">
-        <v>1.5097911E-2</v>
+        <v>1.5109533E-2</v>
       </c>
       <c r="T3" s="3">
-        <v>1.5132652999999999E-2</v>
+        <v>1.5157701000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -710,59 +710,59 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B10" si="1">M2</f>
-        <v>1.539593E-2</v>
+        <v>1.5280185E-2</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5074811E-2</v>
+        <v>1.5095388E-2</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5097622999999999E-2</v>
+        <v>1.5136573E-2</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5198011000000001E-2</v>
+        <v>1.5245296E-2</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5099638E-2</v>
+        <v>1.5152631999999999E-2</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5205282000000001E-2</v>
+        <v>1.5254953999999999E-2</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5051475E-2</v>
+        <v>1.5035247999999999E-2</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" si="0"/>
-        <v>1.5099606E-2</v>
+        <v>1.5090304000000001E-2</v>
       </c>
       <c r="M4" s="3">
-        <v>1.543451E-2</v>
+        <v>1.5417645000000001E-2</v>
       </c>
       <c r="N4" s="3">
-        <v>1.5267509E-2</v>
+        <v>1.531389E-2</v>
       </c>
       <c r="O4" s="3">
-        <v>1.5277885E-2</v>
+        <v>1.5325017E-2</v>
       </c>
       <c r="P4" s="3">
-        <v>1.5348919000000001E-2</v>
+        <v>1.5415241999999999E-2</v>
       </c>
       <c r="Q4" s="3">
-        <v>1.5270183999999999E-2</v>
+        <v>1.5346922000000001E-2</v>
       </c>
       <c r="R4" s="3">
-        <v>1.5333728E-2</v>
+        <v>1.5400436999999999E-2</v>
       </c>
       <c r="S4" s="3">
-        <v>1.5276692999999999E-2</v>
+        <v>1.5299258E-2</v>
       </c>
       <c r="T4" s="3">
-        <v>1.5297659E-2</v>
+        <v>1.5353898E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -771,59 +771,59 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="1"/>
-        <v>1.5393377E-2</v>
+        <v>1.5315468E-2</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5104261000000001E-2</v>
+        <v>1.5138286000000001E-2</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5129914E-2</v>
+        <v>1.5171762E-2</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5230858E-2</v>
+        <v>1.5291423E-2</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5121265E-2</v>
+        <v>1.5203187E-2</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5229763E-2</v>
+        <v>1.5284904E-2</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5097911E-2</v>
+        <v>1.5109533E-2</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5132652999999999E-2</v>
+        <v>1.5157701000000001E-2</v>
       </c>
       <c r="M5" s="3">
-        <v>1.5445716999999999E-2</v>
+        <v>1.5448834999999999E-2</v>
       </c>
       <c r="N5" s="3">
-        <v>1.5353E-2</v>
+        <v>1.5386875E-2</v>
       </c>
       <c r="O5" s="3">
-        <v>1.5349242000000001E-2</v>
+        <v>1.5394672E-2</v>
       </c>
       <c r="P5" s="3">
-        <v>1.5394351000000001E-2</v>
+        <v>1.5449933000000001E-2</v>
       </c>
       <c r="Q5" s="3">
-        <v>1.5349619E-2</v>
+        <v>1.5399690000000001E-2</v>
       </c>
       <c r="R5" s="3">
-        <v>1.5384365000000001E-2</v>
+        <v>1.5445578999999999E-2</v>
       </c>
       <c r="S5" s="3">
-        <v>1.5362894E-2</v>
+        <v>1.5377481E-2</v>
       </c>
       <c r="T5" s="3">
-        <v>1.5374937999999999E-2</v>
+        <v>1.5429864E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -832,59 +832,59 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="1"/>
-        <v>1.543451E-2</v>
+        <v>1.5417645000000001E-2</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5267509E-2</v>
+        <v>1.531389E-2</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5277885E-2</v>
+        <v>1.5325017E-2</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5348919000000001E-2</v>
+        <v>1.5415241999999999E-2</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5270183999999999E-2</v>
+        <v>1.5346922000000001E-2</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5333728E-2</v>
+        <v>1.5400436999999999E-2</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5276692999999999E-2</v>
+        <v>1.5299258E-2</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="0"/>
-        <v>1.5297659E-2</v>
+        <v>1.5353898E-2</v>
       </c>
       <c r="M6" s="3">
-        <v>1.5453516E-2</v>
+        <v>1.5463910000000001E-2</v>
       </c>
       <c r="N6" s="3">
-        <v>1.5384033E-2</v>
+        <v>1.5418181E-2</v>
       </c>
       <c r="O6" s="3">
-        <v>1.5383015999999999E-2</v>
+        <v>1.5428450999999999E-2</v>
       </c>
       <c r="P6" s="3">
-        <v>1.5414821E-2</v>
+        <v>1.5465578000000001E-2</v>
       </c>
       <c r="Q6" s="3">
-        <v>1.5384274999999999E-2</v>
+        <v>1.5427338000000001E-2</v>
       </c>
       <c r="R6" s="3">
-        <v>1.5409056000000001E-2</v>
+        <v>1.5468166E-2</v>
       </c>
       <c r="S6" s="3">
-        <v>1.5402664E-2</v>
+        <v>1.5408043E-2</v>
       </c>
       <c r="T6" s="3">
-        <v>1.5412227000000001E-2</v>
+        <v>1.5460754E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -893,59 +893,59 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="1"/>
-        <v>1.5445716999999999E-2</v>
+        <v>1.5448834999999999E-2</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5353E-2</v>
+        <v>1.5386875E-2</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5349242000000001E-2</v>
+        <v>1.5394672E-2</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5394351000000001E-2</v>
+        <v>1.5449933000000001E-2</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5349619E-2</v>
+        <v>1.5399690000000001E-2</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5384365000000001E-2</v>
+        <v>1.5445578999999999E-2</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5362894E-2</v>
+        <v>1.5377481E-2</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v>1.5374937999999999E-2</v>
+        <v>1.5429864E-2</v>
       </c>
       <c r="M7" s="3">
-        <v>1.5458253E-2</v>
+        <v>1.5492189E-2</v>
       </c>
       <c r="N7" s="3">
-        <v>1.5402229E-2</v>
+        <v>1.5446926E-2</v>
       </c>
       <c r="O7" s="3">
-        <v>1.5401457E-2</v>
+        <v>1.5465527999999999E-2</v>
       </c>
       <c r="P7" s="3">
-        <v>1.5421743999999999E-2</v>
+        <v>1.5496355E-2</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.5399829E-2</v>
+        <v>1.5458401E-2</v>
       </c>
       <c r="R7" s="3">
-        <v>1.5420698E-2</v>
+        <v>1.549727E-2</v>
       </c>
       <c r="S7" s="3">
-        <v>1.5415862000000001E-2</v>
+        <v>1.5442000000000001E-2</v>
       </c>
       <c r="T7" s="3">
-        <v>1.542376E-2</v>
+        <v>1.5492494000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -954,59 +954,59 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="1"/>
-        <v>1.5453516E-2</v>
+        <v>1.5463910000000001E-2</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5384033E-2</v>
+        <v>1.5418181E-2</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5383015999999999E-2</v>
+        <v>1.5428450999999999E-2</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5414821E-2</v>
+        <v>1.5465578000000001E-2</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5384274999999999E-2</v>
+        <v>1.5427338000000001E-2</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5409056000000001E-2</v>
+        <v>1.5468166E-2</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5402664E-2</v>
+        <v>1.5408043E-2</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5412227000000001E-2</v>
+        <v>1.5460754E-2</v>
       </c>
       <c r="M8" s="3">
-        <v>1.5469834999999999E-2</v>
+        <v>1.5504697E-2</v>
       </c>
       <c r="N8" s="3">
-        <v>1.5423177999999999E-2</v>
+        <v>1.5466448000000001E-2</v>
       </c>
       <c r="O8" s="3">
-        <v>1.5425324000000001E-2</v>
+        <v>1.5484144E-2</v>
       </c>
       <c r="P8" s="3">
-        <v>1.5443406E-2</v>
+        <v>1.5507221999999999E-2</v>
       </c>
       <c r="Q8" s="3">
-        <v>1.5424228999999999E-2</v>
+        <v>1.5475898E-2</v>
       </c>
       <c r="R8" s="3">
-        <v>1.544208E-2</v>
+        <v>1.5515568E-2</v>
       </c>
       <c r="S8" s="3">
-        <v>1.5441109999999999E-2</v>
+        <v>1.5455679999999999E-2</v>
       </c>
       <c r="T8" s="3">
-        <v>1.5449595999999999E-2</v>
+        <v>1.5506228E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -1015,59 +1015,59 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="1"/>
-        <v>1.5458253E-2</v>
+        <v>1.5492189E-2</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5402229E-2</v>
+        <v>1.5446926E-2</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5401457E-2</v>
+        <v>1.5465527999999999E-2</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5421743999999999E-2</v>
+        <v>1.5496355E-2</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5399829E-2</v>
+        <v>1.5458401E-2</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5420698E-2</v>
+        <v>1.549727E-2</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5415862000000001E-2</v>
+        <v>1.5442000000000001E-2</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="0"/>
-        <v>1.542376E-2</v>
+        <v>1.5492494000000001E-2</v>
       </c>
       <c r="M9" s="3">
-        <v>9.5857879999999996E-3</v>
+        <v>9.5822270000000005E-3</v>
       </c>
       <c r="N9" s="3">
-        <v>9.5079710000000005E-3</v>
+        <v>9.4977959999999993E-3</v>
       </c>
       <c r="O9" s="3">
-        <v>9.4704880000000009E-3</v>
+        <v>9.394856E-3</v>
       </c>
       <c r="P9" s="3">
-        <v>9.6113629999999995E-3</v>
+        <v>9.5711909999999997E-3</v>
       </c>
       <c r="Q9" s="3">
-        <v>9.4009109999999996E-3</v>
+        <v>9.5120489999999999E-3</v>
       </c>
       <c r="R9" s="3">
-        <v>9.5508899999999994E-3</v>
+        <v>9.5754710000000003E-3</v>
       </c>
       <c r="S9" s="3">
-        <v>9.5773260000000006E-3</v>
+        <v>9.6224640000000007E-3</v>
       </c>
       <c r="T9" s="3">
-        <v>9.4803200000000004E-3</v>
+        <v>9.5837079999999998E-3</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1076,85 +1076,85 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="1"/>
-        <v>1.5469834999999999E-2</v>
+        <v>1.5504697E-2</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5423177999999999E-2</v>
+        <v>1.5466448000000001E-2</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5425324000000001E-2</v>
+        <v>1.5484144E-2</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5443406E-2</v>
+        <v>1.5507221999999999E-2</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5424228999999999E-2</v>
+        <v>1.5475898E-2</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>1.544208E-2</v>
+        <v>1.5515568E-2</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5441109999999999E-2</v>
+        <v>1.5455679999999999E-2</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="0"/>
-        <v>1.5449595999999999E-2</v>
+        <v>1.5506228E-2</v>
       </c>
       <c r="M10" s="3">
-        <v>1.3243167E-2</v>
+        <v>1.3232023000000001E-2</v>
       </c>
       <c r="N10" s="3">
-        <v>1.3283092E-2</v>
+        <v>1.3211479999999999E-2</v>
       </c>
       <c r="O10" s="3">
-        <v>1.3171778E-2</v>
+        <v>1.3152936E-2</v>
       </c>
       <c r="P10" s="3">
-        <v>1.3254002000000001E-2</v>
+        <v>1.3303936000000001E-2</v>
       </c>
       <c r="Q10" s="3">
-        <v>1.3168598E-2</v>
+        <v>1.3236758E-2</v>
       </c>
       <c r="R10" s="3">
-        <v>1.3172807999999999E-2</v>
+        <v>1.3195884999999999E-2</v>
       </c>
       <c r="S10" s="3">
-        <v>1.3273307999999999E-2</v>
+        <v>1.3328517999999999E-2</v>
       </c>
       <c r="T10" s="3">
-        <v>1.3218651E-2</v>
+        <v>1.33197E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M11" s="3">
-        <v>1.4398592999999999E-2</v>
+        <v>1.4369554E-2</v>
       </c>
       <c r="N11" s="3">
-        <v>1.4412874000000001E-2</v>
+        <v>1.4371185999999999E-2</v>
       </c>
       <c r="O11" s="3">
-        <v>1.4301707E-2</v>
+        <v>1.4335250000000001E-2</v>
       </c>
       <c r="P11" s="3">
-        <v>1.4372822E-2</v>
+        <v>1.4449837E-2</v>
       </c>
       <c r="Q11" s="3">
-        <v>1.4317292000000001E-2</v>
+        <v>1.4337994E-2</v>
       </c>
       <c r="R11" s="3">
-        <v>1.4291422E-2</v>
+        <v>1.4394918E-2</v>
       </c>
       <c r="S11" s="3">
-        <v>1.4440583E-2</v>
+        <v>1.4510029000000001E-2</v>
       </c>
       <c r="T11" s="3">
-        <v>1.4366152E-2</v>
+        <v>1.4502374E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -1170,28 +1170,28 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="M12" s="3">
-        <v>1.4702112999999999E-2</v>
+        <v>1.4630387E-2</v>
       </c>
       <c r="N12" s="3">
-        <v>1.4584512000000001E-2</v>
+        <v>1.4610199000000001E-2</v>
       </c>
       <c r="O12" s="3">
-        <v>1.4508119E-2</v>
+        <v>1.4586992999999999E-2</v>
       </c>
       <c r="P12" s="3">
-        <v>1.4570873999999999E-2</v>
+        <v>1.4661422E-2</v>
       </c>
       <c r="Q12" s="3">
-        <v>1.4505763E-2</v>
+        <v>1.4569952000000001E-2</v>
       </c>
       <c r="R12" s="3">
-        <v>1.4571235E-2</v>
+        <v>1.4620716000000001E-2</v>
       </c>
       <c r="S12" s="3">
-        <v>1.4568578E-2</v>
+        <v>1.4661343E-2</v>
       </c>
       <c r="T12" s="3">
-        <v>1.4606920000000001E-2</v>
+        <v>1.4643255000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -1223,28 +1223,28 @@
         <v>8</v>
       </c>
       <c r="M13" s="3">
-        <v>1.4575025E-2</v>
+        <v>1.454693E-2</v>
       </c>
       <c r="N13" s="3">
-        <v>1.4372538000000001E-2</v>
+        <v>1.4394835E-2</v>
       </c>
       <c r="O13" s="3">
-        <v>1.4340105000000001E-2</v>
+        <v>1.4395856E-2</v>
       </c>
       <c r="P13" s="3">
-        <v>1.4466662999999999E-2</v>
+        <v>1.4576501E-2</v>
       </c>
       <c r="Q13" s="3">
-        <v>1.4373998000000001E-2</v>
+        <v>1.4372255E-2</v>
       </c>
       <c r="R13" s="3">
-        <v>1.4446616000000001E-2</v>
+        <v>1.4382135000000001E-2</v>
       </c>
       <c r="S13" s="3">
-        <v>1.4405522E-2</v>
+        <v>1.4469564000000001E-2</v>
       </c>
       <c r="T13" s="3">
-        <v>1.4441905999999999E-2</v>
+        <v>1.4414727E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -1253,59 +1253,59 @@
       </c>
       <c r="B14" s="1">
         <f>M9</f>
-        <v>9.5857879999999996E-3</v>
+        <v>9.5822270000000005E-3</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" ref="C14:I21" si="2">N9</f>
-        <v>9.5079710000000005E-3</v>
+        <v>9.4977959999999993E-3</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="2"/>
-        <v>9.4704880000000009E-3</v>
+        <v>9.394856E-3</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="2"/>
-        <v>9.6113629999999995E-3</v>
+        <v>9.5711909999999997E-3</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="2"/>
-        <v>9.4009109999999996E-3</v>
+        <v>9.5120489999999999E-3</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="2"/>
-        <v>9.5508899999999994E-3</v>
+        <v>9.5754710000000003E-3</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v>9.5773260000000006E-3</v>
+        <v>9.6224640000000007E-3</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>9.4803200000000004E-3</v>
+        <v>9.5837079999999998E-3</v>
       </c>
       <c r="M14" s="3">
-        <v>1.4516436000000001E-2</v>
+        <v>1.4441010000000001E-2</v>
       </c>
       <c r="N14" s="3">
-        <v>1.4223157E-2</v>
+        <v>1.421184E-2</v>
       </c>
       <c r="O14" s="3">
-        <v>1.4168887999999999E-2</v>
+        <v>1.4216562E-2</v>
       </c>
       <c r="P14" s="3">
-        <v>1.4440203E-2</v>
+        <v>1.4574349E-2</v>
       </c>
       <c r="Q14" s="3">
-        <v>1.4163705E-2</v>
+        <v>1.4224326000000001E-2</v>
       </c>
       <c r="R14" s="3">
-        <v>1.4325831000000001E-2</v>
+        <v>1.4226437E-2</v>
       </c>
       <c r="S14" s="3">
-        <v>1.4271053000000001E-2</v>
+        <v>1.4358589999999999E-2</v>
       </c>
       <c r="T14" s="3">
-        <v>1.438797E-2</v>
+        <v>1.421502E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -1314,59 +1314,59 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" ref="B15:B21" si="3">M10</f>
-        <v>1.3243167E-2</v>
+        <v>1.3232023000000001E-2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3283092E-2</v>
+        <v>1.3211479999999999E-2</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3171778E-2</v>
+        <v>1.3152936E-2</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3254002000000001E-2</v>
+        <v>1.3303936000000001E-2</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3168598E-2</v>
+        <v>1.3236758E-2</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3172807999999999E-2</v>
+        <v>1.3195884999999999E-2</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3273307999999999E-2</v>
+        <v>1.3328517999999999E-2</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>1.3218651E-2</v>
+        <v>1.33197E-2</v>
       </c>
       <c r="M15" s="3">
-        <v>1.3876304000000001E-2</v>
+        <v>1.3878400000000001E-2</v>
       </c>
       <c r="N15" s="3">
-        <v>1.3623939999999999E-2</v>
+        <v>1.3701364000000001E-2</v>
       </c>
       <c r="O15" s="3">
-        <v>1.3633045E-2</v>
+        <v>1.3682662999999999E-2</v>
       </c>
       <c r="P15" s="3">
-        <v>1.3937110000000001E-2</v>
+        <v>1.4020035E-2</v>
       </c>
       <c r="Q15" s="3">
-        <v>1.3616359E-2</v>
+        <v>1.3710829000000001E-2</v>
       </c>
       <c r="R15" s="3">
-        <v>1.3776525E-2</v>
+        <v>1.3605122000000001E-2</v>
       </c>
       <c r="S15" s="3">
-        <v>1.3746171E-2</v>
+        <v>1.3719581999999999E-2</v>
       </c>
       <c r="T15" s="3">
-        <v>1.3879752E-2</v>
+        <v>1.3657816E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -1375,59 +1375,59 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="3"/>
-        <v>1.4398592999999999E-2</v>
+        <v>1.4369554E-2</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4412874000000001E-2</v>
+        <v>1.4371185999999999E-2</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4301707E-2</v>
+        <v>1.4335250000000001E-2</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4372822E-2</v>
+        <v>1.4449837E-2</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4317292000000001E-2</v>
+        <v>1.4337994E-2</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4291422E-2</v>
+        <v>1.4394918E-2</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4440583E-2</v>
+        <v>1.4510029000000001E-2</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>1.4366152E-2</v>
+        <v>1.4502374E-2</v>
       </c>
       <c r="M16" s="3">
-        <v>1.136701E-2</v>
+        <v>1.1278979999999999E-2</v>
       </c>
       <c r="N16" s="3">
-        <v>1.1102363000000001E-2</v>
+        <v>1.1275759999999999E-2</v>
       </c>
       <c r="O16" s="3">
-        <v>1.1227157E-2</v>
+        <v>1.1201086000000001E-2</v>
       </c>
       <c r="P16" s="3">
-        <v>1.1634211E-2</v>
+        <v>1.1577718000000001E-2</v>
       </c>
       <c r="Q16" s="3">
-        <v>1.1162033999999999E-2</v>
+        <v>1.1248241000000001E-2</v>
       </c>
       <c r="R16" s="3">
-        <v>1.1302520999999999E-2</v>
+        <v>1.1108547E-2</v>
       </c>
       <c r="S16" s="3">
-        <v>1.1383008999999999E-2</v>
+        <v>1.1233734E-2</v>
       </c>
       <c r="T16" s="3">
-        <v>1.1516579000000001E-2</v>
+        <v>1.1161383E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -1436,59 +1436,59 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="3"/>
-        <v>1.4702112999999999E-2</v>
+        <v>1.4630387E-2</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4584512000000001E-2</v>
+        <v>1.4610199000000001E-2</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4508119E-2</v>
+        <v>1.4586992999999999E-2</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4570873999999999E-2</v>
+        <v>1.4661422E-2</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4505763E-2</v>
+        <v>1.4569952000000001E-2</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4571235E-2</v>
+        <v>1.4620716000000001E-2</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4568578E-2</v>
+        <v>1.4661343E-2</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>1.4606920000000001E-2</v>
+        <v>1.4643255000000001E-2</v>
       </c>
       <c r="M17" s="3">
-        <v>1.5460606999999999E-2</v>
+        <v>1.537171E-2</v>
       </c>
       <c r="N17" s="3">
-        <v>1.5185120999999999E-2</v>
+        <v>1.5220595999999999E-2</v>
       </c>
       <c r="O17" s="3">
-        <v>1.51734E-2</v>
+        <v>1.525495E-2</v>
       </c>
       <c r="P17" s="3">
-        <v>1.5256438000000001E-2</v>
+        <v>1.531502E-2</v>
       </c>
       <c r="Q17" s="3">
-        <v>1.5223633E-2</v>
+        <v>1.5240757000000001E-2</v>
       </c>
       <c r="R17" s="3">
-        <v>1.5263499E-2</v>
+        <v>1.5349572000000001E-2</v>
       </c>
       <c r="S17" s="3">
-        <v>1.5157435E-2</v>
+        <v>1.5112265999999999E-2</v>
       </c>
       <c r="T17" s="3">
-        <v>1.5210446000000001E-2</v>
+        <v>1.5186079E-2</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -1497,59 +1497,59 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="3"/>
-        <v>1.4575025E-2</v>
+        <v>1.454693E-2</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4372538000000001E-2</v>
+        <v>1.4394835E-2</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4340105000000001E-2</v>
+        <v>1.4395856E-2</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4466662999999999E-2</v>
+        <v>1.4576501E-2</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4373998000000001E-2</v>
+        <v>1.4372255E-2</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4446616000000001E-2</v>
+        <v>1.4382135000000001E-2</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4405522E-2</v>
+        <v>1.4469564000000001E-2</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>1.4441905999999999E-2</v>
+        <v>1.4414727E-2</v>
       </c>
       <c r="M18" s="3">
-        <v>1.5388021E-2</v>
+        <v>1.5276534E-2</v>
       </c>
       <c r="N18" s="3">
-        <v>1.5064731E-2</v>
+        <v>1.5087961E-2</v>
       </c>
       <c r="O18" s="3">
-        <v>1.5090933000000001E-2</v>
+        <v>1.5130219E-2</v>
       </c>
       <c r="P18" s="3">
-        <v>1.5193577999999999E-2</v>
+        <v>1.5238064000000001E-2</v>
       </c>
       <c r="Q18" s="3">
-        <v>1.5099306E-2</v>
+        <v>1.5142933000000001E-2</v>
       </c>
       <c r="R18" s="3">
-        <v>1.5197777000000001E-2</v>
+        <v>1.524578E-2</v>
       </c>
       <c r="S18" s="3">
-        <v>1.5053834E-2</v>
+        <v>1.5029307E-2</v>
       </c>
       <c r="T18" s="3">
-        <v>1.5098501E-2</v>
+        <v>1.5083549999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -1558,59 +1558,59 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="3"/>
-        <v>1.4516436000000001E-2</v>
+        <v>1.4441010000000001E-2</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4223157E-2</v>
+        <v>1.421184E-2</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4168887999999999E-2</v>
+        <v>1.4216562E-2</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4440203E-2</v>
+        <v>1.4574349E-2</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4163705E-2</v>
+        <v>1.4224326000000001E-2</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4325831000000001E-2</v>
+        <v>1.4226437E-2</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v>1.4271053000000001E-2</v>
+        <v>1.4358589999999999E-2</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>1.438797E-2</v>
+        <v>1.421502E-2</v>
       </c>
       <c r="M19" s="3">
-        <v>1.5380532000000001E-2</v>
+        <v>1.5302912E-2</v>
       </c>
       <c r="N19" s="3">
-        <v>1.5098355000000001E-2</v>
+        <v>1.5126651E-2</v>
       </c>
       <c r="O19" s="3">
-        <v>1.5121018E-2</v>
+        <v>1.5161286E-2</v>
       </c>
       <c r="P19" s="3">
-        <v>1.5226099999999999E-2</v>
+        <v>1.5284514000000001E-2</v>
       </c>
       <c r="Q19" s="3">
-        <v>1.5116743E-2</v>
+        <v>1.5189166E-2</v>
       </c>
       <c r="R19" s="3">
-        <v>1.5222526E-2</v>
+        <v>1.5273745E-2</v>
       </c>
       <c r="S19" s="3">
-        <v>1.5093499E-2</v>
+        <v>1.5102295999999999E-2</v>
       </c>
       <c r="T19" s="3">
-        <v>1.5124186E-2</v>
+        <v>1.5153955E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1619,59 +1619,59 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="3"/>
-        <v>1.3876304000000001E-2</v>
+        <v>1.3878400000000001E-2</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3623939999999999E-2</v>
+        <v>1.3701364000000001E-2</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3633045E-2</v>
+        <v>1.3682662999999999E-2</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3937110000000001E-2</v>
+        <v>1.4020035E-2</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3616359E-2</v>
+        <v>1.3710829000000001E-2</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3776525E-2</v>
+        <v>1.3605122000000001E-2</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3746171E-2</v>
+        <v>1.3719581999999999E-2</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>1.3879752E-2</v>
+        <v>1.3657816E-2</v>
       </c>
       <c r="M20" s="3">
-        <v>1.5417725E-2</v>
+        <v>1.54001E-2</v>
       </c>
       <c r="N20" s="3">
-        <v>1.5260350000000001E-2</v>
+        <v>1.5298915E-2</v>
       </c>
       <c r="O20" s="3">
-        <v>1.5265997E-2</v>
+        <v>1.5308646E-2</v>
       </c>
       <c r="P20" s="3">
-        <v>1.5337414000000001E-2</v>
+        <v>1.5401229000000001E-2</v>
       </c>
       <c r="Q20" s="3">
-        <v>1.5259754E-2</v>
+        <v>1.5331348E-2</v>
       </c>
       <c r="R20" s="3">
-        <v>1.5325841E-2</v>
+        <v>1.5385831000000001E-2</v>
       </c>
       <c r="S20" s="3">
-        <v>1.5267584000000001E-2</v>
+        <v>1.5289560000000001E-2</v>
       </c>
       <c r="T20" s="3">
-        <v>1.528624E-2</v>
+        <v>1.5340433000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1680,85 +1680,85 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="3"/>
-        <v>1.136701E-2</v>
+        <v>1.1278979999999999E-2</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1102363000000001E-2</v>
+        <v>1.1275759999999999E-2</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1227157E-2</v>
+        <v>1.1201086000000001E-2</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1634211E-2</v>
+        <v>1.1577718000000001E-2</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1162033999999999E-2</v>
+        <v>1.1248241000000001E-2</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1302520999999999E-2</v>
+        <v>1.1108547E-2</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1383008999999999E-2</v>
+        <v>1.1233734E-2</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>1.1516579000000001E-2</v>
+        <v>1.1161383E-2</v>
       </c>
       <c r="M21" s="3">
-        <v>1.5429371000000001E-2</v>
+        <v>1.5430304000000001E-2</v>
       </c>
       <c r="N21" s="3">
-        <v>1.5339591E-2</v>
+        <v>1.5369900000000001E-2</v>
       </c>
       <c r="O21" s="3">
-        <v>1.5337886E-2</v>
+        <v>1.5375969999999999E-2</v>
       </c>
       <c r="P21" s="3">
-        <v>1.5381308999999999E-2</v>
+        <v>1.5434552000000001E-2</v>
       </c>
       <c r="Q21" s="3">
-        <v>1.5336654E-2</v>
+        <v>1.5383864000000001E-2</v>
       </c>
       <c r="R21" s="3">
-        <v>1.5372050999999999E-2</v>
+        <v>1.5428333000000001E-2</v>
       </c>
       <c r="S21" s="3">
-        <v>1.5352174999999999E-2</v>
+        <v>1.5360229E-2</v>
       </c>
       <c r="T21" s="3">
-        <v>1.5363714000000001E-2</v>
+        <v>1.5415059E-2</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M22" s="3">
-        <v>1.5438189E-2</v>
+        <v>1.5446207999999999E-2</v>
       </c>
       <c r="N22" s="3">
-        <v>1.5372445E-2</v>
+        <v>1.5399919999999999E-2</v>
       </c>
       <c r="O22" s="3">
-        <v>1.5371027000000001E-2</v>
+        <v>1.5410881E-2</v>
       </c>
       <c r="P22" s="3">
-        <v>1.5398904E-2</v>
+        <v>1.5451395E-2</v>
       </c>
       <c r="Q22" s="3">
-        <v>1.5368715E-2</v>
+        <v>1.5409291E-2</v>
       </c>
       <c r="R22" s="3">
-        <v>1.5396452999999999E-2</v>
+        <v>1.5451507999999999E-2</v>
       </c>
       <c r="S22" s="3">
-        <v>1.5389172E-2</v>
+        <v>1.5392539E-2</v>
       </c>
       <c r="T22" s="3">
-        <v>1.5395835E-2</v>
+        <v>1.5444571000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -1774,28 +1774,28 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="M23" s="3">
-        <v>1.5438093E-2</v>
+        <v>1.5476652E-2</v>
       </c>
       <c r="N23" s="3">
-        <v>1.5384689999999999E-2</v>
+        <v>1.5433664999999999E-2</v>
       </c>
       <c r="O23" s="3">
-        <v>1.5387779000000001E-2</v>
+        <v>1.5447400999999999E-2</v>
       </c>
       <c r="P23" s="3">
-        <v>1.5409419000000001E-2</v>
+        <v>1.5478057999999999E-2</v>
       </c>
       <c r="Q23" s="3">
-        <v>1.5384178E-2</v>
+        <v>1.54436E-2</v>
       </c>
       <c r="R23" s="3">
-        <v>1.5408744E-2</v>
+        <v>1.5481340999999999E-2</v>
       </c>
       <c r="S23" s="3">
-        <v>1.5400811E-2</v>
+        <v>1.5429965E-2</v>
       </c>
       <c r="T23" s="3">
-        <v>1.5408893E-2</v>
+        <v>1.5469368000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1827,28 +1827,28 @@
         <v>8</v>
       </c>
       <c r="M24" s="3">
-        <v>1.545443E-2</v>
+        <v>1.5481933999999999E-2</v>
       </c>
       <c r="N24" s="3">
-        <v>1.5409826999999999E-2</v>
+        <v>1.5444373000000001E-2</v>
       </c>
       <c r="O24" s="3">
-        <v>1.5409910000000001E-2</v>
+        <v>1.5460544E-2</v>
       </c>
       <c r="P24" s="3">
-        <v>1.5426683E-2</v>
+        <v>1.5483986E-2</v>
       </c>
       <c r="Q24" s="3">
-        <v>1.5407743999999999E-2</v>
+        <v>1.5453415999999999E-2</v>
       </c>
       <c r="R24" s="3">
-        <v>1.5426611999999999E-2</v>
+        <v>1.5491134E-2</v>
       </c>
       <c r="S24" s="3">
-        <v>1.5426082000000001E-2</v>
+        <v>1.543623E-2</v>
       </c>
       <c r="T24" s="3">
-        <v>1.5429859000000001E-2</v>
+        <v>1.548588E-2</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1857,59 +1857,59 @@
       </c>
       <c r="B25" s="2">
         <f>20*LOG(((B14)*B$6)/(B3*(B$17)), 10)</f>
-        <v>-3.7313102512266716</v>
+        <v>-3.6510192529741339</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25:I25" si="4">20*LOG(((C14)*C$6)/(C3*(C$17)), 10)</f>
-        <v>-3.6720598398462116</v>
+        <v>-3.6930846547336129</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.646474637238204</v>
+        <v>-3.7824905625291825</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.5626046085475642</v>
+        <v>-3.6507181332350318</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.7403633791838917</v>
+        <v>-3.6481154522912624</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.6281814145943736</v>
+        <v>-3.6498543319677901</v>
       </c>
       <c r="H25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.5755100504911672</v>
+        <v>-3.554630802759799</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="4"/>
-        <v>-3.7063070340580824</v>
+        <v>-3.5859112832186146</v>
       </c>
       <c r="M25" s="3">
-        <v>9.7773419999999996E-3</v>
+        <v>9.7392220000000005E-3</v>
       </c>
       <c r="N25" s="3">
-        <v>9.7637880000000007E-3</v>
+        <v>9.6926679999999998E-3</v>
       </c>
       <c r="O25" s="3">
-        <v>9.8411220000000008E-3</v>
+        <v>9.6832910000000001E-3</v>
       </c>
       <c r="P25" s="3">
-        <v>9.8550749999999996E-3</v>
+        <v>9.8253079999999996E-3</v>
       </c>
       <c r="Q25" s="3">
-        <v>9.7710999999999996E-3</v>
+        <v>9.7569849999999993E-3</v>
       </c>
       <c r="R25" s="3">
-        <v>9.8427540000000004E-3</v>
+        <v>9.8408239999999998E-3</v>
       </c>
       <c r="S25" s="3">
-        <v>9.8370479999999993E-3</v>
+        <v>9.9364910000000004E-3</v>
       </c>
       <c r="T25" s="3">
-        <v>9.7172249999999995E-3</v>
+        <v>9.8244449999999994E-3</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1918,59 +1918,59 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" ref="B26:I26" si="5">20*LOG(((B15)*B$6)/(B4*(B$17)), 10)</f>
-        <v>-0.88601964216684748</v>
+        <v>-0.7948027564657284</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.70152825464386037</v>
+        <v>-0.74926833456755637</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.73624093076836683</v>
+        <v>-0.7913932481820265</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.73695062390219845</v>
+        <v>-0.74762922422014988</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.74246605755747608</v>
+        <v>-0.72286564369283601</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.80329448933223424</v>
+        <v>-0.8081595417809937</v>
       </c>
       <c r="H26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.67975403753787922</v>
+        <v>-0.67664237700705043</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="5"/>
-        <v>-0.75424307266107493</v>
+        <v>-0.67245039490899827</v>
       </c>
       <c r="M26" s="3">
-        <v>1.3472259E-2</v>
+        <v>1.3521164E-2</v>
       </c>
       <c r="N26" s="3">
-        <v>1.3613867999999999E-2</v>
+        <v>1.3509754000000001E-2</v>
       </c>
       <c r="O26" s="3">
-        <v>1.3554066E-2</v>
+        <v>1.3502767000000001E-2</v>
       </c>
       <c r="P26" s="3">
-        <v>1.3572486999999999E-2</v>
+        <v>1.3554392E-2</v>
       </c>
       <c r="Q26" s="3">
-        <v>1.3506873000000001E-2</v>
+        <v>1.3512667000000001E-2</v>
       </c>
       <c r="R26" s="3">
-        <v>1.3530873000000001E-2</v>
+        <v>1.3557862E-2</v>
       </c>
       <c r="S26" s="3">
-        <v>1.3602635E-2</v>
+        <v>1.3656359E-2</v>
       </c>
       <c r="T26" s="3">
-        <v>1.3586007000000001E-2</v>
+        <v>1.3682948E-2</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -1979,59 +1979,59 @@
       </c>
       <c r="B27" s="2">
         <f t="shared" ref="B27:I27" si="6">20*LOG(((B16)*B$6)/(B5*(B$17)), 10)</f>
-        <v>-0.15801519860075486</v>
+        <v>-9.8495120483395121E-2</v>
       </c>
       <c r="C27" s="2">
         <f t="shared" si="6"/>
-        <v>-9.4521815251235944E-3</v>
+        <v>-4.309407385632423E-2</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="6"/>
-        <v>-3.9929110859919729E-2</v>
+        <v>-6.3911192886027354E-2</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="6"/>
-        <v>-5.1802610352136208E-2</v>
+        <v>-5.6214026202694105E-2</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="6"/>
-        <v>-2.8470987591029413E-2</v>
+        <v>-5.7661564756208206E-2</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="6"/>
-        <v>-0.10932617866061028</v>
+        <v>-6.9782337642626077E-2</v>
       </c>
       <c r="H27" s="2">
         <f t="shared" si="6"/>
-        <v>2.5601075183208543E-2</v>
+        <v>1.8277064370483046E-2</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="6"/>
-        <v>-5.016582602582173E-2</v>
+        <v>2.7735815826397489E-2</v>
       </c>
       <c r="M27" s="3">
-        <v>1.4641395E-2</v>
+        <v>1.4656371E-2</v>
       </c>
       <c r="N27" s="3">
-        <v>1.4792606999999999E-2</v>
+        <v>1.4689580000000001E-2</v>
       </c>
       <c r="O27" s="3">
-        <v>1.4695919E-2</v>
+        <v>1.4700311000000001E-2</v>
       </c>
       <c r="P27" s="3">
-        <v>1.4671152E-2</v>
+        <v>1.4688962E-2</v>
       </c>
       <c r="Q27" s="3">
-        <v>1.4683015000000001E-2</v>
+        <v>1.4722381999999999E-2</v>
       </c>
       <c r="R27" s="3">
-        <v>1.466275E-2</v>
+        <v>1.4728161E-2</v>
       </c>
       <c r="S27" s="3">
-        <v>1.47735E-2</v>
+        <v>1.4833964999999999E-2</v>
       </c>
       <c r="T27" s="3">
-        <v>1.4697029E-2</v>
+        <v>1.4792021000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -2071,28 +2071,28 @@
         <v>0</v>
       </c>
       <c r="M28" s="3">
-        <v>1.4925163999999999E-2</v>
+        <v>1.4940078000000001E-2</v>
       </c>
       <c r="N28" s="3">
-        <v>1.490814E-2</v>
+        <v>1.4903112E-2</v>
       </c>
       <c r="O28" s="3">
-        <v>1.4847898999999999E-2</v>
+        <v>1.4896120000000001E-2</v>
       </c>
       <c r="P28" s="3">
-        <v>1.4876749999999999E-2</v>
+        <v>1.4899880000000001E-2</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.4882256E-2</v>
+        <v>1.4895815E-2</v>
       </c>
       <c r="R28" s="3">
-        <v>1.4855302000000001E-2</v>
+        <v>1.4916688000000001E-2</v>
       </c>
       <c r="S28" s="3">
-        <v>1.4888268E-2</v>
+        <v>1.4942001E-2</v>
       </c>
       <c r="T28" s="3">
-        <v>1.4903115E-2</v>
+        <v>1.4939419000000001E-2</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -2101,59 +2101,59 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29:I29" si="8">20*LOG(((B18)*B$6)/(B7*(B$17)), 10)</f>
-        <v>-8.1713497966003287E-2</v>
+        <v>-6.724316632820479E-2</v>
       </c>
       <c r="C29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.17567003636583928</v>
+        <v>-0.17028685244371955</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.14164949009851607</v>
+        <v>-0.1539551202770901</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="8"/>
-        <v>-8.8016565146174994E-2</v>
+        <v>-6.9981217836276199E-2</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.12432654782394886</v>
+        <v>-0.14847799092633257</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.10324106514750692</v>
+        <v>-0.16832857736849083</v>
       </c>
       <c r="H29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.1466369274411341</v>
+        <v>-0.15866279422493373</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="8"/>
-        <v>-0.14245068181638851</v>
+        <v>-0.17949301258916359</v>
       </c>
       <c r="M29" s="3">
-        <v>1.4766206E-2</v>
+        <v>1.4722702000000001E-2</v>
       </c>
       <c r="N29" s="3">
-        <v>1.4670516E-2</v>
+        <v>1.4605903E-2</v>
       </c>
       <c r="O29" s="3">
-        <v>1.4656508E-2</v>
+        <v>1.4687578E-2</v>
       </c>
       <c r="P29" s="3">
-        <v>1.4688618000000001E-2</v>
+        <v>1.474457E-2</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.4647568E-2</v>
+        <v>1.4672409000000001E-2</v>
       </c>
       <c r="R29" s="3">
-        <v>1.4706597E-2</v>
+        <v>1.4688984E-2</v>
       </c>
       <c r="S29" s="3">
-        <v>1.4677529E-2</v>
+        <v>1.4689661E-2</v>
       </c>
       <c r="T29" s="3">
-        <v>1.4668687E-2</v>
+        <v>1.4645182E-2</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2162,59 +2162,59 @@
       </c>
       <c r="B30" s="2">
         <f t="shared" ref="B30:I30" si="9">20*LOG(((B19)*B$6)/(B8*(B$17)), 10)</f>
-        <v>-0.12108424675943605</v>
+        <v>-0.13919034560425678</v>
       </c>
       <c r="C30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.28395832673165861</v>
+        <v>-0.29906876733208182</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.26507193706097654</v>
+        <v>-0.281851035120883</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.11545991753305658</v>
+        <v>-8.0054758008378218E-2</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.27192938203339645</v>
+        <v>-0.25392265420455379</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.19009634359910116</v>
+        <v>-0.27556551864521317</v>
       </c>
       <c r="H30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.25055269966333671</v>
+        <v>-0.24278145555357367</v>
       </c>
       <c r="I30" s="2">
         <f t="shared" si="9"/>
-        <v>-0.19599096353314246</v>
+        <v>-0.31804338314418445</v>
       </c>
       <c r="M30" s="3">
-        <v>1.4539389999999999E-2</v>
+        <v>1.4537194999999999E-2</v>
       </c>
       <c r="N30" s="3">
-        <v>1.4393131E-2</v>
+        <v>1.4425596000000001E-2</v>
       </c>
       <c r="O30" s="3">
-        <v>1.4454369E-2</v>
+        <v>1.4420534E-2</v>
       </c>
       <c r="P30" s="3">
-        <v>1.4580408E-2</v>
+        <v>1.4598710000000001E-2</v>
       </c>
       <c r="Q30" s="3">
-        <v>1.4406587E-2</v>
+        <v>1.4435475999999999E-2</v>
       </c>
       <c r="R30" s="3">
-        <v>1.451565E-2</v>
+        <v>1.4439664E-2</v>
       </c>
       <c r="S30" s="3">
-        <v>1.4451637999999999E-2</v>
+        <v>1.4436869999999999E-2</v>
       </c>
       <c r="T30" s="3">
-        <v>1.4554111999999999E-2</v>
+        <v>1.4366103999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -2223,59 +2223,59 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" ref="B31:I31" si="10">20*LOG(((B20)*B$6)/(B9*(B$17)), 10)</f>
-        <v>-0.51547030331790711</v>
+        <v>-0.50022317420723517</v>
       </c>
       <c r="C31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.66809142650989128</v>
+        <v>-0.63297739769491146</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.61033623787013713</v>
+        <v>-0.63517861293090505</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.42737140594206013</v>
+        <v>-0.43412412662636374</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.62302425190445465</v>
+        <v>-0.5907537946298751</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.53625909138843453</v>
+        <v>-0.67976711585934535</v>
       </c>
       <c r="H31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.58347768306695058</v>
+        <v>-0.65732108099221265</v>
       </c>
       <c r="I31" s="2">
         <f t="shared" si="10"/>
-        <v>-0.51484454710816929</v>
+        <v>-0.68318106497763154</v>
       </c>
       <c r="M31" s="3">
-        <v>1.3876416000000001E-2</v>
+        <v>1.3874345E-2</v>
       </c>
       <c r="N31" s="3">
-        <v>1.3730727999999999E-2</v>
+        <v>1.3795257E-2</v>
       </c>
       <c r="O31" s="3">
-        <v>1.378098E-2</v>
+        <v>1.3789627E-2</v>
       </c>
       <c r="P31" s="3">
-        <v>1.404476E-2</v>
+        <v>1.4012739999999999E-2</v>
       </c>
       <c r="Q31" s="3">
-        <v>1.3730674E-2</v>
+        <v>1.3801658E-2</v>
       </c>
       <c r="R31" s="3">
-        <v>1.3871333E-2</v>
+        <v>1.3751288E-2</v>
       </c>
       <c r="S31" s="3">
-        <v>1.384909E-2</v>
+        <v>1.3805642999999999E-2</v>
       </c>
       <c r="T31" s="3">
-        <v>1.3953897999999999E-2</v>
+        <v>1.3707453E-2</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -2284,111 +2284,111 @@
       </c>
       <c r="B32" s="2">
         <f t="shared" ref="B32:I32" si="11">20*LOG(((B21)*B$6)/(B10*(B$17)), 10)</f>
-        <v>-2.2545269888378296</v>
+        <v>-2.3086245896261097</v>
       </c>
       <c r="C32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.4576433098595691</v>
+        <v>-2.3363074072849175</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.3102474305827765</v>
+        <v>-2.383837588874393</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.0082792300476706</v>
+        <v>-2.1027356859932094</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.363128615561588</v>
+        <v>-2.3201616210964069</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.2675816530691213</v>
+        <v>-2.4509203789359679</v>
       </c>
       <c r="H32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.236184999367834</v>
+        <v>-2.4013473382436485</v>
       </c>
       <c r="I32" s="2">
         <f t="shared" si="11"/>
-        <v>-2.1505462221511942</v>
+        <v>-2.4441425704195723</v>
       </c>
       <c r="M32" s="3">
-        <v>1.127977E-2</v>
+        <v>1.1209828999999999E-2</v>
       </c>
       <c r="N32" s="3">
-        <v>1.1121809E-2</v>
+        <v>1.1263472E-2</v>
       </c>
       <c r="O32" s="3">
-        <v>1.1278541E-2</v>
+        <v>1.1166921999999999E-2</v>
       </c>
       <c r="P32" s="3">
-        <v>1.1598567000000001E-2</v>
+        <v>1.1460118E-2</v>
       </c>
       <c r="Q32" s="3">
-        <v>1.12041E-2</v>
+        <v>1.1244463E-2</v>
       </c>
       <c r="R32" s="3">
-        <v>1.1327940999999999E-2</v>
+        <v>1.1107272E-2</v>
       </c>
       <c r="S32" s="3">
-        <v>1.1388987E-2</v>
+        <v>1.1206143999999999E-2</v>
       </c>
       <c r="T32" s="3">
-        <v>1.1515795000000001E-2</v>
+        <v>1.1116256E-2</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M33" s="3">
-        <v>1.5456351E-2</v>
+        <v>1.5364991E-2</v>
       </c>
       <c r="N33" s="3">
-        <v>1.5186470000000001E-2</v>
+        <v>1.5212253E-2</v>
       </c>
       <c r="O33" s="3">
-        <v>1.5170253E-2</v>
+        <v>1.5245514999999999E-2</v>
       </c>
       <c r="P33" s="3">
-        <v>1.5258571E-2</v>
+        <v>1.5310472E-2</v>
       </c>
       <c r="Q33" s="3">
-        <v>1.5220925E-2</v>
+        <v>1.5230541E-2</v>
       </c>
       <c r="R33" s="3">
-        <v>1.5265224000000001E-2</v>
+        <v>1.5342536E-2</v>
       </c>
       <c r="S33" s="3">
-        <v>1.5154994999999999E-2</v>
+        <v>1.5106544E-2</v>
       </c>
       <c r="T33" s="3">
-        <v>1.5214017999999999E-2</v>
+        <v>1.5176354E-2</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M34" s="3">
-        <v>1.5379199E-2</v>
+        <v>1.5263607E-2</v>
       </c>
       <c r="N34" s="3">
-        <v>1.5056742E-2</v>
+        <v>1.5078693000000001E-2</v>
       </c>
       <c r="O34" s="3">
-        <v>1.5084901E-2</v>
+        <v>1.5123292999999999E-2</v>
       </c>
       <c r="P34" s="3">
-        <v>1.5190164000000001E-2</v>
+        <v>1.5232614E-2</v>
       </c>
       <c r="Q34" s="3">
-        <v>1.5094196000000001E-2</v>
+        <v>1.5132318000000001E-2</v>
       </c>
       <c r="R34" s="3">
-        <v>1.5195800000000001E-2</v>
+        <v>1.5243675999999999E-2</v>
       </c>
       <c r="S34" s="3">
-        <v>1.504753E-2</v>
+        <v>1.5021514999999999E-2</v>
       </c>
       <c r="T34" s="3">
-        <v>1.5094394000000001E-2</v>
+        <v>1.5077962E-2</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -2404,28 +2404,28 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="M35" s="3">
-        <v>1.5373443000000001E-2</v>
+        <v>1.5291971E-2</v>
       </c>
       <c r="N35" s="3">
-        <v>1.5092080000000001E-2</v>
+        <v>1.5118056E-2</v>
       </c>
       <c r="O35" s="3">
-        <v>1.5114818E-2</v>
+        <v>1.5153069999999999E-2</v>
       </c>
       <c r="P35" s="3">
-        <v>1.5218784000000001E-2</v>
+        <v>1.5277394999999999E-2</v>
       </c>
       <c r="Q35" s="3">
-        <v>1.5115544E-2</v>
+        <v>1.5174701000000001E-2</v>
       </c>
       <c r="R35" s="3">
-        <v>1.5218046000000001E-2</v>
+        <v>1.5266620999999999E-2</v>
       </c>
       <c r="S35" s="3">
-        <v>1.5087816E-2</v>
+        <v>1.5092365999999999E-2</v>
       </c>
       <c r="T35" s="3">
-        <v>1.5121875E-2</v>
+        <v>1.5140532999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -2457,28 +2457,28 @@
         <v>8</v>
       </c>
       <c r="M36" s="3">
-        <v>1.5406510999999999E-2</v>
+        <v>1.5386696E-2</v>
       </c>
       <c r="N36" s="3">
-        <v>1.5250400000000001E-2</v>
+        <v>1.528419E-2</v>
       </c>
       <c r="O36" s="3">
-        <v>1.5250825000000001E-2</v>
+        <v>1.5296255999999999E-2</v>
       </c>
       <c r="P36" s="3">
-        <v>1.5326559E-2</v>
+        <v>1.5384824E-2</v>
       </c>
       <c r="Q36" s="3">
-        <v>1.5252496000000001E-2</v>
+        <v>1.531239E-2</v>
       </c>
       <c r="R36" s="3">
-        <v>1.5317608E-2</v>
+        <v>1.5371806E-2</v>
       </c>
       <c r="S36" s="3">
-        <v>1.5258776E-2</v>
+        <v>1.5277892E-2</v>
       </c>
       <c r="T36" s="3">
-        <v>1.5274411E-2</v>
+        <v>1.5328534E-2</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -2487,59 +2487,59 @@
       </c>
       <c r="B37" s="1">
         <f t="shared" ref="B37:I44" si="12">M17</f>
-        <v>1.5460606999999999E-2</v>
+        <v>1.537171E-2</v>
       </c>
       <c r="C37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5185120999999999E-2</v>
+        <v>1.5220595999999999E-2</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>1.51734E-2</v>
+        <v>1.525495E-2</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5256438000000001E-2</v>
+        <v>1.531502E-2</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5223633E-2</v>
+        <v>1.5240757000000001E-2</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5263499E-2</v>
+        <v>1.5349572000000001E-2</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5157435E-2</v>
+        <v>1.5112265999999999E-2</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="12"/>
-        <v>1.5210446000000001E-2</v>
+        <v>1.5186079E-2</v>
       </c>
       <c r="M37" s="3">
-        <v>1.5417923E-2</v>
+        <v>1.5416226999999999E-2</v>
       </c>
       <c r="N37" s="3">
-        <v>1.5326576999999999E-2</v>
+        <v>1.5356242000000001E-2</v>
       </c>
       <c r="O37" s="3">
-        <v>1.5325893E-2</v>
+        <v>1.5365182E-2</v>
       </c>
       <c r="P37" s="3">
-        <v>1.5367877E-2</v>
+        <v>1.5418064E-2</v>
       </c>
       <c r="Q37" s="3">
-        <v>1.5325834E-2</v>
+        <v>1.5372701000000001E-2</v>
       </c>
       <c r="R37" s="3">
-        <v>1.5358261E-2</v>
+        <v>1.5414761000000001E-2</v>
       </c>
       <c r="S37" s="3">
-        <v>1.5337750000000001E-2</v>
+        <v>1.5351508999999999E-2</v>
       </c>
       <c r="T37" s="3">
-        <v>1.5349091E-2</v>
+        <v>1.5399862E-2</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -2548,59 +2548,59 @@
       </c>
       <c r="B38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5388021E-2</v>
+        <v>1.5276534E-2</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5064731E-2</v>
+        <v>1.5087961E-2</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5090933000000001E-2</v>
+        <v>1.5130219E-2</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5193577999999999E-2</v>
+        <v>1.5238064000000001E-2</v>
       </c>
       <c r="F38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5099306E-2</v>
+        <v>1.5142933000000001E-2</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5197777000000001E-2</v>
+        <v>1.524578E-2</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5053834E-2</v>
+        <v>1.5029307E-2</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="12"/>
-        <v>1.5098501E-2</v>
+        <v>1.5083549999999999E-2</v>
       </c>
       <c r="M38" s="3">
-        <v>1.5422623999999999E-2</v>
+        <v>1.5432939E-2</v>
       </c>
       <c r="N38" s="3">
-        <v>1.5359256999999999E-2</v>
+        <v>1.5383913000000001E-2</v>
       </c>
       <c r="O38" s="3">
-        <v>1.5359533E-2</v>
+        <v>1.5398755E-2</v>
       </c>
       <c r="P38" s="3">
-        <v>1.5389976E-2</v>
+        <v>1.5435116E-2</v>
       </c>
       <c r="Q38" s="3">
-        <v>1.5360478E-2</v>
+        <v>1.5395997E-2</v>
       </c>
       <c r="R38" s="3">
-        <v>1.5382511E-2</v>
+        <v>1.5437895E-2</v>
       </c>
       <c r="S38" s="3">
-        <v>1.5375088E-2</v>
+        <v>1.5379514E-2</v>
       </c>
       <c r="T38" s="3">
-        <v>1.5383152000000001E-2</v>
+        <v>1.5430251000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -2609,59 +2609,59 @@
       </c>
       <c r="B39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5380532000000001E-2</v>
+        <v>1.5302912E-2</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5098355000000001E-2</v>
+        <v>1.5126651E-2</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5121018E-2</v>
+        <v>1.5161286E-2</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5226099999999999E-2</v>
+        <v>1.5284514000000001E-2</v>
       </c>
       <c r="F39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5116743E-2</v>
+        <v>1.5189166E-2</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5222526E-2</v>
+        <v>1.5273745E-2</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5093499E-2</v>
+        <v>1.5102295999999999E-2</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="12"/>
-        <v>1.5124186E-2</v>
+        <v>1.5153955E-2</v>
       </c>
       <c r="M39" s="3">
-        <v>1.5426034999999999E-2</v>
+        <v>1.5458361E-2</v>
       </c>
       <c r="N39" s="3">
-        <v>1.5373392E-2</v>
+        <v>1.5422467E-2</v>
       </c>
       <c r="O39" s="3">
-        <v>1.5372200000000001E-2</v>
+        <v>1.5435766E-2</v>
       </c>
       <c r="P39" s="3">
-        <v>1.5396236000000001E-2</v>
+        <v>1.5464623E-2</v>
       </c>
       <c r="Q39" s="3">
-        <v>1.5369041999999999E-2</v>
+        <v>1.5431321E-2</v>
       </c>
       <c r="R39" s="3">
-        <v>1.5391066E-2</v>
+        <v>1.5465848000000001E-2</v>
       </c>
       <c r="S39" s="3">
-        <v>1.5389130000000001E-2</v>
+        <v>1.5410093E-2</v>
       </c>
       <c r="T39" s="3">
-        <v>1.5398926E-2</v>
+        <v>1.5461403E-2</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -2670,59 +2670,59 @@
       </c>
       <c r="B40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5417725E-2</v>
+        <v>1.54001E-2</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5260350000000001E-2</v>
+        <v>1.5298915E-2</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5265997E-2</v>
+        <v>1.5308646E-2</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5337414000000001E-2</v>
+        <v>1.5401229000000001E-2</v>
       </c>
       <c r="F40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5259754E-2</v>
+        <v>1.5331348E-2</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5325841E-2</v>
+        <v>1.5385831000000001E-2</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="12"/>
-        <v>1.5267584000000001E-2</v>
+        <v>1.5289560000000001E-2</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="12"/>
-        <v>1.528624E-2</v>
+        <v>1.5340433000000001E-2</v>
       </c>
       <c r="M40" s="3">
-        <v>1.5442566E-2</v>
+        <v>1.5474115E-2</v>
       </c>
       <c r="N40" s="3">
-        <v>1.5396356E-2</v>
+        <v>1.5436159E-2</v>
       </c>
       <c r="O40" s="3">
-        <v>1.5397286E-2</v>
+        <v>1.5453435E-2</v>
       </c>
       <c r="P40" s="3">
-        <v>1.5415491999999999E-2</v>
+        <v>1.5475342E-2</v>
       </c>
       <c r="Q40" s="3">
-        <v>1.5393258999999999E-2</v>
+        <v>1.5446117000000001E-2</v>
       </c>
       <c r="R40" s="3">
-        <v>1.5412945000000001E-2</v>
+        <v>1.5482644E-2</v>
       </c>
       <c r="S40" s="3">
-        <v>1.5411213999999999E-2</v>
+        <v>1.543079E-2</v>
       </c>
       <c r="T40" s="3">
-        <v>1.5420672E-2</v>
+        <v>1.5478779999999999E-2</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -2731,59 +2731,59 @@
       </c>
       <c r="B41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5429371000000001E-2</v>
+        <v>1.5430304000000001E-2</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5339591E-2</v>
+        <v>1.5369900000000001E-2</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5337886E-2</v>
+        <v>1.5375969999999999E-2</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5381308999999999E-2</v>
+        <v>1.5434552000000001E-2</v>
       </c>
       <c r="F41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5336654E-2</v>
+        <v>1.5383864000000001E-2</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5372050999999999E-2</v>
+        <v>1.5428333000000001E-2</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5352174999999999E-2</v>
+        <v>1.5360229E-2</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="12"/>
-        <v>1.5363714000000001E-2</v>
+        <v>1.5415059E-2</v>
       </c>
       <c r="M41" s="3">
-        <v>4.8893674999999998E-2</v>
+        <v>4.8829499999999998E-2</v>
       </c>
       <c r="N41" s="3">
-        <v>4.8400595999999997E-2</v>
+        <v>4.8345774000000001E-2</v>
       </c>
       <c r="O41" s="3">
-        <v>4.8553981000000003E-2</v>
+        <v>4.8113695999999997E-2</v>
       </c>
       <c r="P41" s="3">
-        <v>4.8901728999999998E-2</v>
+        <v>4.8806503000000001E-2</v>
       </c>
       <c r="Q41" s="3">
-        <v>4.8554952999999998E-2</v>
+        <v>4.8506524000000002E-2</v>
       </c>
       <c r="R41" s="3">
-        <v>4.8802707000000001E-2</v>
+        <v>4.8574570999999997E-2</v>
       </c>
       <c r="S41" s="3">
-        <v>4.8563343000000002E-2</v>
+        <v>4.8942260000000001E-2</v>
       </c>
       <c r="T41" s="3">
-        <v>4.8299680999999997E-2</v>
+        <v>4.9176365E-2</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -2792,59 +2792,59 @@
       </c>
       <c r="B42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5438189E-2</v>
+        <v>1.5446207999999999E-2</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5372445E-2</v>
+        <v>1.5399919999999999E-2</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5371027000000001E-2</v>
+        <v>1.5410881E-2</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5398904E-2</v>
+        <v>1.5451395E-2</v>
       </c>
       <c r="F42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5368715E-2</v>
+        <v>1.5409291E-2</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5396452999999999E-2</v>
+        <v>1.5451507999999999E-2</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5389172E-2</v>
+        <v>1.5392539E-2</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="12"/>
-        <v>1.5395835E-2</v>
+        <v>1.5444571000000001E-2</v>
       </c>
       <c r="M42" s="3">
-        <v>6.7720040999999995E-2</v>
+        <v>6.7165694999999997E-2</v>
       </c>
       <c r="N42" s="3">
-        <v>6.7619525E-2</v>
+        <v>6.7156515999999999E-2</v>
       </c>
       <c r="O42" s="3">
-        <v>6.7129247000000003E-2</v>
+        <v>6.6872925E-2</v>
       </c>
       <c r="P42" s="3">
-        <v>6.7505783999999999E-2</v>
+        <v>6.7651956999999999E-2</v>
       </c>
       <c r="Q42" s="3">
-        <v>6.7328595000000005E-2</v>
+        <v>6.7152492999999994E-2</v>
       </c>
       <c r="R42" s="3">
-        <v>6.7247323999999997E-2</v>
+        <v>6.7042432999999998E-2</v>
       </c>
       <c r="S42" s="3">
-        <v>6.7851111000000006E-2</v>
+        <v>6.7812501999999997E-2</v>
       </c>
       <c r="T42" s="3">
-        <v>6.7479364999999999E-2</v>
+        <v>6.8044059000000004E-2</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -2853,59 +2853,59 @@
       </c>
       <c r="B43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5438093E-2</v>
+        <v>1.5476652E-2</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5384689999999999E-2</v>
+        <v>1.5433664999999999E-2</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5387779000000001E-2</v>
+        <v>1.5447400999999999E-2</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5409419000000001E-2</v>
+        <v>1.5478057999999999E-2</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5384178E-2</v>
+        <v>1.54436E-2</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5408744E-2</v>
+        <v>1.5481340999999999E-2</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5400811E-2</v>
+        <v>1.5429965E-2</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="12"/>
-        <v>1.5408893E-2</v>
+        <v>1.5469368000000001E-2</v>
       </c>
       <c r="M43" s="3">
-        <v>7.3252185999999997E-2</v>
+        <v>7.3087201000000004E-2</v>
       </c>
       <c r="N43" s="3">
-        <v>7.3296040000000007E-2</v>
+        <v>7.3272184000000004E-2</v>
       </c>
       <c r="O43" s="3">
-        <v>7.2994805999999995E-2</v>
+        <v>7.2809674000000005E-2</v>
       </c>
       <c r="P43" s="3">
-        <v>7.3272466999999994E-2</v>
+        <v>7.3401794000000006E-2</v>
       </c>
       <c r="Q43" s="3">
-        <v>7.2891787E-2</v>
+        <v>7.3207773000000004E-2</v>
       </c>
       <c r="R43" s="3">
-        <v>7.2940654999999993E-2</v>
+        <v>7.2836310000000001E-2</v>
       </c>
       <c r="S43" s="3">
-        <v>7.3257751999999995E-2</v>
+        <v>7.3530159999999997E-2</v>
       </c>
       <c r="T43" s="3">
-        <v>7.3206119E-2</v>
+        <v>7.3546349999999996E-2</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -2914,85 +2914,85 @@
       </c>
       <c r="B44" s="1">
         <f t="shared" si="12"/>
-        <v>1.545443E-2</v>
+        <v>1.5481933999999999E-2</v>
       </c>
       <c r="C44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5409826999999999E-2</v>
+        <v>1.5444373000000001E-2</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5409910000000001E-2</v>
+        <v>1.5460544E-2</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5426683E-2</v>
+        <v>1.5483986E-2</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5407743999999999E-2</v>
+        <v>1.5453415999999999E-2</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5426611999999999E-2</v>
+        <v>1.5491134E-2</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5426082000000001E-2</v>
+        <v>1.543623E-2</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="12"/>
-        <v>1.5429859000000001E-2</v>
+        <v>1.548588E-2</v>
       </c>
       <c r="M44" s="3">
-        <v>7.4525810999999997E-2</v>
+        <v>7.4561163999999999E-2</v>
       </c>
       <c r="N44" s="3">
-        <v>7.3929942999999998E-2</v>
+        <v>7.4071004999999995E-2</v>
       </c>
       <c r="O44" s="3">
-        <v>7.3795400999999997E-2</v>
+        <v>7.4062839000000005E-2</v>
       </c>
       <c r="P44" s="3">
-        <v>7.4281535999999995E-2</v>
+        <v>7.4305385000000002E-2</v>
       </c>
       <c r="Q44" s="3">
-        <v>7.3930033000000006E-2</v>
+        <v>7.4136964999999999E-2</v>
       </c>
       <c r="R44" s="3">
-        <v>7.3860325000000004E-2</v>
+        <v>7.3857188000000004E-2</v>
       </c>
       <c r="S44" s="3">
-        <v>7.3983974999999993E-2</v>
+        <v>7.4293256000000002E-2</v>
       </c>
       <c r="T44" s="3">
-        <v>7.4154221000000006E-2</v>
+        <v>7.4216239000000003E-2</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M45" s="3">
-        <v>7.4060424999999999E-2</v>
+        <v>7.3737345999999995E-2</v>
       </c>
       <c r="N45" s="3">
-        <v>7.2829335999999995E-2</v>
+        <v>7.3081136000000005E-2</v>
       </c>
       <c r="O45" s="3">
-        <v>7.2868265000000002E-2</v>
+        <v>7.3108121999999998E-2</v>
       </c>
       <c r="P45" s="3">
-        <v>7.3500827000000005E-2</v>
+        <v>7.3708676000000001E-2</v>
       </c>
       <c r="Q45" s="3">
-        <v>7.2823256000000003E-2</v>
+        <v>7.3098927999999994E-2</v>
       </c>
       <c r="R45" s="3">
-        <v>7.3190346000000003E-2</v>
+        <v>7.3057324000000007E-2</v>
       </c>
       <c r="S45" s="3">
-        <v>7.2956398000000006E-2</v>
+        <v>7.3199920000000002E-2</v>
       </c>
       <c r="T45" s="3">
-        <v>7.3363669000000006E-2</v>
+        <v>7.2974025999999997E-2</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -3008,28 +3008,28 @@
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="M46" s="3">
-        <v>7.3310606E-2</v>
+        <v>7.3021113999999998E-2</v>
       </c>
       <c r="N46" s="3">
-        <v>7.1946762999999997E-2</v>
+        <v>7.2269976E-2</v>
       </c>
       <c r="O46" s="3">
-        <v>7.2069384E-2</v>
+        <v>7.2029917999999998E-2</v>
       </c>
       <c r="P46" s="3">
-        <v>7.3216870000000003E-2</v>
+        <v>7.3393299999999995E-2</v>
       </c>
       <c r="Q46" s="3">
-        <v>7.2059235999999999E-2</v>
+        <v>7.2220184000000007E-2</v>
       </c>
       <c r="R46" s="3">
-        <v>7.2695039000000003E-2</v>
+        <v>7.1956596999999997E-2</v>
       </c>
       <c r="S46" s="3">
-        <v>7.2240911000000005E-2</v>
+        <v>7.2313681000000005E-2</v>
       </c>
       <c r="T46" s="3">
-        <v>7.2916083000000007E-2</v>
+        <v>7.1914381999999999E-2</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -3061,28 +3061,28 @@
         <v>8</v>
       </c>
       <c r="M47" s="3">
-        <v>7.0239446999999997E-2</v>
+        <v>7.0084258999999996E-2</v>
       </c>
       <c r="N47" s="3">
-        <v>6.8778678999999995E-2</v>
+        <v>6.9415346000000003E-2</v>
       </c>
       <c r="O47" s="3">
-        <v>6.9237999999999994E-2</v>
+        <v>6.9206662000000002E-2</v>
       </c>
       <c r="P47" s="3">
-        <v>7.0637718000000002E-2</v>
+        <v>7.0685713999999997E-2</v>
       </c>
       <c r="Q47" s="3">
-        <v>6.9006965000000003E-2</v>
+        <v>6.9369897E-2</v>
       </c>
       <c r="R47" s="3">
-        <v>6.9739640000000006E-2</v>
+        <v>6.8763234000000006E-2</v>
       </c>
       <c r="S47" s="3">
-        <v>6.9361254999999997E-2</v>
+        <v>6.9219053000000003E-2</v>
       </c>
       <c r="T47" s="3">
-        <v>7.0175751999999994E-2</v>
+        <v>6.8996452E-2</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -3091,59 +3091,59 @@
       </c>
       <c r="B48" s="1">
         <f t="shared" ref="B48:I55" si="13">M25</f>
-        <v>9.7773419999999996E-3</v>
+        <v>9.7392220000000005E-3</v>
       </c>
       <c r="C48" s="1">
         <f t="shared" si="13"/>
-        <v>9.7637880000000007E-3</v>
+        <v>9.6926679999999998E-3</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" si="13"/>
-        <v>9.8411220000000008E-3</v>
+        <v>9.6832910000000001E-3</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="13"/>
-        <v>9.8550749999999996E-3</v>
+        <v>9.8253079999999996E-3</v>
       </c>
       <c r="F48" s="1">
         <f t="shared" si="13"/>
-        <v>9.7710999999999996E-3</v>
+        <v>9.7569849999999993E-3</v>
       </c>
       <c r="G48" s="1">
         <f t="shared" si="13"/>
-        <v>9.8427540000000004E-3</v>
+        <v>9.8408239999999998E-3</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="13"/>
-        <v>9.8370479999999993E-3</v>
+        <v>9.9364910000000004E-3</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="13"/>
-        <v>9.7172249999999995E-3</v>
+        <v>9.8244449999999994E-3</v>
       </c>
       <c r="M48" s="3">
-        <v>5.7371872999999997E-2</v>
+        <v>5.6911695999999998E-2</v>
       </c>
       <c r="N48" s="3">
-        <v>5.6134224000000003E-2</v>
+        <v>5.7009707999999999E-2</v>
       </c>
       <c r="O48" s="3">
-        <v>5.6891110000000002E-2</v>
+        <v>5.6477338000000002E-2</v>
       </c>
       <c r="P48" s="3">
-        <v>5.8820426000000002E-2</v>
+        <v>5.8397401000000002E-2</v>
       </c>
       <c r="Q48" s="3">
-        <v>5.6537110000000002E-2</v>
+        <v>5.6859634999999999E-2</v>
       </c>
       <c r="R48" s="3">
-        <v>5.7187389999999998E-2</v>
+        <v>5.5951099999999997E-2</v>
       </c>
       <c r="S48" s="3">
-        <v>5.7378247E-2</v>
+        <v>5.6663367999999999E-2</v>
       </c>
       <c r="T48" s="3">
-        <v>5.8160684999999997E-2</v>
+        <v>5.6356705999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -3152,59 +3152,59 @@
       </c>
       <c r="B49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3472259E-2</v>
+        <v>1.3521164E-2</v>
       </c>
       <c r="C49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3613867999999999E-2</v>
+        <v>1.3509754000000001E-2</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3554066E-2</v>
+        <v>1.3502767000000001E-2</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3572486999999999E-2</v>
+        <v>1.3554392E-2</v>
       </c>
       <c r="F49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3506873000000001E-2</v>
+        <v>1.3512667000000001E-2</v>
       </c>
       <c r="G49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3530873000000001E-2</v>
+        <v>1.3557862E-2</v>
       </c>
       <c r="H49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3602635E-2</v>
+        <v>1.3656359E-2</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="13"/>
-        <v>1.3586007000000001E-2</v>
+        <v>1.3682948E-2</v>
       </c>
       <c r="M49" s="6">
-        <v>1.5458105999999999E-2</v>
+        <v>1.536471E-2</v>
       </c>
       <c r="N49" s="6">
-        <v>1.518369E-2</v>
+        <v>1.5210559E-2</v>
       </c>
       <c r="O49" s="6">
-        <v>1.5167762E-2</v>
+        <v>1.5244013000000001E-2</v>
       </c>
       <c r="P49" s="6">
-        <v>1.5258224000000001E-2</v>
+        <v>1.5310315E-2</v>
       </c>
       <c r="Q49" s="6">
-        <v>1.522163E-2</v>
+        <v>1.5226285000000001E-2</v>
       </c>
       <c r="R49" s="6">
-        <v>1.5264764E-2</v>
+        <v>1.5344086E-2</v>
       </c>
       <c r="S49" s="6">
-        <v>1.5151697E-2</v>
+        <v>1.5106509000000001E-2</v>
       </c>
       <c r="T49" s="6">
-        <v>1.5213450999999999E-2</v>
+        <v>1.5178832E-2</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -3213,59 +3213,59 @@
       </c>
       <c r="B50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4641395E-2</v>
+        <v>1.4656371E-2</v>
       </c>
       <c r="C50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4792606999999999E-2</v>
+        <v>1.4689580000000001E-2</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4695919E-2</v>
+        <v>1.4700311000000001E-2</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4671152E-2</v>
+        <v>1.4688962E-2</v>
       </c>
       <c r="F50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4683015000000001E-2</v>
+        <v>1.4722381999999999E-2</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="13"/>
-        <v>1.466275E-2</v>
+        <v>1.4728161E-2</v>
       </c>
       <c r="H50" s="1">
         <f t="shared" si="13"/>
-        <v>1.47735E-2</v>
+        <v>1.4833964999999999E-2</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="13"/>
-        <v>1.4697029E-2</v>
+        <v>1.4792021000000001E-2</v>
       </c>
       <c r="M50" s="6">
-        <v>1.5376584E-2</v>
+        <v>1.5266025000000001E-2</v>
       </c>
       <c r="N50" s="6">
-        <v>1.5061064000000001E-2</v>
+        <v>1.5074218E-2</v>
       </c>
       <c r="O50" s="6">
-        <v>1.5079922000000001E-2</v>
+        <v>1.5118825000000001E-2</v>
       </c>
       <c r="P50" s="6">
-        <v>1.5188978000000001E-2</v>
+        <v>1.5226236000000001E-2</v>
       </c>
       <c r="Q50" s="6">
-        <v>1.5093535999999999E-2</v>
+        <v>1.5128496E-2</v>
       </c>
       <c r="R50" s="6">
-        <v>1.5197492999999999E-2</v>
+        <v>1.5237949000000001E-2</v>
       </c>
       <c r="S50" s="6">
-        <v>1.5047131E-2</v>
+        <v>1.5021141E-2</v>
       </c>
       <c r="T50" s="6">
-        <v>1.5096561999999999E-2</v>
+        <v>1.507767E-2</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -3274,59 +3274,59 @@
       </c>
       <c r="B51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4925163999999999E-2</v>
+        <v>1.4940078000000001E-2</v>
       </c>
       <c r="C51" s="1">
         <f t="shared" si="13"/>
-        <v>1.490814E-2</v>
+        <v>1.4903112E-2</v>
       </c>
       <c r="D51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4847898999999999E-2</v>
+        <v>1.4896120000000001E-2</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4876749999999999E-2</v>
+        <v>1.4899880000000001E-2</v>
       </c>
       <c r="F51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4882256E-2</v>
+        <v>1.4895815E-2</v>
       </c>
       <c r="G51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4855302000000001E-2</v>
+        <v>1.4916688000000001E-2</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4888268E-2</v>
+        <v>1.4942001E-2</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="13"/>
-        <v>1.4903115E-2</v>
+        <v>1.4939419000000001E-2</v>
       </c>
       <c r="M51" s="6">
-        <v>1.5368214999999999E-2</v>
+        <v>1.5284743999999999E-2</v>
       </c>
       <c r="N51" s="6">
-        <v>1.508789E-2</v>
+        <v>1.5115571E-2</v>
       </c>
       <c r="O51" s="6">
-        <v>1.5111299E-2</v>
+        <v>1.5146227999999999E-2</v>
       </c>
       <c r="P51" s="6">
-        <v>1.5212384000000001E-2</v>
+        <v>1.5269825000000001E-2</v>
       </c>
       <c r="Q51" s="6">
-        <v>1.5112672000000001E-2</v>
+        <v>1.5171158000000001E-2</v>
       </c>
       <c r="R51" s="6">
-        <v>1.5215317000000001E-2</v>
+        <v>1.5260098999999999E-2</v>
       </c>
       <c r="S51" s="6">
-        <v>1.5086145E-2</v>
+        <v>1.5084669E-2</v>
       </c>
       <c r="T51" s="6">
-        <v>1.5120635E-2</v>
+        <v>1.5136441E-2</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -3335,59 +3335,59 @@
       </c>
       <c r="B52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4766206E-2</v>
+        <v>1.4722702000000001E-2</v>
       </c>
       <c r="C52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4670516E-2</v>
+        <v>1.4605903E-2</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4656508E-2</v>
+        <v>1.4687578E-2</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4688618000000001E-2</v>
+        <v>1.474457E-2</v>
       </c>
       <c r="F52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4647568E-2</v>
+        <v>1.4672409000000001E-2</v>
       </c>
       <c r="G52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4706597E-2</v>
+        <v>1.4688984E-2</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4677529E-2</v>
+        <v>1.4689661E-2</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="13"/>
-        <v>1.4668687E-2</v>
+        <v>1.4645182E-2</v>
       </c>
       <c r="M52" s="6">
-        <v>1.5399909E-2</v>
+        <v>1.5379573000000001E-2</v>
       </c>
       <c r="N52" s="6">
-        <v>1.5244442E-2</v>
+        <v>1.5278363999999999E-2</v>
       </c>
       <c r="O52" s="6">
-        <v>1.5247925000000001E-2</v>
+        <v>1.5288717E-2</v>
       </c>
       <c r="P52" s="6">
-        <v>1.5319309999999999E-2</v>
+        <v>1.5377686E-2</v>
       </c>
       <c r="Q52" s="6">
-        <v>1.524943E-2</v>
+        <v>1.5311058000000001E-2</v>
       </c>
       <c r="R52" s="6">
-        <v>1.5309053E-2</v>
+        <v>1.5362224000000001E-2</v>
       </c>
       <c r="S52" s="6">
-        <v>1.5255037000000001E-2</v>
+        <v>1.5269631000000001E-2</v>
       </c>
       <c r="T52" s="6">
-        <v>1.5268432E-2</v>
+        <v>1.5322463999999999E-2</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -3396,59 +3396,59 @@
       </c>
       <c r="B53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4539389999999999E-2</v>
+        <v>1.4537194999999999E-2</v>
       </c>
       <c r="C53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4393131E-2</v>
+        <v>1.4425596000000001E-2</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4454369E-2</v>
+        <v>1.4420534E-2</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4580408E-2</v>
+        <v>1.4598710000000001E-2</v>
       </c>
       <c r="F53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4406587E-2</v>
+        <v>1.4435475999999999E-2</v>
       </c>
       <c r="G53" s="1">
         <f t="shared" si="13"/>
-        <v>1.451565E-2</v>
+        <v>1.4439664E-2</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4451637999999999E-2</v>
+        <v>1.4436869999999999E-2</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="13"/>
-        <v>1.4554111999999999E-2</v>
+        <v>1.4366103999999999E-2</v>
       </c>
       <c r="M53" s="6">
-        <v>1.5408434E-2</v>
+        <v>1.5408354000000001E-2</v>
       </c>
       <c r="N53" s="6">
-        <v>1.5317936000000001E-2</v>
+        <v>1.5349323E-2</v>
       </c>
       <c r="O53" s="6">
-        <v>1.5318429E-2</v>
+        <v>1.5355280000000001E-2</v>
       </c>
       <c r="P53" s="6">
-        <v>1.5362005E-2</v>
+        <v>1.5411048E-2</v>
       </c>
       <c r="Q53" s="6">
-        <v>1.5319121999999999E-2</v>
+        <v>1.5360232E-2</v>
       </c>
       <c r="R53" s="6">
-        <v>1.5354639999999999E-2</v>
+        <v>1.5405106999999999E-2</v>
       </c>
       <c r="S53" s="6">
-        <v>1.5335807999999999E-2</v>
+        <v>1.5340397E-2</v>
       </c>
       <c r="T53" s="6">
-        <v>1.534428E-2</v>
+        <v>1.5388737E-2</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -3457,59 +3457,59 @@
       </c>
       <c r="B54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3876416000000001E-2</v>
+        <v>1.3874345E-2</v>
       </c>
       <c r="C54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3730727999999999E-2</v>
+        <v>1.3795257E-2</v>
       </c>
       <c r="D54" s="1">
         <f t="shared" si="13"/>
-        <v>1.378098E-2</v>
+        <v>1.3789627E-2</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="13"/>
-        <v>1.404476E-2</v>
+        <v>1.4012739999999999E-2</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3730674E-2</v>
+        <v>1.3801658E-2</v>
       </c>
       <c r="G54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3871333E-2</v>
+        <v>1.3751288E-2</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="13"/>
-        <v>1.384909E-2</v>
+        <v>1.3805642999999999E-2</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="13"/>
-        <v>1.3953897999999999E-2</v>
+        <v>1.3707453E-2</v>
       </c>
       <c r="M54" s="6">
-        <v>1.5420224E-2</v>
+        <v>1.5419867E-2</v>
       </c>
       <c r="N54" s="6">
-        <v>1.5356537999999999E-2</v>
+        <v>1.5376762E-2</v>
       </c>
       <c r="O54" s="6">
-        <v>1.5353924E-2</v>
+        <v>1.5389053999999999E-2</v>
       </c>
       <c r="P54" s="6">
-        <v>1.5384284999999999E-2</v>
+        <v>1.5424853000000001E-2</v>
       </c>
       <c r="Q54" s="6">
-        <v>1.5356013999999999E-2</v>
+        <v>1.5387091E-2</v>
       </c>
       <c r="R54" s="6">
-        <v>1.5376562999999999E-2</v>
+        <v>1.5423394E-2</v>
       </c>
       <c r="S54" s="6">
-        <v>1.5371108E-2</v>
+        <v>1.5369657E-2</v>
       </c>
       <c r="T54" s="6">
-        <v>1.5375493E-2</v>
+        <v>1.5419377999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -3518,85 +3518,85 @@
       </c>
       <c r="B55" s="1">
         <f t="shared" si="13"/>
-        <v>1.127977E-2</v>
+        <v>1.1209828999999999E-2</v>
       </c>
       <c r="C55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1121809E-2</v>
+        <v>1.1263472E-2</v>
       </c>
       <c r="D55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1278541E-2</v>
+        <v>1.1166921999999999E-2</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1598567000000001E-2</v>
+        <v>1.1460118E-2</v>
       </c>
       <c r="F55" s="1">
         <f t="shared" si="13"/>
-        <v>1.12041E-2</v>
+        <v>1.1244463E-2</v>
       </c>
       <c r="G55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1327940999999999E-2</v>
+        <v>1.1107272E-2</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1388987E-2</v>
+        <v>1.1206143999999999E-2</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="13"/>
-        <v>1.1515795000000001E-2</v>
+        <v>1.1116256E-2</v>
       </c>
       <c r="M55" s="6">
-        <v>1.5419894999999999E-2</v>
+        <v>1.5449305999999999E-2</v>
       </c>
       <c r="N55" s="6">
-        <v>1.5366869999999999E-2</v>
+        <v>1.5412252E-2</v>
       </c>
       <c r="O55" s="6">
-        <v>1.5362082000000001E-2</v>
+        <v>1.5422458E-2</v>
       </c>
       <c r="P55" s="6">
-        <v>1.5388957E-2</v>
+        <v>1.5446856E-2</v>
       </c>
       <c r="Q55" s="6">
-        <v>1.5367093E-2</v>
+        <v>1.5416503999999999E-2</v>
       </c>
       <c r="R55" s="6">
-        <v>1.5391864E-2</v>
+        <v>1.545065E-2</v>
       </c>
       <c r="S55" s="6">
-        <v>1.5381381E-2</v>
+        <v>1.5400581999999999E-2</v>
       </c>
       <c r="T55" s="6">
-        <v>1.5389238E-2</v>
+        <v>1.5447344E-2</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M56" s="6">
-        <v>1.5434586E-2</v>
+        <v>1.5461569999999999E-2</v>
       </c>
       <c r="N56" s="6">
-        <v>1.5390067E-2</v>
+        <v>1.5424524E-2</v>
       </c>
       <c r="O56" s="6">
-        <v>1.5389442999999999E-2</v>
+        <v>1.5440285999999999E-2</v>
       </c>
       <c r="P56" s="6">
-        <v>1.5407472E-2</v>
+        <v>1.5463564000000001E-2</v>
       </c>
       <c r="Q56" s="6">
-        <v>1.5389874E-2</v>
+        <v>1.5432955E-2</v>
       </c>
       <c r="R56" s="6">
-        <v>1.5408707000000001E-2</v>
+        <v>1.5467687000000001E-2</v>
       </c>
       <c r="S56" s="6">
-        <v>1.5404196E-2</v>
+        <v>1.5418434999999999E-2</v>
       </c>
       <c r="T56" s="6">
-        <v>1.5411829E-2</v>
+        <v>1.5466616000000001E-2</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -3612,28 +3612,28 @@
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="M57" s="6">
-        <v>4.9540217999999997E-2</v>
+        <v>4.9426649000000003E-2</v>
       </c>
       <c r="N57" s="6">
-        <v>4.9637806E-2</v>
+        <v>4.8979606000000002E-2</v>
       </c>
       <c r="O57" s="6">
-        <v>4.9648370999999997E-2</v>
+        <v>4.9054648999999999E-2</v>
       </c>
       <c r="P57" s="6">
-        <v>4.9901268999999998E-2</v>
+        <v>4.9213156000000001E-2</v>
       </c>
       <c r="Q57" s="6">
-        <v>4.9295380999999999E-2</v>
+        <v>4.9667696999999997E-2</v>
       </c>
       <c r="R57" s="6">
-        <v>4.9923967999999999E-2</v>
+        <v>4.9568839000000003E-2</v>
       </c>
       <c r="S57" s="6">
-        <v>4.9807835000000002E-2</v>
+        <v>5.0062321E-2</v>
       </c>
       <c r="T57" s="6">
-        <v>4.9401298000000003E-2</v>
+        <v>4.9680850999999998E-2</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -3665,28 +3665,28 @@
         <v>8</v>
       </c>
       <c r="M58" s="6">
-        <v>6.8212852000000004E-2</v>
+        <v>6.7824692000000006E-2</v>
       </c>
       <c r="N58" s="6">
-        <v>6.8477012000000004E-2</v>
+        <v>6.8402096999999995E-2</v>
       </c>
       <c r="O58" s="6">
-        <v>6.8461551999999995E-2</v>
+        <v>6.7922883000000003E-2</v>
       </c>
       <c r="P58" s="6">
-        <v>6.8622321E-2</v>
+        <v>6.8258181000000001E-2</v>
       </c>
       <c r="Q58" s="6">
-        <v>6.8436555999999996E-2</v>
+        <v>6.8326077999999998E-2</v>
       </c>
       <c r="R58" s="6">
-        <v>6.8514145999999998E-2</v>
+        <v>6.8045176999999998E-2</v>
       </c>
       <c r="S58" s="6">
-        <v>6.8813345999999997E-2</v>
+        <v>6.8624876000000001E-2</v>
       </c>
       <c r="T58" s="6">
-        <v>6.8445474000000006E-2</v>
+        <v>6.8935952999999994E-2</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -3695,59 +3695,59 @@
       </c>
       <c r="B59" s="2">
         <f>20*LOG(((B48)*B$40)/(B37*(B$51)), 10)</f>
-        <v>-3.6980910216122687</v>
+        <v>-3.7005448211527474</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59:I59" si="14">20*LOG(((C48)*C$40)/(C37*(C$51)), 10)</f>
-        <v>-3.63317767823062</v>
+        <v>-3.6920930992909944</v>
       </c>
       <c r="D59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.5195624603742126</v>
+        <v>-3.7104837387164387</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.5309827804767608</v>
+        <v>-3.5679757449666964</v>
       </c>
       <c r="F59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.633921722954903</v>
+        <v>-3.62349659330649</v>
       </c>
       <c r="G59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.5398928249956256</v>
+        <v>-3.5923250786733307</v>
       </c>
       <c r="H59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.5366956739335449</v>
+        <v>-3.4422063866578299</v>
       </c>
       <c r="I59" s="2">
         <f t="shared" si="14"/>
-        <v>-3.671521371546814</v>
+        <v>-3.5526743765751152</v>
       </c>
       <c r="M59" s="6">
-        <v>7.3851809000000004E-2</v>
+        <v>7.3756583000000001E-2</v>
       </c>
       <c r="N59" s="6">
-        <v>7.4448108999999998E-2</v>
+        <v>7.4141658999999999E-2</v>
       </c>
       <c r="O59" s="6">
-        <v>7.4213736000000002E-2</v>
+        <v>7.3884620999999998E-2</v>
       </c>
       <c r="P59" s="6">
-        <v>7.4221156999999996E-2</v>
+        <v>7.3916458000000004E-2</v>
       </c>
       <c r="Q59" s="6">
-        <v>7.4111752000000003E-2</v>
+        <v>7.4262365999999996E-2</v>
       </c>
       <c r="R59" s="6">
-        <v>7.4011266000000006E-2</v>
+        <v>7.3969073999999996E-2</v>
       </c>
       <c r="S59" s="6">
-        <v>7.4454658000000007E-2</v>
+        <v>7.4572272999999994E-2</v>
       </c>
       <c r="T59" s="6">
-        <v>7.4084647000000003E-2</v>
+        <v>7.4500366999999998E-2</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -3756,59 +3756,59 @@
       </c>
       <c r="B60" s="2">
         <f t="shared" ref="B60:I60" si="15">20*LOG(((B49)*B$40)/(B38*(B$51)), 10)</f>
-        <v>-0.87282327528582226</v>
+        <v>-0.79680148987785404</v>
       </c>
       <c r="C60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.67677627859035083</v>
+        <v>-0.73198890750372136</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.69172653744626644</v>
+        <v>-0.75117644627815228</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.71513099401081859</v>
+        <v>-0.72954288181619364</v>
       </c>
       <c r="F60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.75046817098444873</v>
+        <v>-0.73905709509047046</v>
       </c>
       <c r="G60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.73822839058796452</v>
+        <v>-0.75019775382123177</v>
       </c>
       <c r="H60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.6619587533027198</v>
+        <v>-0.63235608631497076</v>
       </c>
       <c r="I60" s="2">
         <f t="shared" si="15"/>
-        <v>-0.69636753728764456</v>
+        <v>-0.61639960962273488</v>
       </c>
       <c r="M60" s="6">
-        <v>7.4848792999999997E-2</v>
+        <v>7.4933722999999994E-2</v>
       </c>
       <c r="N60" s="6">
-        <v>7.5100801999999994E-2</v>
+        <v>7.4760287999999994E-2</v>
       </c>
       <c r="O60" s="6">
-        <v>7.4987634999999997E-2</v>
+        <v>7.4914842999999995E-2</v>
       </c>
       <c r="P60" s="6">
-        <v>7.4915684999999996E-2</v>
+        <v>7.4823543000000006E-2</v>
       </c>
       <c r="Q60" s="6">
-        <v>7.5086242999999997E-2</v>
+        <v>7.5091443999999993E-2</v>
       </c>
       <c r="R60" s="6">
-        <v>7.4831612000000006E-2</v>
+        <v>7.5089357999999995E-2</v>
       </c>
       <c r="S60" s="6">
-        <v>7.4999629999999998E-2</v>
+        <v>7.5052596999999999E-2</v>
       </c>
       <c r="T60" s="6">
-        <v>7.4865936999999994E-2</v>
+        <v>7.5083219000000007E-2</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -3817,59 +3817,59 @@
       </c>
       <c r="B61" s="2">
         <f t="shared" ref="B61:I61" si="16">20*LOG(((B50)*B$40)/(B39*(B$51)), 10)</f>
-        <v>-0.14575434314041386</v>
+        <v>-0.11153909854250259</v>
       </c>
       <c r="C61" s="2">
         <f t="shared" si="16"/>
-        <v>2.512237507926917E-2</v>
+        <v>-2.6994836783478256E-2</v>
       </c>
       <c r="D61" s="2">
         <f t="shared" si="16"/>
-        <v>-6.4822553784038136E-3</v>
+        <v>-3.0917985408942601E-2</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="16"/>
-        <v>-5.7607709160747714E-2</v>
+        <v>-5.7758381227361932E-2</v>
       </c>
       <c r="F61" s="2">
         <f t="shared" si="16"/>
-        <v>-3.5284512205711716E-2</v>
+        <v>-2.0795492361053419E-2</v>
       </c>
       <c r="G61" s="2">
         <f t="shared" si="16"/>
-        <v>-5.4569283709857502E-2</v>
+        <v>-4.6969218469719243E-2</v>
       </c>
       <c r="H61" s="2">
         <f t="shared" si="16"/>
-        <v>3.239212937290132E-2</v>
+        <v>4.4009966969627487E-2</v>
       </c>
       <c r="I61" s="2">
         <f t="shared" si="16"/>
-        <v>-2.8376748792804329E-2</v>
+        <v>2.0108634633674401E-2</v>
       </c>
       <c r="M61" s="6">
-        <v>7.4073501E-2</v>
+        <v>7.4095875000000005E-2</v>
       </c>
       <c r="N61" s="6">
-        <v>7.3739886000000004E-2</v>
+        <v>7.3564782999999995E-2</v>
       </c>
       <c r="O61" s="6">
-        <v>7.3732017999999996E-2</v>
+        <v>7.3698482999999995E-2</v>
       </c>
       <c r="P61" s="6">
-        <v>7.4109419999999995E-2</v>
+        <v>7.3928780999999999E-2</v>
       </c>
       <c r="Q61" s="6">
-        <v>7.3733293000000005E-2</v>
+        <v>7.3666491000000001E-2</v>
       </c>
       <c r="R61" s="6">
-        <v>7.3868430999999998E-2</v>
+        <v>7.3648788000000007E-2</v>
       </c>
       <c r="S61" s="6">
-        <v>7.3617630000000003E-2</v>
+        <v>7.3541693000000005E-2</v>
       </c>
       <c r="T61" s="6">
-        <v>7.3978594999999994E-2</v>
+        <v>7.3505528000000001E-2</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -3909,28 +3909,28 @@
         <v>0</v>
       </c>
       <c r="M62" s="6">
-        <v>7.2855771E-2</v>
+        <v>7.28544E-2</v>
       </c>
       <c r="N62" s="6">
-        <v>7.2293072999999999E-2</v>
+        <v>7.2328455999999999E-2</v>
       </c>
       <c r="O62" s="6">
-        <v>7.2535679000000006E-2</v>
+        <v>7.2314358999999995E-2</v>
       </c>
       <c r="P62" s="6">
-        <v>7.3320642000000005E-2</v>
+        <v>7.2936237000000001E-2</v>
       </c>
       <c r="Q62" s="6">
-        <v>7.2364739999999997E-2</v>
+        <v>7.2550267000000002E-2</v>
       </c>
       <c r="R62" s="6">
-        <v>7.2964914000000006E-2</v>
+        <v>7.2134323E-2</v>
       </c>
       <c r="S62" s="6">
-        <v>7.2494417000000005E-2</v>
+        <v>7.2288431E-2</v>
       </c>
       <c r="T62" s="6">
-        <v>7.2973556999999994E-2</v>
+        <v>7.2013319000000006E-2</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -3939,59 +3939,59 @@
       </c>
       <c r="B63" s="2">
         <f t="shared" ref="B63:I63" si="18">20*LOG(((B52)*B$40)/(B41*(B$51)), 10)</f>
-        <v>-9.9562315739595564E-2</v>
+        <v>-0.14432569325912564</v>
       </c>
       <c r="C63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.18454717784804869</v>
+        <v>-0.21517926705121004</v>
       </c>
       <c r="D63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.1534965621188156</v>
+        <v>-0.160574375187649</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.1353656948555827</v>
+        <v>-0.10978617912150725</v>
       </c>
       <c r="F63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.18172670764775553</v>
+        <v>-0.16095871059721018</v>
       </c>
       <c r="G63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.11353588996866029</v>
+        <v>-0.15757388907898492</v>
       </c>
       <c r="H63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.17181649762953038</v>
+        <v>-0.18799381149944722</v>
       </c>
       <c r="I63" s="2">
         <f t="shared" si="18"/>
-        <v>-0.18162702287941113</v>
+        <v>-0.21493015702852442</v>
       </c>
       <c r="M63" s="6">
-        <v>6.9480291999999999E-2</v>
+        <v>6.9485723999999999E-2</v>
       </c>
       <c r="N63" s="6">
-        <v>6.8796702000000001E-2</v>
+        <v>6.9172106999999997E-2</v>
       </c>
       <c r="O63" s="6">
-        <v>6.9327644999999993E-2</v>
+        <v>6.9011352999999998E-2</v>
       </c>
       <c r="P63" s="6">
-        <v>7.0328526000000002E-2</v>
+        <v>6.9958939999999997E-2</v>
       </c>
       <c r="Q63" s="6">
-        <v>6.9095232000000006E-2</v>
+        <v>6.9192334999999994E-2</v>
       </c>
       <c r="R63" s="6">
-        <v>6.9613330000000001E-2</v>
+        <v>6.8692558000000001E-2</v>
       </c>
       <c r="S63" s="6">
-        <v>6.9358185000000003E-2</v>
+        <v>6.8997360999999993E-2</v>
       </c>
       <c r="T63" s="6">
-        <v>6.9980472000000002E-2</v>
+        <v>6.8634182000000002E-2</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -4000,59 +4000,59 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64:I64" si="19">20*LOG(((B53)*B$40)/(B42*(B$51)), 10)</f>
-        <v>-0.23897968394121738</v>
+        <v>-0.26341173393944972</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.36893275645620427</v>
+        <v>-0.34002066090271843</v>
       </c>
       <c r="D64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.29287159892476944</v>
+        <v>-0.33965011708180048</v>
       </c>
       <c r="E64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.20952117793528841</v>
+        <v>-0.20561211616645478</v>
       </c>
       <c r="F64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.34395378368504392</v>
+        <v>-0.31670952061954138</v>
       </c>
       <c r="G64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.24082724378657663</v>
+        <v>-0.31930463398704179</v>
       </c>
       <c r="H64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.32744078021360401</v>
+        <v>-0.35701980865628991</v>
       </c>
       <c r="I64" s="2">
         <f t="shared" si="19"/>
-        <v>-0.26787828323755325</v>
+        <v>-0.39865866294939545</v>
       </c>
       <c r="M64" s="6">
-        <v>5.6386000999999998E-2</v>
+        <v>5.6000154000000003E-2</v>
       </c>
       <c r="N64" s="6">
-        <v>5.5701266999999999E-2</v>
+        <v>5.6415170000000001E-2</v>
       </c>
       <c r="O64" s="6">
-        <v>5.6465998000000003E-2</v>
+        <v>5.5904038000000003E-2</v>
       </c>
       <c r="P64" s="6">
-        <v>5.8106456000000001E-2</v>
+        <v>5.7364396999999998E-2</v>
       </c>
       <c r="Q64" s="6">
-        <v>5.6130592E-2</v>
+        <v>5.6276622999999998E-2</v>
       </c>
       <c r="R64" s="6">
-        <v>5.6656115E-2</v>
+        <v>5.5478609999999998E-2</v>
       </c>
       <c r="S64" s="6">
-        <v>5.6843578999999998E-2</v>
+        <v>5.5995174000000002E-2</v>
       </c>
       <c r="T64" s="6">
-        <v>5.7500194999999997E-2</v>
+        <v>5.5604409E-2</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -4061,35 +4061,35 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65:I65" si="20">20*LOG(((B54)*B$40)/(B43*(B$51)), 10)</f>
-        <v>-0.64430317265970904</v>
+        <v>-0.68587703706560654</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.78508307491504226</v>
+        <v>-0.74711214499074363</v>
       </c>
       <c r="D65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.71671339726616667</v>
+        <v>-0.74878566758409815</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.54055732631082476</v>
+        <v>-0.57641596203012779</v>
       </c>
       <c r="F65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.77007357042859015</v>
+        <v>-0.72602422607683914</v>
       </c>
       <c r="G65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.64212423593933909</v>
+        <v>-0.76033294391102912</v>
       </c>
       <c r="H65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.70392426653946005</v>
+        <v>-0.76644151513505665</v>
       </c>
       <c r="I65" s="2">
         <f t="shared" si="20"/>
-        <v>-0.64104548330058131</v>
+        <v>-0.82023790498810423</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -4098,35 +4098,35 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66:I66" si="21">20*LOG(((B55)*B$40)/(B44*(B$51)), 10)</f>
-        <v>-2.4530312874357705</v>
+        <v>-2.5411109590487246</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.6296259747106059</v>
+        <v>-2.5142866320198158</v>
       </c>
       <c r="D66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.4697402322349356</v>
+        <v>-2.5885534044412672</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.2124828821942129</v>
+        <v>-2.326421457783975</v>
       </c>
       <c r="F66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.5496663206052301</v>
+        <v>-2.5113940868780409</v>
       </c>
       <c r="G66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.4115349555571464</v>
+        <v>-2.6205450343357919</v>
       </c>
       <c r="H66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.4168879619286261</v>
+        <v>-2.5819763127390285</v>
       </c>
       <c r="I66" s="2">
         <f t="shared" si="21"/>
-        <v>-2.3208882225237479</v>
+        <v>-2.6494687914650346</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -4177,35 +4177,35 @@
       </c>
       <c r="B70" s="1">
         <f>M33</f>
-        <v>1.5456351E-2</v>
+        <v>1.5364991E-2</v>
       </c>
       <c r="C70" s="1">
         <f t="shared" ref="C70:I70" si="22">N33</f>
-        <v>1.5186470000000001E-2</v>
+        <v>1.5212253E-2</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5170253E-2</v>
+        <v>1.5245514999999999E-2</v>
       </c>
       <c r="E70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5258571E-2</v>
+        <v>1.5310472E-2</v>
       </c>
       <c r="F70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5220925E-2</v>
+        <v>1.5230541E-2</v>
       </c>
       <c r="G70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5265224000000001E-2</v>
+        <v>1.5342536E-2</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5154994999999999E-2</v>
+        <v>1.5106544E-2</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="22"/>
-        <v>1.5214017999999999E-2</v>
+        <v>1.5176354E-2</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -4214,35 +4214,35 @@
       </c>
       <c r="B71" s="1">
         <f t="shared" ref="B71:B77" si="23">M34</f>
-        <v>1.5379199E-2</v>
+        <v>1.5263607E-2</v>
       </c>
       <c r="C71" s="1">
         <f t="shared" ref="C71:C77" si="24">N34</f>
-        <v>1.5056742E-2</v>
+        <v>1.5078693000000001E-2</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" ref="D71:D77" si="25">O34</f>
-        <v>1.5084901E-2</v>
+        <v>1.5123292999999999E-2</v>
       </c>
       <c r="E71" s="1">
         <f t="shared" ref="E71:E77" si="26">P34</f>
-        <v>1.5190164000000001E-2</v>
+        <v>1.5232614E-2</v>
       </c>
       <c r="F71" s="1">
         <f t="shared" ref="F71:F77" si="27">Q34</f>
-        <v>1.5094196000000001E-2</v>
+        <v>1.5132318000000001E-2</v>
       </c>
       <c r="G71" s="1">
         <f t="shared" ref="G71:G77" si="28">R34</f>
-        <v>1.5195800000000001E-2</v>
+        <v>1.5243675999999999E-2</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" ref="H71:H77" si="29">S34</f>
-        <v>1.504753E-2</v>
+        <v>1.5021514999999999E-2</v>
       </c>
       <c r="I71" s="1">
         <f t="shared" ref="I71:I77" si="30">T34</f>
-        <v>1.5094394000000001E-2</v>
+        <v>1.5077962E-2</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -4251,35 +4251,35 @@
       </c>
       <c r="B72" s="1">
         <f t="shared" si="23"/>
-        <v>1.5373443000000001E-2</v>
+        <v>1.5291971E-2</v>
       </c>
       <c r="C72" s="1">
         <f t="shared" si="24"/>
-        <v>1.5092080000000001E-2</v>
+        <v>1.5118056E-2</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="25"/>
-        <v>1.5114818E-2</v>
+        <v>1.5153069999999999E-2</v>
       </c>
       <c r="E72" s="1">
         <f t="shared" si="26"/>
-        <v>1.5218784000000001E-2</v>
+        <v>1.5277394999999999E-2</v>
       </c>
       <c r="F72" s="1">
         <f t="shared" si="27"/>
-        <v>1.5115544E-2</v>
+        <v>1.5174701000000001E-2</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="28"/>
-        <v>1.5218046000000001E-2</v>
+        <v>1.5266620999999999E-2</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="29"/>
-        <v>1.5087816E-2</v>
+        <v>1.5092365999999999E-2</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="30"/>
-        <v>1.5121875E-2</v>
+        <v>1.5140532999999999E-2</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -4288,35 +4288,35 @@
       </c>
       <c r="B73" s="1">
         <f t="shared" si="23"/>
-        <v>1.5406510999999999E-2</v>
+        <v>1.5386696E-2</v>
       </c>
       <c r="C73" s="1">
         <f t="shared" si="24"/>
-        <v>1.5250400000000001E-2</v>
+        <v>1.528419E-2</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="25"/>
-        <v>1.5250825000000001E-2</v>
+        <v>1.5296255999999999E-2</v>
       </c>
       <c r="E73" s="1">
         <f t="shared" si="26"/>
-        <v>1.5326559E-2</v>
+        <v>1.5384824E-2</v>
       </c>
       <c r="F73" s="1">
         <f t="shared" si="27"/>
-        <v>1.5252496000000001E-2</v>
+        <v>1.531239E-2</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="28"/>
-        <v>1.5317608E-2</v>
+        <v>1.5371806E-2</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="29"/>
-        <v>1.5258776E-2</v>
+        <v>1.5277892E-2</v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="30"/>
-        <v>1.5274411E-2</v>
+        <v>1.5328534E-2</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -4325,35 +4325,35 @@
       </c>
       <c r="B74" s="1">
         <f t="shared" si="23"/>
-        <v>1.5417923E-2</v>
+        <v>1.5416226999999999E-2</v>
       </c>
       <c r="C74" s="1">
         <f t="shared" si="24"/>
-        <v>1.5326576999999999E-2</v>
+        <v>1.5356242000000001E-2</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="25"/>
-        <v>1.5325893E-2</v>
+        <v>1.5365182E-2</v>
       </c>
       <c r="E74" s="1">
         <f t="shared" si="26"/>
-        <v>1.5367877E-2</v>
+        <v>1.5418064E-2</v>
       </c>
       <c r="F74" s="1">
         <f t="shared" si="27"/>
-        <v>1.5325834E-2</v>
+        <v>1.5372701000000001E-2</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="28"/>
-        <v>1.5358261E-2</v>
+        <v>1.5414761000000001E-2</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="29"/>
-        <v>1.5337750000000001E-2</v>
+        <v>1.5351508999999999E-2</v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="30"/>
-        <v>1.5349091E-2</v>
+        <v>1.5399862E-2</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -4362,35 +4362,35 @@
       </c>
       <c r="B75" s="1">
         <f t="shared" si="23"/>
-        <v>1.5422623999999999E-2</v>
+        <v>1.5432939E-2</v>
       </c>
       <c r="C75" s="1">
         <f t="shared" si="24"/>
-        <v>1.5359256999999999E-2</v>
+        <v>1.5383913000000001E-2</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" si="25"/>
-        <v>1.5359533E-2</v>
+        <v>1.5398755E-2</v>
       </c>
       <c r="E75" s="1">
         <f t="shared" si="26"/>
-        <v>1.5389976E-2</v>
+        <v>1.5435116E-2</v>
       </c>
       <c r="F75" s="1">
         <f t="shared" si="27"/>
-        <v>1.5360478E-2</v>
+        <v>1.5395997E-2</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="28"/>
-        <v>1.5382511E-2</v>
+        <v>1.5437895E-2</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="29"/>
-        <v>1.5375088E-2</v>
+        <v>1.5379514E-2</v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="30"/>
-        <v>1.5383152000000001E-2</v>
+        <v>1.5430251000000001E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -4399,35 +4399,35 @@
       </c>
       <c r="B76" s="1">
         <f t="shared" si="23"/>
-        <v>1.5426034999999999E-2</v>
+        <v>1.5458361E-2</v>
       </c>
       <c r="C76" s="1">
         <f t="shared" si="24"/>
-        <v>1.5373392E-2</v>
+        <v>1.5422467E-2</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="25"/>
-        <v>1.5372200000000001E-2</v>
+        <v>1.5435766E-2</v>
       </c>
       <c r="E76" s="1">
         <f t="shared" si="26"/>
-        <v>1.5396236000000001E-2</v>
+        <v>1.5464623E-2</v>
       </c>
       <c r="F76" s="1">
         <f t="shared" si="27"/>
-        <v>1.5369041999999999E-2</v>
+        <v>1.5431321E-2</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="28"/>
-        <v>1.5391066E-2</v>
+        <v>1.5465848000000001E-2</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="29"/>
-        <v>1.5389130000000001E-2</v>
+        <v>1.5410093E-2</v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="30"/>
-        <v>1.5398926E-2</v>
+        <v>1.5461403E-2</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -4436,35 +4436,35 @@
       </c>
       <c r="B77" s="1">
         <f t="shared" si="23"/>
-        <v>1.5442566E-2</v>
+        <v>1.5474115E-2</v>
       </c>
       <c r="C77" s="1">
         <f t="shared" si="24"/>
-        <v>1.5396356E-2</v>
+        <v>1.5436159E-2</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="25"/>
-        <v>1.5397286E-2</v>
+        <v>1.5453435E-2</v>
       </c>
       <c r="E77" s="1">
         <f t="shared" si="26"/>
-        <v>1.5415491999999999E-2</v>
+        <v>1.5475342E-2</v>
       </c>
       <c r="F77" s="1">
         <f t="shared" si="27"/>
-        <v>1.5393258999999999E-2</v>
+        <v>1.5446117000000001E-2</v>
       </c>
       <c r="G77" s="1">
         <f t="shared" si="28"/>
-        <v>1.5412945000000001E-2</v>
+        <v>1.5482644E-2</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="29"/>
-        <v>1.5411213999999999E-2</v>
+        <v>1.543079E-2</v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="30"/>
-        <v>1.5420672E-2</v>
+        <v>1.5478779999999999E-2</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -4515,35 +4515,35 @@
       </c>
       <c r="B81" s="1">
         <f>M41</f>
-        <v>4.8893674999999998E-2</v>
+        <v>4.8829499999999998E-2</v>
       </c>
       <c r="C81" s="1">
         <f t="shared" ref="C81:I81" si="31">N41</f>
-        <v>4.8400595999999997E-2</v>
+        <v>4.8345774000000001E-2</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8553981000000003E-2</v>
+        <v>4.8113695999999997E-2</v>
       </c>
       <c r="E81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8901728999999998E-2</v>
+        <v>4.8806503000000001E-2</v>
       </c>
       <c r="F81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8554952999999998E-2</v>
+        <v>4.8506524000000002E-2</v>
       </c>
       <c r="G81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8802707000000001E-2</v>
+        <v>4.8574570999999997E-2</v>
       </c>
       <c r="H81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8563343000000002E-2</v>
+        <v>4.8942260000000001E-2</v>
       </c>
       <c r="I81" s="1">
         <f t="shared" si="31"/>
-        <v>4.8299680999999997E-2</v>
+        <v>4.9176365E-2</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -4552,35 +4552,35 @@
       </c>
       <c r="B82" s="1">
         <f t="shared" ref="B82:B88" si="32">M42</f>
-        <v>6.7720040999999995E-2</v>
+        <v>6.7165694999999997E-2</v>
       </c>
       <c r="C82" s="1">
         <f t="shared" ref="C82:C88" si="33">N42</f>
-        <v>6.7619525E-2</v>
+        <v>6.7156515999999999E-2</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" ref="D82:D88" si="34">O42</f>
-        <v>6.7129247000000003E-2</v>
+        <v>6.6872925E-2</v>
       </c>
       <c r="E82" s="1">
         <f t="shared" ref="E82:E88" si="35">P42</f>
-        <v>6.7505783999999999E-2</v>
+        <v>6.7651956999999999E-2</v>
       </c>
       <c r="F82" s="1">
         <f t="shared" ref="F82:F88" si="36">Q42</f>
-        <v>6.7328595000000005E-2</v>
+        <v>6.7152492999999994E-2</v>
       </c>
       <c r="G82" s="1">
         <f t="shared" ref="G82:G88" si="37">R42</f>
-        <v>6.7247323999999997E-2</v>
+        <v>6.7042432999999998E-2</v>
       </c>
       <c r="H82" s="1">
         <f t="shared" ref="H82:H88" si="38">S42</f>
-        <v>6.7851111000000006E-2</v>
+        <v>6.7812501999999997E-2</v>
       </c>
       <c r="I82" s="1">
         <f t="shared" ref="I82:I88" si="39">T42</f>
-        <v>6.7479364999999999E-2</v>
+        <v>6.8044059000000004E-2</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -4589,35 +4589,35 @@
       </c>
       <c r="B83" s="1">
         <f t="shared" si="32"/>
-        <v>7.3252185999999997E-2</v>
+        <v>7.3087201000000004E-2</v>
       </c>
       <c r="C83" s="1">
         <f t="shared" si="33"/>
-        <v>7.3296040000000007E-2</v>
+        <v>7.3272184000000004E-2</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="34"/>
-        <v>7.2994805999999995E-2</v>
+        <v>7.2809674000000005E-2</v>
       </c>
       <c r="E83" s="1">
         <f t="shared" si="35"/>
-        <v>7.3272466999999994E-2</v>
+        <v>7.3401794000000006E-2</v>
       </c>
       <c r="F83" s="1">
         <f t="shared" si="36"/>
-        <v>7.2891787E-2</v>
+        <v>7.3207773000000004E-2</v>
       </c>
       <c r="G83" s="1">
         <f t="shared" si="37"/>
-        <v>7.2940654999999993E-2</v>
+        <v>7.2836310000000001E-2</v>
       </c>
       <c r="H83" s="1">
         <f t="shared" si="38"/>
-        <v>7.3257751999999995E-2</v>
+        <v>7.3530159999999997E-2</v>
       </c>
       <c r="I83" s="1">
         <f t="shared" si="39"/>
-        <v>7.3206119E-2</v>
+        <v>7.3546349999999996E-2</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -4626,35 +4626,35 @@
       </c>
       <c r="B84" s="1">
         <f t="shared" si="32"/>
-        <v>7.4525810999999997E-2</v>
+        <v>7.4561163999999999E-2</v>
       </c>
       <c r="C84" s="1">
         <f t="shared" si="33"/>
-        <v>7.3929942999999998E-2</v>
+        <v>7.4071004999999995E-2</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="34"/>
-        <v>7.3795400999999997E-2</v>
+        <v>7.4062839000000005E-2</v>
       </c>
       <c r="E84" s="1">
         <f t="shared" si="35"/>
-        <v>7.4281535999999995E-2</v>
+        <v>7.4305385000000002E-2</v>
       </c>
       <c r="F84" s="1">
         <f t="shared" si="36"/>
-        <v>7.3930033000000006E-2</v>
+        <v>7.4136964999999999E-2</v>
       </c>
       <c r="G84" s="1">
         <f t="shared" si="37"/>
-        <v>7.3860325000000004E-2</v>
+        <v>7.3857188000000004E-2</v>
       </c>
       <c r="H84" s="1">
         <f t="shared" si="38"/>
-        <v>7.3983974999999993E-2</v>
+        <v>7.4293256000000002E-2</v>
       </c>
       <c r="I84" s="1">
         <f t="shared" si="39"/>
-        <v>7.4154221000000006E-2</v>
+        <v>7.4216239000000003E-2</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -4663,35 +4663,35 @@
       </c>
       <c r="B85" s="1">
         <f t="shared" si="32"/>
-        <v>7.4060424999999999E-2</v>
+        <v>7.3737345999999995E-2</v>
       </c>
       <c r="C85" s="1">
         <f t="shared" si="33"/>
-        <v>7.2829335999999995E-2</v>
+        <v>7.3081136000000005E-2</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="34"/>
-        <v>7.2868265000000002E-2</v>
+        <v>7.3108121999999998E-2</v>
       </c>
       <c r="E85" s="1">
         <f t="shared" si="35"/>
-        <v>7.3500827000000005E-2</v>
+        <v>7.3708676000000001E-2</v>
       </c>
       <c r="F85" s="1">
         <f t="shared" si="36"/>
-        <v>7.2823256000000003E-2</v>
+        <v>7.3098927999999994E-2</v>
       </c>
       <c r="G85" s="1">
         <f t="shared" si="37"/>
-        <v>7.3190346000000003E-2</v>
+        <v>7.3057324000000007E-2</v>
       </c>
       <c r="H85" s="1">
         <f t="shared" si="38"/>
-        <v>7.2956398000000006E-2</v>
+        <v>7.3199920000000002E-2</v>
       </c>
       <c r="I85" s="1">
         <f t="shared" si="39"/>
-        <v>7.3363669000000006E-2</v>
+        <v>7.2974025999999997E-2</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -4700,35 +4700,35 @@
       </c>
       <c r="B86" s="1">
         <f t="shared" si="32"/>
-        <v>7.3310606E-2</v>
+        <v>7.3021113999999998E-2</v>
       </c>
       <c r="C86" s="1">
         <f t="shared" si="33"/>
-        <v>7.1946762999999997E-2</v>
+        <v>7.2269976E-2</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="34"/>
-        <v>7.2069384E-2</v>
+        <v>7.2029917999999998E-2</v>
       </c>
       <c r="E86" s="1">
         <f t="shared" si="35"/>
-        <v>7.3216870000000003E-2</v>
+        <v>7.3393299999999995E-2</v>
       </c>
       <c r="F86" s="1">
         <f t="shared" si="36"/>
-        <v>7.2059235999999999E-2</v>
+        <v>7.2220184000000007E-2</v>
       </c>
       <c r="G86" s="1">
         <f t="shared" si="37"/>
-        <v>7.2695039000000003E-2</v>
+        <v>7.1956596999999997E-2</v>
       </c>
       <c r="H86" s="1">
         <f t="shared" si="38"/>
-        <v>7.2240911000000005E-2</v>
+        <v>7.2313681000000005E-2</v>
       </c>
       <c r="I86" s="1">
         <f t="shared" si="39"/>
-        <v>7.2916083000000007E-2</v>
+        <v>7.1914381999999999E-2</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -4737,35 +4737,35 @@
       </c>
       <c r="B87" s="1">
         <f t="shared" si="32"/>
-        <v>7.0239446999999997E-2</v>
+        <v>7.0084258999999996E-2</v>
       </c>
       <c r="C87" s="1">
         <f t="shared" si="33"/>
-        <v>6.8778678999999995E-2</v>
+        <v>6.9415346000000003E-2</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="34"/>
-        <v>6.9237999999999994E-2</v>
+        <v>6.9206662000000002E-2</v>
       </c>
       <c r="E87" s="1">
         <f t="shared" si="35"/>
-        <v>7.0637718000000002E-2</v>
+        <v>7.0685713999999997E-2</v>
       </c>
       <c r="F87" s="1">
         <f t="shared" si="36"/>
-        <v>6.9006965000000003E-2</v>
+        <v>6.9369897E-2</v>
       </c>
       <c r="G87" s="1">
         <f t="shared" si="37"/>
-        <v>6.9739640000000006E-2</v>
+        <v>6.8763234000000006E-2</v>
       </c>
       <c r="H87" s="1">
         <f t="shared" si="38"/>
-        <v>6.9361254999999997E-2</v>
+        <v>6.9219053000000003E-2</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="39"/>
-        <v>7.0175751999999994E-2</v>
+        <v>6.8996452E-2</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -4774,35 +4774,35 @@
       </c>
       <c r="B88" s="1">
         <f t="shared" si="32"/>
-        <v>5.7371872999999997E-2</v>
+        <v>5.6911695999999998E-2</v>
       </c>
       <c r="C88" s="1">
         <f t="shared" si="33"/>
-        <v>5.6134224000000003E-2</v>
+        <v>5.7009707999999999E-2</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="34"/>
-        <v>5.6891110000000002E-2</v>
+        <v>5.6477338000000002E-2</v>
       </c>
       <c r="E88" s="1">
         <f t="shared" si="35"/>
-        <v>5.8820426000000002E-2</v>
+        <v>5.8397401000000002E-2</v>
       </c>
       <c r="F88" s="1">
         <f t="shared" si="36"/>
-        <v>5.6537110000000002E-2</v>
+        <v>5.6859634999999999E-2</v>
       </c>
       <c r="G88" s="1">
         <f t="shared" si="37"/>
-        <v>5.7187389999999998E-2</v>
+        <v>5.5951099999999997E-2</v>
       </c>
       <c r="H88" s="1">
         <f t="shared" si="38"/>
-        <v>5.7378247E-2</v>
+        <v>5.6663367999999999E-2</v>
       </c>
       <c r="I88" s="1">
         <f t="shared" si="39"/>
-        <v>5.8160684999999997E-2</v>
+        <v>5.6356705999999999E-2</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -4853,35 +4853,35 @@
       </c>
       <c r="B92" s="2">
         <f>20*LOG(((B81/5)*B$73)/(B70*(B$84/5)), 10)</f>
-        <v>-3.6891340528825909</v>
+        <v>-3.664346777939111</v>
       </c>
       <c r="C92" s="2">
         <f t="shared" ref="C92:I92" si="40">20*LOG(((C81/5)*C$73)/(C70*(C$84/5)), 10)</f>
-        <v>-3.6429052702734128</v>
+        <v>-3.6648166311284895</v>
       </c>
       <c r="D92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.5900787810789625</v>
+        <v>-3.7177718382482867</v>
       </c>
       <c r="E92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.5925172487574679</v>
+        <v>-3.6087728905538619</v>
       </c>
       <c r="F92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.6337497643784462</v>
+        <v>-3.6381399445155695</v>
       </c>
       <c r="G92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.5695906489463964</v>
+        <v>-3.6231210203448097</v>
       </c>
       <c r="H92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.5973037222666071</v>
+        <v>-3.5273411354387409</v>
       </c>
       <c r="I92" s="2">
         <f t="shared" si="40"/>
-        <v>-3.6894213590209581</v>
+        <v>-3.488186906443826</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -4890,35 +4890,35 @@
       </c>
       <c r="B93" s="2">
         <f t="shared" ref="B93:I93" si="41">20*LOG(((B82/5)*B$73)/(B71*(B$84/5)), 10)</f>
-        <v>-0.81637833205311994</v>
+        <v>-0.83753936912762783</v>
       </c>
       <c r="C93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.66396059094300885</v>
+        <v>-0.73362702310050387</v>
       </c>
       <c r="D93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.72733296005432446</v>
+        <v>-0.78822517861218799</v>
       </c>
       <c r="E93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.75315382896561045</v>
+        <v>-0.72843658555383706</v>
       </c>
       <c r="F93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.72180827105102974</v>
+        <v>-0.75670280309535132</v>
       </c>
       <c r="G93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.74537650358771079</v>
+        <v>-0.76815632922028043</v>
       </c>
       <c r="H93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.63052436673401879</v>
+        <v>-0.64579848187395528</v>
       </c>
       <c r="I93" s="2">
         <f t="shared" si="41"/>
-        <v>-0.71632198924392643</v>
+        <v>-0.61101505250453259</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -4927,35 +4927,35 @@
       </c>
       <c r="B94" s="2">
         <f t="shared" ref="B94:I94" si="42">20*LOG(((B83/5)*B$73)/(B72*(B$84/5)), 10)</f>
-        <v>-0.1310592980541696</v>
+        <v>-0.11978883084387541</v>
       </c>
       <c r="C94" s="2">
         <f t="shared" si="42"/>
-        <v>1.5845526152597406E-2</v>
+        <v>7.4754988088050517E-4</v>
       </c>
       <c r="D94" s="2">
         <f t="shared" si="42"/>
-        <v>-1.6938456298792346E-2</v>
+        <v>-6.6535101680261319E-2</v>
       </c>
       <c r="E94" s="2">
         <f t="shared" si="42"/>
-        <v>-5.7507066553697445E-2</v>
+        <v>-4.540778742993444E-2</v>
       </c>
       <c r="F94" s="2">
         <f t="shared" si="42"/>
-        <v>-4.4503293226553095E-2</v>
+        <v>-3.1095360258832166E-2</v>
       </c>
       <c r="G94" s="2">
         <f t="shared" si="42"/>
-        <v>-5.2189936086409816E-2</v>
+        <v>-6.1257245191478113E-2</v>
       </c>
       <c r="H94" s="2">
         <f t="shared" si="42"/>
-        <v>1.2184897752901727E-2</v>
+        <v>1.6444515247621572E-2</v>
       </c>
       <c r="I94" s="2">
         <f t="shared" si="42"/>
-        <v>-2.459329887802017E-2</v>
+        <v>2.8432788231662221E-2</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -5001,35 +5001,35 @@
       </c>
       <c r="B96" s="2">
         <f t="shared" ref="B96:I96" si="44">20*LOG(((B85/5)*B$73)/(B74*(B$84/5)), 10)</f>
-        <v>-6.0841697509282644E-2</v>
+        <v>-0.11315800721543473</v>
       </c>
       <c r="C96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.17355914989785776</v>
+        <v>-0.15770934812019854</v>
       </c>
       <c r="D96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.15246638869571233</v>
+        <v>-0.15174586143748825</v>
       </c>
       <c r="E96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.11515728917063225</v>
+        <v>-8.8779805327084932E-2</v>
       </c>
       <c r="F96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.17268009499094422</v>
+        <v>-0.15661986623863233</v>
       </c>
       <c r="G96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.10217013439304393</v>
+        <v>-0.11881817537242913</v>
       </c>
       <c r="H96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.1663246896651224</v>
+        <v>-0.17052843534430345</v>
       </c>
       <c r="I96" s="2">
         <f t="shared" si="44"/>
-        <v>-0.13546045526462047</v>
+        <v>-0.18693685319928352</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -5038,35 +5038,35 @@
       </c>
       <c r="B97" s="2">
         <f t="shared" ref="B97:I97" si="45">20*LOG(((B86/5)*B$73)/(B75*(B$84/5)), 10)</f>
-        <v>-0.15187747318385247</v>
+        <v>-0.20734982702764798</v>
       </c>
       <c r="C97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.29796169413545126</v>
+        <v>-0.2702942818785925</v>
       </c>
       <c r="D97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.2672632137824536</v>
+        <v>-0.29975802047970129</v>
       </c>
       <c r="E97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.16125995510145749</v>
+        <v>-0.13562477330377914</v>
       </c>
       <c r="F97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.28390115339424138</v>
+        <v>-0.27482096759233449</v>
       </c>
       <c r="G97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.17485447291505984</v>
+        <v>-0.2637068032106179</v>
       </c>
       <c r="H97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.2730471967009343</v>
+        <v>-0.29216198632775658</v>
       </c>
       <c r="I97" s="2">
         <f t="shared" si="45"/>
-        <v>-0.207868106228773</v>
+        <v>-0.33111117308906118</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -5075,35 +5075,35 @@
       </c>
       <c r="B98" s="2">
         <f t="shared" ref="B98:I98" si="46">20*LOG(((B87/5)*B$73)/(B76*(B$84/5)), 10)</f>
-        <v>-0.52551282282004774</v>
+        <v>-0.57820530442565421</v>
       </c>
       <c r="C98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.69710014885339522</v>
+        <v>-0.64208332605739282</v>
       </c>
       <c r="D98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.62254942318667972</v>
+        <v>-0.6679099132893469</v>
       </c>
       <c r="E98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.47628226146856145</v>
+        <v>-0.47870888688890273</v>
       </c>
       <c r="F98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.66467701229760368</v>
+        <v>-0.64447753950359599</v>
       </c>
       <c r="G98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.54018525069118173</v>
+        <v>-0.67370635026261894</v>
       </c>
       <c r="H98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.63430179156361266</v>
+        <v>-0.68931126010293264</v>
       </c>
       <c r="I98" s="2">
         <f t="shared" si="46"/>
-        <v>-0.54949522779650595</v>
+        <v>-0.70840924383050718</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -5112,35 +5112,35 @@
       </c>
       <c r="B99" s="2">
         <f t="shared" ref="B99:I99" si="47">20*LOG(((B88/5)*B$73)/(B77*(B$84/5)), 10)</f>
-        <v>-2.2924570038981433</v>
+        <v>-2.395431960791321</v>
       </c>
       <c r="C99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.4745871521877834</v>
+        <v>-2.3599247236888847</v>
       </c>
       <c r="D99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.3427145747948637</v>
+        <v>-2.4433204679588112</v>
       </c>
       <c r="E99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.07730877718142</v>
+        <v>-2.1434898572855707</v>
       </c>
       <c r="F99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.4095390402903285</v>
+        <v>-2.3801414767606599</v>
       </c>
       <c r="G99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.2761123163895123</v>
+        <v>-2.4740874497839456</v>
       </c>
       <c r="H99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.2941507823686766</v>
+        <v>-2.4394346536579952</v>
       </c>
       <c r="I99" s="2">
         <f t="shared" si="47"/>
-        <v>-2.1929038301309696</v>
+        <v>-2.4757889451003545</v>
       </c>
     </row>
   </sheetData>
